--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -652,7 +652,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -972,7 +972,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1372,7 +1372,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1502,7 +1502,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1692,7 +1692,7 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1842,7 +1842,7 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -2020,7 +2020,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -2528,7 +2528,7 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -2856,7 +2856,7 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -2982,7 +2982,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -3084,7 +3084,7 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -3182,7 +3182,7 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -3304,7 +3304,7 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -3394,7 +3394,7 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -3488,7 +3488,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -3578,7 +3578,7 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -3688,7 +3688,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -3778,7 +3778,7 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -3868,7 +3868,7 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -4068,7 +4068,7 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -4198,7 +4198,7 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -4288,7 +4288,7 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -4378,7 +4378,7 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -4488,7 +4488,7 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -4668,7 +4668,7 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -4868,7 +4868,7 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -4974,7 +4974,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -5196,7 +5196,7 @@
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -5310,7 +5310,7 @@
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -5536,7 +5536,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -5666,7 +5666,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -6046,7 +6046,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -6386,7 +6386,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -6576,7 +6576,7 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -6726,7 +6726,7 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -6904,7 +6904,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -7154,7 +7154,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -7428,7 +7428,7 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -7586,7 +7586,7 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -7890,7 +7890,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -7992,7 +7992,7 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -8090,7 +8090,7 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -8212,7 +8212,7 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -8302,7 +8302,7 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -8396,7 +8396,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8486,7 +8486,7 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8596,7 +8596,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -8686,7 +8686,7 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -8882,7 +8882,7 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9122,7 +9122,7 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9220,7 +9220,7 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9318,7 +9318,7 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9428,7 +9428,7 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9542,7 +9542,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -9636,7 +9636,7 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -9734,7 +9734,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -9844,7 +9844,7 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>■ Row 1 (QWERTY 上段)</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -9950,7 +9950,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>■ Row 2 (home row)</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10176,7 +10176,7 @@
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>■ Row 3 (Z row)</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -10290,7 +10290,7 @@
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>■ Row 4 (thumb)</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -722,7 +722,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -1042,7 +1042,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -1442,7 +1442,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1572,7 +1572,7 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1762,7 +1762,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr"/>
@@ -2090,7 +2090,7 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -2598,7 +2598,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -2756,7 +2756,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -3154,7 +3154,7 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr"/>
@@ -3374,7 +3374,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr"/>
@@ -3464,7 +3464,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr"/>
@@ -3558,7 +3558,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr"/>
@@ -3648,7 +3648,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr"/>
@@ -3758,7 +3758,7 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr"/>
@@ -3938,7 +3938,7 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr"/>
@@ -4028,7 +4028,7 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr"/>
@@ -4138,7 +4138,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -4268,7 +4268,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr"/>
@@ -4448,7 +4448,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr"/>
@@ -4558,7 +4558,7 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr"/>
@@ -4648,7 +4648,7 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr"/>
@@ -4738,7 +4738,7 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr"/>
@@ -4828,7 +4828,7 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr"/>
@@ -4938,7 +4938,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr"/>
@@ -5044,7 +5044,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -5380,7 +5380,7 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5736,7 +5736,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -6646,7 +6646,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr"/>
@@ -6974,7 +6974,7 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr"/>
@@ -7224,7 +7224,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -7498,7 +7498,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -7656,7 +7656,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr"/>
@@ -7826,7 +7826,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr"/>
@@ -7960,7 +7960,7 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -8062,7 +8062,7 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr"/>
@@ -8282,7 +8282,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr"/>
@@ -8372,7 +8372,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr"/>
@@ -8466,7 +8466,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr"/>
@@ -8556,7 +8556,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr"/>
@@ -8756,7 +8756,7 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr"/>
@@ -8854,7 +8854,7 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr"/>
@@ -8952,7 +8952,7 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -9192,7 +9192,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr"/>
@@ -9290,7 +9290,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr"/>
@@ -9388,7 +9388,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr"/>
@@ -9498,7 +9498,7 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -9612,7 +9612,7 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -9706,7 +9706,7 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr"/>
@@ -9804,7 +9804,7 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr"/>
@@ -9914,7 +9914,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr"/>
@@ -10020,7 +10020,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -10360,7 +10360,7 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>単発タップ</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -2059,13 +2059,13 @@
       <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Y
-&amp;mm_vim_shift_y</t>
+&amp;mm_vim_y</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
           <t>U
-&amp;mm_vim_ctrl_u</t>
+&amp;mm_vim_u</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -2077,7 +2077,7 @@
       <c r="M29" s="7" t="inlineStr">
         <is>
           <t>O
-&amp;mm_vim_shift_o</t>
+&amp;mm_vim_o</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
@@ -2280,7 +2280,7 @@
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>D
-&amp;mm_vim_ctrl_then_shift_d</t>
+&amp;mm_vim_d</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -6943,13 +6943,13 @@
       <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Y
-&amp;mm_vim_shift_y</t>
+&amp;mm_vim_y</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
           <t>U
-&amp;mm_vim_ctrl_u</t>
+&amp;mm_vim_u</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -6961,7 +6961,7 @@
       <c r="M29" s="7" t="inlineStr">
         <is>
           <t>O
-&amp;mm_vim_shift_o</t>
+&amp;mm_vim_o</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
@@ -6999,18 +6999,18 @@
       <c r="I30" s="9" t="inlineStr"/>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_shift_y[0] → td_vim_y[0] → &amp;none</t>
+          <t>mm_vim_y[0] → td_vim_y[0] → &amp;none</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_ctrl_u[0] → &amp;kp LC(Z)</t>
+          <t>mm_vim_u[0] → &amp;kp LC(Z)</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr"/>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_shift_o[0] → macro_vim_o</t>
+          <t>mm_vim_o[0] → macro_vim_o</t>
         </is>
       </c>
       <c r="N30" s="9" t="inlineStr">
@@ -7043,7 +7043,7 @@
       <c r="I31" s="9" t="inlineStr"/>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_shift_y[0] → td_vim_y[1] → macro_vim_yy</t>
+          <t>mm_vim_y[0] → td_vim_y[1] → macro_vim_yy</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -7087,7 +7087,7 @@
       <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_shift_y[1] → macro_vim_shift_y</t>
+          <t>mm_vim_y[1] → macro_vim_shift_y</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -7098,7 +7098,7 @@
       <c r="L32" s="9" t="inlineStr"/>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_shift_o[1] → macro_vim_shift_o</t>
+          <t>mm_vim_o[1] → macro_vim_shift_o</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
@@ -7136,7 +7136,7 @@
       <c r="J33" s="9" t="inlineStr"/>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_ctrl_u[1] → &amp;kp PAGE_UP</t>
+          <t>mm_vim_u[1] → &amp;kp PAGE_UP</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr"/>
@@ -7172,7 +7172,7 @@
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>D
-&amp;mm_vim_ctrl_then_shift_d</t>
+&amp;mm_vim_d</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -7235,7 +7235,7 @@
       <c r="C35" s="9" t="inlineStr"/>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_ctrl_then_shift_d[0] → mm_vim_shift_d[0] → td_vim_d[0] → &amp;none</t>
+          <t>mm_vim_d[0] → mm_vim_shift_d[0] → td_vim_d[0] → &amp;none</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr"/>
@@ -7287,7 +7287,7 @@
       <c r="C36" s="9" t="inlineStr"/>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_ctrl_then_shift_d[0] → mm_vim_shift_d[0] → td_vim_d[1] → macro_vim_dd</t>
+          <t>mm_vim_d[0] → mm_vim_shift_d[0] → td_vim_d[1] → macro_vim_dd</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr"/>
@@ -7339,7 +7339,7 @@
       <c r="C37" s="9" t="inlineStr"/>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_ctrl_then_shift_d[0] → mm_vim_shift_d[1] → macro_vim_shift_d</t>
+          <t>mm_vim_d[0] → mm_vim_shift_d[1] → macro_vim_shift_d</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr"/>
@@ -7391,7 +7391,7 @@
       <c r="C38" s="9" t="inlineStr"/>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_ctrl_then_shift_d[1] → &amp;kp PAGE_DOWN</t>
+          <t>mm_vim_d[1] → &amp;kp PAGE_DOWN</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -2087,7 +2087,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -2118,7 +2118,8 @@
       <c r="L30" s="9" t="inlineStr"/>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>END ▸ ENTER</t>
+          <t>END
+▸ ENTER</t>
         </is>
       </c>
       <c r="N30" s="9" t="inlineStr">
@@ -2127,7 +2128,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>ダブルタップ</t>
@@ -2151,7 +2152,9 @@
       <c r="I31" s="9" t="inlineStr"/>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>HOME ▸ Shift+END ▸ Ctrl+C</t>
+          <t>HOME
+▸ Shift+END
+▸ Ctrl+C</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -2171,7 +2174,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -2195,7 +2198,8 @@
       <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>Shift+END ▸ Ctrl+C</t>
+          <t>Shift+END
+▸ Ctrl+C</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -2206,7 +2210,9 @@
       <c r="L32" s="9" t="inlineStr"/>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>HOME ▸ ENTER ▸ ↑</t>
+          <t>HOME
+▸ ENTER
+▸ ↑</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
@@ -2373,7 +2379,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ダブルタップ</t>
@@ -2387,7 +2393,9 @@
       <c r="C36" s="9" t="inlineStr"/>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>HOME ▸ Shift+END ▸ Ctrl+X</t>
+          <t>HOME
+▸ Shift+END
+▸ Ctrl+X</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr"/>
@@ -2425,7 +2433,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -2439,7 +2447,8 @@
       <c r="C37" s="9" t="inlineStr"/>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Shift+END ▸ Ctrl+X</t>
+          <t>Shift+END
+▸ Ctrl+X</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr"/>
@@ -2458,7 +2467,9 @@
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>END ▸ DEL ▸ SPACE</t>
+          <t>END
+▸ DEL
+▸ SPACE</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -2639,7 +2650,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -2658,7 +2669,9 @@
       <c r="D41" s="9" t="inlineStr"/>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>HOME ▸ Shift+↓ ▸ レイヤー VIM_VISUAL へ</t>
+          <t>HOME
+▸ Shift+↓
+▸ レイヤー VIM_VISUAL へ</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
@@ -4935,7 +4948,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="75" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -4959,7 +4972,11 @@
       <c r="I93" s="9" t="inlineStr"/>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>LShift ▸ RShift ▸ Ctrl+C ▸ → ▸ レイヤー DEFAULT へ</t>
+          <t>LShift
+▸ RShift
+▸ Ctrl+C
+▸ →
+▸ レイヤー DEFAULT へ</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr"/>
@@ -4967,7 +4984,10 @@
       <c r="M93" s="9" t="inlineStr"/>
       <c r="N93" s="9" t="inlineStr">
         <is>
-          <t>LShift ▸ RShift ▸ Ctrl+V ▸ レイヤー DEFAULT へ</t>
+          <t>LShift
+▸ RShift
+▸ Ctrl+V
+▸ レイヤー DEFAULT へ</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5061,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="60" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -5055,7 +5075,10 @@
       <c r="C95" s="9" t="inlineStr"/>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>LShift ▸ RShift ▸ Ctrl+X ▸ レイヤー DEFAULT へ</t>
+          <t>LShift
+▸ RShift
+▸ Ctrl+X
+▸ レイヤー DEFAULT へ</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr"/>
@@ -5263,7 +5286,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="60" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -5276,13 +5299,19 @@
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>LShift ▸ RShift ▸ Ctrl+X ▸ レイヤー DEFAULT へ</t>
+          <t>LShift
+▸ RShift
+▸ Ctrl+X
+▸ レイヤー DEFAULT へ</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr"/>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>LShift ▸ RShift ▸ → ▸ レイヤー DEFAULT へ</t>
+          <t>LShift
+▸ RShift
+▸ →
+▸ レイヤー DEFAULT へ</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
@@ -6971,7 +7000,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -6980,7 +7009,8 @@
       <c r="B30" s="9" t="inlineStr"/>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_w[0] → &amp;kp LC(RIGHT)</t>
+          <t>mm_vim_w[0]
+▸ &amp;kp LC(RIGHT)</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -6990,7 +7020,8 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_ctrl_r[0] → &amp;none</t>
+          <t>mm_vim_ctrl_r[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr"/>
@@ -6999,18 +7030,22 @@
       <c r="I30" s="9" t="inlineStr"/>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_y[0] → td_vim_y[0] → &amp;none</t>
+          <t>mm_vim_y[0]
+▸ td_vim_y[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_u[0] → &amp;kp LC(Z)</t>
+          <t>mm_vim_u[0]
+▸ &amp;kp LC(Z)</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr"/>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_o[0] → macro_vim_o</t>
+          <t>mm_vim_o[0]
+▸ macro_vim_o</t>
         </is>
       </c>
       <c r="N30" s="9" t="inlineStr">
@@ -7019,7 +7054,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>ダブルタップ</t>
@@ -7043,7 +7078,9 @@
       <c r="I31" s="9" t="inlineStr"/>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_y[0] → td_vim_y[1] → macro_vim_yy</t>
+          <t>mm_vim_y[0]
+▸ td_vim_y[1]
+▸ macro_vim_yy</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -7063,7 +7100,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -7087,7 +7124,8 @@
       <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_y[1] → macro_vim_shift_y</t>
+          <t>mm_vim_y[1]
+▸ macro_vim_shift_y</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -7098,7 +7136,8 @@
       <c r="L32" s="9" t="inlineStr"/>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_o[1] → macro_vim_shift_o</t>
+          <t>mm_vim_o[1]
+▸ macro_vim_shift_o</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
@@ -7107,7 +7146,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Ctrl+</t>
@@ -7116,7 +7155,8 @@
       <c r="B33" s="9" t="inlineStr"/>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_w[1] → &amp;kp LC(BACKSPACE)</t>
+          <t>mm_vim_w[1]
+▸ &amp;kp LC(BACKSPACE)</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -7126,7 +7166,8 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_ctrl_r[1] → &amp;kp LC(Y)</t>
+          <t>mm_vim_ctrl_r[1]
+▸ &amp;kp LC(Y)</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr"/>
@@ -7136,7 +7177,8 @@
       <c r="J33" s="9" t="inlineStr"/>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_u[1] → &amp;kp PAGE_UP</t>
+          <t>mm_vim_u[1]
+▸ &amp;kp PAGE_UP</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr"/>
@@ -7221,7 +7263,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -7235,13 +7277,18 @@
       <c r="C35" s="9" t="inlineStr"/>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_d[0] → mm_vim_shift_d[0] → td_vim_d[0] → &amp;none</t>
+          <t>mm_vim_d[0]
+▸ mm_vim_shift_d[0]
+▸ td_vim_d[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr"/>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_g[0] → td_vim_g[0] → &amp;none</t>
+          <t>mm_vim_g[0]
+▸ td_vim_g[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr"/>
@@ -7254,7 +7301,8 @@
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_j[0] → &amp;kp DOWN</t>
+          <t>mm_vim_j[0]
+▸ &amp;kp DOWN</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
@@ -7273,7 +7321,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ダブルタップ</t>
@@ -7287,13 +7335,18 @@
       <c r="C36" s="9" t="inlineStr"/>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_d[0] → mm_vim_shift_d[0] → td_vim_d[1] → macro_vim_dd</t>
+          <t>mm_vim_d[0]
+▸ mm_vim_shift_d[0]
+▸ td_vim_d[1]
+▸ macro_vim_dd</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr"/>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_g[0] → td_vim_g[1] → &amp;kp LC(HOME)</t>
+          <t>mm_vim_g[0]
+▸ td_vim_g[1]
+▸ &amp;kp LC(HOME)</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
@@ -7325,7 +7378,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -7339,13 +7392,16 @@
       <c r="C37" s="9" t="inlineStr"/>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_d[0] → mm_vim_shift_d[1] → macro_vim_shift_d</t>
+          <t>mm_vim_d[0]
+▸ mm_vim_shift_d[1]
+▸ macro_vim_shift_d</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr"/>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_g[1] → &amp;kp LC(END)</t>
+          <t>mm_vim_g[1]
+▸ &amp;kp LC(END)</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
@@ -7358,7 +7414,8 @@
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_j[1] → macro_vim_join</t>
+          <t>mm_vim_j[1]
+▸ macro_vim_join</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -7377,7 +7434,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Ctrl+</t>
@@ -7391,7 +7448,8 @@
       <c r="C38" s="9" t="inlineStr"/>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_d[1] → &amp;kp PAGE_DOWN</t>
+          <t>mm_vim_d[1]
+▸ &amp;kp PAGE_DOWN</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr"/>
@@ -7495,7 +7553,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -7514,7 +7572,8 @@
       <c r="D40" s="9" t="inlineStr"/>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_v[0] → &amp;to VIM_VISUAL</t>
+          <t>mm_vim_v[0]
+▸ &amp;to VIM_VISUAL</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -7527,7 +7586,8 @@
       <c r="I40" s="9" t="inlineStr"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_n[0] → &amp;kp F3</t>
+          <t>mm_vim_n[0]
+▸ &amp;kp F3</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr"/>
@@ -7539,7 +7599,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -7558,7 +7618,8 @@
       <c r="D41" s="9" t="inlineStr"/>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_v[1] → macro_vim_v_line</t>
+          <t>mm_vim_v[1]
+▸ macro_vim_v_line</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
@@ -7571,7 +7632,8 @@
       <c r="I41" s="9" t="inlineStr"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_n[1] → &amp;kp LS(F3)</t>
+          <t>mm_vim_n[1]
+▸ &amp;kp LS(F3)</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr"/>
@@ -7823,7 +7885,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -7834,7 +7896,8 @@
       <c r="D47" s="9" t="inlineStr"/>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_shift_4[0] → &amp;none</t>
+          <t>mm_vim_shift_4[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr"/>
@@ -7843,7 +7906,8 @@
       <c r="I47" s="9" t="inlineStr"/>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_shift_6[0] → &amp;none</t>
+          <t>mm_vim_shift_6[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr"/>
@@ -7855,7 +7919,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -7866,7 +7930,8 @@
       <c r="D48" s="9" t="inlineStr"/>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_shift_4[1] → &amp;kp END</t>
+          <t>mm_vim_shift_4[1]
+▸ &amp;kp END</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr"/>
@@ -7875,7 +7940,8 @@
       <c r="I48" s="9" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_shift_6[1] → &amp;kp HOME</t>
+          <t>mm_vim_shift_6[1]
+▸ &amp;kp HOME</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr"/>
@@ -10017,7 +10083,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="45" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -10037,7 +10103,9 @@
       <c r="E95" s="9" t="inlineStr"/>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_visual_g[0] → td_vim_visual_g[0] → &amp;none</t>
+          <t>mm_vim_visual_g[0]
+▸ td_vim_visual_g[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr"/>
@@ -10069,7 +10137,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="45" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
           <t>ダブルタップ</t>
@@ -10089,7 +10157,9 @@
       <c r="E96" s="9" t="inlineStr"/>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_visual_g[0] → td_vim_visual_g[1] → &amp;kp LS(LC(HOME))</t>
+          <t>mm_vim_visual_g[0]
+▸ td_vim_visual_g[1]
+▸ &amp;kp LS(LC(HOME))</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr"/>
@@ -10121,7 +10191,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="30" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -10141,7 +10211,8 @@
       <c r="E97" s="9" t="inlineStr"/>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_visual_g[1] → &amp;kp LS(LC(END))</t>
+          <t>mm_vim_visual_g[1]
+▸ &amp;kp LS(LC(END))</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -539,19 +539,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5452,19 +5452,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -2096,12 +2096,12 @@
       <c r="B30" s="9" t="inlineStr"/>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+→</t>
+          <t>⌃→</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+→</t>
+          <t>⌃→</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
       <c r="J30" s="9" t="inlineStr"/>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+Z</t>
+          <t>⌃Z</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+V</t>
+          <t>⌃V</t>
         </is>
       </c>
     </row>
@@ -2153,8 +2153,8 @@
       <c r="J31" s="9" t="inlineStr">
         <is>
           <t>HOME
-▸ Shift+END
-▸ Ctrl+C</t>
+▸ ⇧END
+▸ ⌃C</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -2198,8 +2198,8 @@
       <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>Shift+END
-▸ Ctrl+C</t>
+          <t>⇧END
+▸ ⌃C</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -2230,7 +2230,7 @@
       <c r="B33" s="9" t="inlineStr"/>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+BS</t>
+          <t>⌃BS</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+Y</t>
+          <t>⌃Y</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr"/>
@@ -2394,14 +2394,14 @@
       <c r="D36" s="9" t="inlineStr">
         <is>
           <t>HOME
-▸ Shift+END
-▸ Ctrl+X</t>
+▸ ⇧END
+▸ ⌃X</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr"/>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+HOME</t>
+          <t>⌃HOME</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
@@ -2447,14 +2447,14 @@
       <c r="C37" s="9" t="inlineStr"/>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Shift+END
-▸ Ctrl+X</t>
+          <t>⇧END
+▸ ⌃X</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr"/>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+END</t>
+          <t>⌃END</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+←</t>
+          <t>⌃←</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr"/>
@@ -2670,7 +2670,7 @@
       <c r="E41" s="9" t="inlineStr">
         <is>
           <t>HOME
-▸ Shift+↓
+▸ ⇧↓
 ▸ レイヤー VIM_VISUAL へ</t>
         </is>
       </c>
@@ -2684,7 +2684,7 @@
       <c r="I41" s="9" t="inlineStr"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Shift+F3</t>
+          <t>〃</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr"/>
@@ -4957,12 +4957,12 @@
       <c r="B93" s="9" t="inlineStr"/>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Shift+Ctrl+→</t>
+          <t>⇧⌃→</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Shift+Ctrl+→</t>
+          <t>⇧⌃→</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr"/>
@@ -4974,7 +4974,7 @@
         <is>
           <t>LShift
 ▸ RShift
-▸ Ctrl+C
+▸ ⌃C
 ▸ →
 ▸ レイヤー DEFAULT へ</t>
         </is>
@@ -4986,7 +4986,7 @@
         <is>
           <t>LShift
 ▸ RShift
-▸ Ctrl+V
+▸ ⌃V
 ▸ レイヤー DEFAULT へ</t>
         </is>
       </c>
@@ -5077,7 +5077,7 @@
         <is>
           <t>LShift
 ▸ RShift
-▸ Ctrl+X
+▸ ⌃X
 ▸ レイヤー DEFAULT へ</t>
         </is>
       </c>
@@ -5088,22 +5088,22 @@
       <c r="I95" s="9" t="inlineStr"/>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>Shift+←</t>
+          <t>⇧←</t>
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr">
         <is>
-          <t>Shift+↓</t>
+          <t>⇧↓</t>
         </is>
       </c>
       <c r="L95" s="9" t="inlineStr">
         <is>
-          <t>Shift+↑</t>
+          <t>⇧↑</t>
         </is>
       </c>
       <c r="M95" s="9" t="inlineStr">
         <is>
-          <t>Shift+→</t>
+          <t>⇧→</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -5132,7 +5132,7 @@
       <c r="E96" s="9" t="inlineStr"/>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>Shift+Ctrl+HOME</t>
+          <t>⇧⌃HOME</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr"/>
@@ -5184,7 +5184,7 @@
       <c r="E97" s="9" t="inlineStr"/>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>Shift+Ctrl+END</t>
+          <t>⇧⌃END</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr"/>
@@ -5301,7 +5301,7 @@
         <is>
           <t>LShift
 ▸ RShift
-▸ Ctrl+X
+▸ ⌃X
 ▸ レイヤー DEFAULT へ</t>
         </is>
       </c>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>Shift+Ctrl+←</t>
+          <t>⇧⌃←</t>
         </is>
       </c>
       <c r="G99" s="9" t="inlineStr"/>
@@ -7632,8 +7632,7 @@
       <c r="I41" s="9" t="inlineStr"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_n[1]
-▸ &amp;kp LS(F3)</t>
+          <t>〃</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,6 +169,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2116,7 +2119,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>END
 ▸ ENTER</t>
@@ -2150,7 +2153,7 @@
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr"/>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ⇧END
@@ -2196,7 +2199,7 @@
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr"/>
       <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>⇧END
 ▸ ⌃C</t>
@@ -2208,7 +2211,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ENTER
@@ -2391,7 +2394,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ⇧END
@@ -2445,7 +2448,7 @@
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr"/>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>⇧END
 ▸ ⌃X</t>
@@ -2465,7 +2468,7 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>END
 ▸ DEL
@@ -2667,7 +2670,7 @@
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ⇧↓
@@ -4970,7 +4973,7 @@
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
       <c r="I93" s="9" t="inlineStr"/>
-      <c r="J93" s="9" t="inlineStr">
+      <c r="J93" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -4982,7 +4985,7 @@
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
       <c r="M93" s="9" t="inlineStr"/>
-      <c r="N93" s="9" t="inlineStr">
+      <c r="N93" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -5073,7 +5076,7 @@
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr"/>
-      <c r="D95" s="9" t="inlineStr">
+      <c r="D95" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -5297,7 +5300,7 @@
           <t>LShift</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -5306,7 +5309,7 @@
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr"/>
-      <c r="E99" s="9" t="inlineStr">
+      <c r="E99" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -7007,7 +7010,7 @@
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr"/>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_w[0]
 ▸ &amp;kp LC(RIGHT)</t>
@@ -7018,7 +7021,7 @@
           <t>&amp;kp LC(RIGHT)</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_ctrl_r[0]
 ▸ &amp;none</t>
@@ -7028,21 +7031,21 @@
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr"/>
       <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[0]
 ▸ td_vim_y[0]
 ▸ &amp;none</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_u[0]
 ▸ &amp;kp LC(Z)</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_o[0]
 ▸ macro_vim_o</t>
@@ -7076,7 +7079,7 @@
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr"/>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[0]
 ▸ td_vim_y[1]
@@ -7122,7 +7125,7 @@
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr"/>
       <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[1]
 ▸ macro_vim_shift_y</t>
@@ -7134,7 +7137,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>mm_vim_o[1]
 ▸ macro_vim_shift_o</t>
@@ -7153,7 +7156,7 @@
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr"/>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>mm_vim_w[1]
 ▸ &amp;kp LC(BACKSPACE)</t>
@@ -7164,7 +7167,7 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>mm_vim_ctrl_r[1]
 ▸ &amp;kp LC(Y)</t>
@@ -7175,7 +7178,7 @@
       <c r="H33" s="9" t="inlineStr"/>
       <c r="I33" s="9" t="inlineStr"/>
       <c r="J33" s="9" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>mm_vim_u[1]
 ▸ &amp;kp PAGE_UP</t>
@@ -7275,7 +7278,7 @@
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr"/>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>mm_vim_d[0]
 ▸ mm_vim_shift_d[0]
@@ -7284,7 +7287,7 @@
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>mm_vim_g[0]
 ▸ td_vim_g[0]
@@ -7299,7 +7302,7 @@
           <t>&amp;kp LEFT</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>mm_vim_j[0]
 ▸ &amp;kp DOWN</t>
@@ -7333,7 +7336,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>mm_vim_d[0]
 ▸ mm_vim_shift_d[0]
@@ -7342,7 +7345,7 @@
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>mm_vim_g[0]
 ▸ td_vim_g[1]
@@ -7390,7 +7393,7 @@
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr"/>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>mm_vim_d[0]
 ▸ mm_vim_shift_d[1]
@@ -7398,7 +7401,7 @@
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr"/>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>mm_vim_g[1]
 ▸ &amp;kp LC(END)</t>
@@ -7412,7 +7415,7 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>mm_vim_j[1]
 ▸ macro_vim_join</t>
@@ -7446,7 +7449,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr"/>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>mm_vim_d[1]
 ▸ &amp;kp PAGE_DOWN</t>
@@ -7570,7 +7573,7 @@
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr"/>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>mm_vim_v[0]
 ▸ &amp;to VIM_VISUAL</t>
@@ -7584,7 +7587,7 @@
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="9" t="inlineStr"/>
       <c r="I40" s="9" t="inlineStr"/>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>mm_vim_n[0]
 ▸ &amp;kp F3</t>
@@ -7616,7 +7619,7 @@
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>mm_vim_v[1]
 ▸ macro_vim_v_line</t>
@@ -7893,7 +7896,7 @@
       <c r="B47" s="9" t="inlineStr"/>
       <c r="C47" s="9" t="inlineStr"/>
       <c r="D47" s="9" t="inlineStr"/>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_4[0]
 ▸ &amp;none</t>
@@ -7903,7 +7906,7 @@
       <c r="G47" s="9" t="inlineStr"/>
       <c r="H47" s="9" t="inlineStr"/>
       <c r="I47" s="9" t="inlineStr"/>
-      <c r="J47" s="9" t="inlineStr">
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_6[0]
 ▸ &amp;none</t>
@@ -7927,7 +7930,7 @@
       <c r="B48" s="9" t="inlineStr"/>
       <c r="C48" s="9" t="inlineStr"/>
       <c r="D48" s="9" t="inlineStr"/>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_4[1]
 ▸ &amp;kp END</t>
@@ -7937,7 +7940,7 @@
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="9" t="inlineStr"/>
       <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="9" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_6[1]
 ▸ &amp;kp HOME</t>
@@ -10100,7 +10103,7 @@
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>mm_vim_visual_g[0]
 ▸ td_vim_visual_g[0]
@@ -10154,7 +10157,7 @@
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr"/>
-      <c r="F96" s="9" t="inlineStr">
+      <c r="F96" s="10" t="inlineStr">
         <is>
           <t>mm_vim_visual_g[0]
 ▸ td_vim_visual_g[1]
@@ -10208,7 +10211,7 @@
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr"/>
-      <c r="F97" s="9" t="inlineStr">
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>mm_vim_visual_g[1]
 ▸ &amp;kp LS(LC(END))</t>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -545,12 +545,12 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -2628,7 +2628,7 @@
       <c r="D40" s="9" t="inlineStr"/>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>⇒L8</t>
+          <t>⇒VIM_VISUAL</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -2674,7 +2674,7 @@
         <is>
           <t>HOME
 ▸ ⇧↓
-▸ レイヤー VIM_VISUAL へ</t>
+▸ ⇒VIM_VISUAL</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
@@ -4979,7 +4979,7 @@
 ▸ RShift
 ▸ ⌃C
 ▸ →
-▸ レイヤー DEFAULT へ</t>
+▸ ⇒DEFAULT</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
           <t>LShift
 ▸ RShift
 ▸ ⌃V
-▸ レイヤー DEFAULT へ</t>
+▸ ⇒DEFAULT</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
           <t>LShift
 ▸ RShift
 ▸ ⌃X
-▸ レイヤー DEFAULT へ</t>
+▸ ⇒DEFAULT</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr"/>
@@ -5305,7 +5305,7 @@
           <t>LShift
 ▸ RShift
 ▸ ⌃X
-▸ レイヤー DEFAULT へ</t>
+▸ ⇒DEFAULT</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr"/>
@@ -5314,7 +5314,7 @@
           <t>LShift
 ▸ RShift
 ▸ →
-▸ レイヤー DEFAULT へ</t>
+▸ ⇒DEFAULT</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -546,11 +546,11 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -1008,9 +1008,19 @@
 &amp;kp B</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>N
@@ -1073,9 +1083,17 @@
           <t>B</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
       <c r="H11" s="9" t="inlineStr"/>
-      <c r="I11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
           <t>N</t>
@@ -1133,9 +1151,17 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1171,7 +1197,7 @@
       <c r="B13" s="7" t="inlineStr">
         <is>
           <t>mo6 (L outer)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1189,32 +1215,32 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 2 SPACE</t>
+&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 2 SPACE</t>
+&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo 1</t>
+&amp;mo SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo 2</t>
+&amp;mo VIM_NORMAL_1</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt 1 ENTER</t>
+&amp;lt SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr"/>
@@ -1222,13 +1248,13 @@
       <c r="M13" s="7" t="inlineStr">
         <is>
           <t>mo6 (R)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
           <t>mo6 (R outer)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
     </row>
@@ -1728,9 +1754,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>N
@@ -1869,13 +1905,13 @@
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 3 SPACE</t>
+&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 3 SPACE</t>
+&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1888,7 +1924,7 @@
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo 3</t>
+&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -2575,9 +2611,19 @@
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
           <t>N
@@ -2738,7 +2784,7 @@
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo 3</t>
+&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
@@ -2751,7 +2797,7 @@
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt 3 ENTER</t>
+&amp;lt VIM_NORMAL_2 ENTER</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -3133,9 +3179,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
           <t>N
@@ -3461,7 +3517,7 @@
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>K
-&amp;mo 5</t>
+&amp;mo SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -3537,9 +3593,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
           <t>N
@@ -3917,9 +3983,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
           <t>N
@@ -4337,9 +4413,19 @@
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
           <t>N
@@ -4717,9 +4803,19 @@
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
           <t>N
@@ -5255,9 +5351,19 @@
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
           <t>N
@@ -5921,9 +6027,19 @@
 &amp;kp B</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>N
@@ -5986,9 +6102,17 @@
           <t>&amp;kp B</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="H11" s="9" t="inlineStr"/>
-      <c r="I11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N</t>
@@ -6046,9 +6170,17 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6084,7 +6216,7 @@
       <c r="B13" s="7" t="inlineStr">
         <is>
           <t>mo6 (L outer)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -6102,32 +6234,32 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 2 SPACE</t>
+&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 2 SPACE</t>
+&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo 1</t>
+&amp;mo SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo 2</t>
+&amp;mo VIM_NORMAL_1</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt 1 ENTER</t>
+&amp;lt SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr"/>
@@ -6135,13 +6267,13 @@
       <c r="M13" s="7" t="inlineStr">
         <is>
           <t>mo6 (R)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
           <t>mo6 (R outer)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
     </row>
@@ -6641,9 +6773,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>N
@@ -6782,13 +6924,13 @@
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 3 SPACE</t>
+&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 3 SPACE</t>
+&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -6801,7 +6943,7 @@
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo 3</t>
+&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -7522,9 +7664,19 @@
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
           <t>N
@@ -7686,7 +7838,7 @@
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo 3</t>
+&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
@@ -7699,7 +7851,7 @@
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt 3 ENTER</t>
+&amp;lt VIM_NORMAL_2 ENTER</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -8093,9 +8245,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
           <t>N
@@ -8421,7 +8583,7 @@
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>K
-&amp;mo 5</t>
+&amp;mo SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -8497,9 +8659,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
           <t>N
@@ -8885,9 +9057,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
           <t>N
@@ -9321,9 +9503,19 @@
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
           <t>N
@@ -9737,9 +9929,19 @@
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
           <t>N
@@ -10282,9 +10484,19 @@
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
           <t>N

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,6 +169,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -539,19 +542,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1005,9 +1008,19 @@
 &amp;kp B</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>N
@@ -1070,9 +1083,17 @@
           <t>B</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
       <c r="H11" s="9" t="inlineStr"/>
-      <c r="I11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
           <t>N</t>
@@ -1130,9 +1151,17 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1168,7 +1197,7 @@
       <c r="B13" s="7" t="inlineStr">
         <is>
           <t>mo6 (L outer)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1186,32 +1215,32 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 2 SPACE</t>
+&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 2 SPACE</t>
+&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo 1</t>
+&amp;mo SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo 2</t>
+&amp;mo VIM_NORMAL_1</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt 1 ENTER</t>
+&amp;lt SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr"/>
@@ -1219,13 +1248,13 @@
       <c r="M13" s="7" t="inlineStr">
         <is>
           <t>mo6 (R)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
           <t>mo6 (R outer)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
     </row>
@@ -1725,9 +1754,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>N
@@ -1866,13 +1905,13 @@
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 3 SPACE</t>
+&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 3 SPACE</t>
+&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1885,7 +1924,7 @@
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo 3</t>
+&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -2087,7 +2126,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -2096,12 +2135,12 @@
       <c r="B30" s="9" t="inlineStr"/>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+→</t>
+          <t>⌃→</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+→</t>
+          <t>⌃→</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr"/>
@@ -2112,22 +2151,23 @@
       <c r="J30" s="9" t="inlineStr"/>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+Z</t>
+          <t>⌃Z</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>END ▸ ENTER</t>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>END
+▸ ENTER</t>
         </is>
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+V</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+          <t>⌃V</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>ダブルタップ</t>
@@ -2149,9 +2189,11 @@
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr"/>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>HOME ▸ Shift+END ▸ Ctrl+C</t>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>HOME
+▸ ⇧END
+▸ ⌃C</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -2171,7 +2213,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -2193,9 +2235,10 @@
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr"/>
       <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>Shift+END ▸ Ctrl+C</t>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>⇧END
+▸ ⌃C</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -2204,9 +2247,11 @@
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr">
-        <is>
-          <t>HOME ▸ ENTER ▸ ↑</t>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>HOME
+▸ ENTER
+▸ ↑</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
@@ -2224,7 +2269,7 @@
       <c r="B33" s="9" t="inlineStr"/>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+BS</t>
+          <t>⌃BS</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -2234,7 +2279,7 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+Y</t>
+          <t>⌃Y</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr"/>
@@ -2373,7 +2418,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ダブルタップ</t>
@@ -2385,15 +2430,17 @@
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>HOME ▸ Shift+END ▸ Ctrl+X</t>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>HOME
+▸ ⇧END
+▸ ⌃X</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr"/>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+HOME</t>
+          <t>⌃HOME</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
@@ -2425,7 +2472,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -2437,15 +2484,16 @@
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr"/>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Shift+END ▸ Ctrl+X</t>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>⇧END
+▸ ⌃X</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr"/>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+END</t>
+          <t>⌃END</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
@@ -2456,9 +2504,11 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
-        <is>
-          <t>END ▸ DEL ▸ SPACE</t>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>END
+▸ DEL
+▸ SPACE</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -2561,9 +2611,19 @@
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
           <t>N
@@ -2614,12 +2674,12 @@
       <c r="D40" s="9" t="inlineStr"/>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>⇒L8</t>
+          <t>⇒VIM_VISUAL</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>Ctrl+←</t>
+          <t>⌃←</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr"/>
@@ -2639,7 +2699,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -2656,9 +2716,11 @@
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>HOME ▸ Shift+↓ ▸ レイヤー 8 へ</t>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>HOME
+▸ ⇧↓
+▸ ⇒VIM_VISUAL</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
@@ -2671,7 +2733,7 @@
       <c r="I41" s="9" t="inlineStr"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Shift+F3</t>
+          <t>〃</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr"/>
@@ -2722,7 +2784,7 @@
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo 3</t>
+&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
@@ -2735,7 +2797,7 @@
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt 3 ENTER</t>
+&amp;lt VIM_NORMAL_2 ENTER</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -3117,9 +3179,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
           <t>N
@@ -3445,7 +3517,7 @@
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>K
-&amp;mo 5</t>
+&amp;mo SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -3521,9 +3593,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
           <t>N
@@ -3901,9 +3983,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
           <t>N
@@ -4321,9 +4413,19 @@
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
           <t>N
@@ -4701,9 +4803,19 @@
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
           <t>N
@@ -4935,7 +5047,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="75" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -4944,12 +5056,12 @@
       <c r="B93" s="9" t="inlineStr"/>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Shift+Ctrl+→</t>
+          <t>⇧⌃→</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Shift+Ctrl+→</t>
+          <t>⇧⌃→</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr"/>
@@ -4957,17 +5069,24 @@
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
       <c r="I93" s="9" t="inlineStr"/>
-      <c r="J93" s="9" t="inlineStr">
-        <is>
-          <t>LShift ▸ RShift ▸ Ctrl+C ▸ → ▸ レイヤー 0 へ</t>
+      <c r="J93" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃C
+▸ →
+▸ ⇒DEFAULT</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
       <c r="M93" s="9" t="inlineStr"/>
-      <c r="N93" s="9" t="inlineStr">
-        <is>
-          <t>LShift ▸ RShift ▸ Ctrl+V ▸ レイヤー 0 へ</t>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃V
+▸ ⇒DEFAULT</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5160,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="60" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -5053,9 +5172,12 @@
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr"/>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>LShift ▸ RShift ▸ Ctrl+X ▸ レイヤー 0 へ</t>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃X
+▸ ⇒DEFAULT</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr"/>
@@ -5065,22 +5187,22 @@
       <c r="I95" s="9" t="inlineStr"/>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>Shift+←</t>
+          <t>⇧←</t>
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr">
         <is>
-          <t>Shift+↓</t>
+          <t>⇧↓</t>
         </is>
       </c>
       <c r="L95" s="9" t="inlineStr">
         <is>
-          <t>Shift+↑</t>
+          <t>⇧↑</t>
         </is>
       </c>
       <c r="M95" s="9" t="inlineStr">
         <is>
-          <t>Shift+→</t>
+          <t>⇧→</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -5109,7 +5231,7 @@
       <c r="E96" s="9" t="inlineStr"/>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>Shift+Ctrl+HOME</t>
+          <t>⇧⌃HOME</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr"/>
@@ -5161,7 +5283,7 @@
       <c r="E97" s="9" t="inlineStr"/>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>Shift+Ctrl+END</t>
+          <t>⇧⌃END</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr"/>
@@ -5229,9 +5351,19 @@
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
           <t>N
@@ -5263,7 +5395,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="60" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -5274,20 +5406,26 @@
           <t>LShift</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>LShift ▸ RShift ▸ Ctrl+X ▸ レイヤー 0 へ</t>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃X
+▸ ⇒DEFAULT</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr"/>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>LShift ▸ RShift ▸ → ▸ レイヤー 0 へ</t>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ →
+▸ ⇒DEFAULT</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>Shift+Ctrl+←</t>
+          <t>⇧⌃←</t>
         </is>
       </c>
       <c r="G99" s="9" t="inlineStr"/>
@@ -5423,19 +5561,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5889,9 +6027,19 @@
 &amp;kp B</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>N
@@ -5954,9 +6102,17 @@
           <t>&amp;kp B</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="H11" s="9" t="inlineStr"/>
-      <c r="I11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N</t>
@@ -6014,9 +6170,17 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6052,7 +6216,7 @@
       <c r="B13" s="7" t="inlineStr">
         <is>
           <t>mo6 (L outer)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -6070,32 +6234,32 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 2 SPACE</t>
+&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 2 SPACE</t>
+&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo 1</t>
+&amp;mo SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo 2</t>
+&amp;mo VIM_NORMAL_1</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt 1 ENTER</t>
+&amp;lt SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr"/>
@@ -6103,13 +6267,13 @@
       <c r="M13" s="7" t="inlineStr">
         <is>
           <t>mo6 (R)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
           <t>mo6 (R outer)
-&amp;mo 6</t>
+&amp;mo FUNCTION</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6285,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo 6</t>
+          <t>&amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -6136,40 +6300,40 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo 1</t>
+          <t>&amp;mo SYMBOL</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo 2</t>
+          <t>&amp;mo VIM_NORMAL_1</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 1 ENTER</t>
+          <t>&amp;lt SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr"/>
       <c r="L14" s="9" t="inlineStr"/>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo 6</t>
+          <t>&amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo 6</t>
+          <t>&amp;mo FUNCTION</t>
         </is>
       </c>
     </row>
@@ -6196,12 +6360,12 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -6217,7 +6381,7 @@
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 1 ENTER</t>
+          <t>&amp;lt SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -6609,9 +6773,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>N
@@ -6750,13 +6924,13 @@
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 3 SPACE</t>
+&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt 3 SPACE</t>
+&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -6769,7 +6943,7 @@
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo 3</t>
+&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -6812,19 +6986,19 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 3 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 3 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo 3</t>
+          <t>&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr"/>
@@ -6856,12 +7030,12 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 3 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 3 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr"/>
@@ -6971,16 +7145,17 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr"/>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_w[0] → &amp;kp LC(RIGHT)</t>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_w[0]
+▸ &amp;kp LC(RIGHT)</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -6988,29 +7163,34 @@
           <t>&amp;kp LC(RIGHT)</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_ctrl_r[0] → &amp;none</t>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_ctrl_r[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr"/>
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr"/>
       <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_y[0] → td_vim_y[0] → &amp;none</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_u[0] → &amp;kp LC(Z)</t>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_y[0]
+▸ td_vim_y[0]
+▸ &amp;none</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_u[0]
+▸ &amp;kp LC(Z)</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_o[0] → macro_vim_o</t>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_o[0]
+▸ macro_vim_o</t>
         </is>
       </c>
       <c r="N30" s="9" t="inlineStr">
@@ -7019,7 +7199,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>ダブルタップ</t>
@@ -7041,9 +7221,11 @@
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr"/>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_y[0] → td_vim_y[1] → macro_vim_yy</t>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_y[0]
+▸ td_vim_y[1]
+▸ macro_vim_yy</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -7063,7 +7245,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -7085,9 +7267,10 @@
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr"/>
       <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_y[1] → macro_vim_shift_y</t>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_y[1]
+▸ macro_vim_shift_y</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -7096,9 +7279,10 @@
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_o[1] → macro_vim_shift_o</t>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_o[1]
+▸ macro_vim_shift_o</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
@@ -7107,16 +7291,17 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Ctrl+</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr"/>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_w[1] → &amp;kp LC(BACKSPACE)</t>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_w[1]
+▸ &amp;kp LC(BACKSPACE)</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -7124,9 +7309,10 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_ctrl_r[1] → &amp;kp LC(Y)</t>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_ctrl_r[1]
+▸ &amp;kp LC(Y)</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr"/>
@@ -7134,9 +7320,10 @@
       <c r="H33" s="9" t="inlineStr"/>
       <c r="I33" s="9" t="inlineStr"/>
       <c r="J33" s="9" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_u[1] → &amp;kp PAGE_UP</t>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_u[1]
+▸ &amp;kp PAGE_UP</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr"/>
@@ -7221,7 +7408,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -7233,15 +7420,20 @@
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr"/>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_d[0] → mm_vim_shift_d[0] → td_vim_d[0] → &amp;none</t>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_d[0]
+▸ mm_vim_shift_d[0]
+▸ td_vim_d[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_g[0] → td_vim_g[0] → &amp;none</t>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_g[0]
+▸ td_vim_g[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr"/>
@@ -7252,9 +7444,10 @@
           <t>&amp;kp LEFT</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_j[0] → &amp;kp DOWN</t>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_j[0]
+▸ &amp;kp DOWN</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
@@ -7273,7 +7466,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ダブルタップ</t>
@@ -7285,15 +7478,20 @@
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_d[0] → mm_vim_shift_d[0] → td_vim_d[1] → macro_vim_dd</t>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_d[0]
+▸ mm_vim_shift_d[0]
+▸ td_vim_d[1]
+▸ macro_vim_dd</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_g[0] → td_vim_g[1] → &amp;kp LC(HOME)</t>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_g[0]
+▸ td_vim_g[1]
+▸ &amp;kp LC(HOME)</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
@@ -7325,7 +7523,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -7337,15 +7535,18 @@
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr"/>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_d[0] → mm_vim_shift_d[1] → macro_vim_shift_d</t>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_d[0]
+▸ mm_vim_shift_d[1]
+▸ macro_vim_shift_d</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr"/>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_g[1] → &amp;kp LC(END)</t>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_g[1]
+▸ &amp;kp LC(END)</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
@@ -7356,9 +7557,10 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_j[1] → macro_vim_join</t>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_j[1]
+▸ macro_vim_join</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -7377,7 +7579,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Ctrl+</t>
@@ -7389,9 +7591,10 @@
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr"/>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_d[1] → &amp;kp PAGE_DOWN</t>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_d[1]
+▸ &amp;kp PAGE_DOWN</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr"/>
@@ -7461,9 +7664,19 @@
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
           <t>N
@@ -7495,7 +7708,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -7512,9 +7725,10 @@
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr"/>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_v[0] → &amp;to 8</t>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_v[0]
+▸ &amp;to VIM_VISUAL</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -7525,9 +7739,10 @@
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="9" t="inlineStr"/>
       <c r="I40" s="9" t="inlineStr"/>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_n[0] → &amp;kp F3</t>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_n[0]
+▸ &amp;kp F3</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr"/>
@@ -7539,7 +7754,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -7556,9 +7771,10 @@
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_v[1] → macro_vim_v_line</t>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_v[1]
+▸ macro_vim_v_line</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
@@ -7571,7 +7787,7 @@
       <c r="I41" s="9" t="inlineStr"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>mm_vim_n[1] → &amp;kp LS(F3)</t>
+          <t>〃</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr"/>
@@ -7622,7 +7838,7 @@
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo 3</t>
+&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
@@ -7635,7 +7851,7 @@
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt 3 ENTER</t>
+&amp;lt VIM_NORMAL_2 ENTER</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -7674,14 +7890,14 @@
       <c r="F43" s="9" t="inlineStr"/>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo 3</t>
+          <t>&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr"/>
       <c r="I43" s="9" t="inlineStr"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 3 ENTER</t>
+          <t>&amp;lt VIM_NORMAL_2 ENTER</t>
         </is>
       </c>
       <c r="K43" s="9" t="inlineStr"/>
@@ -7721,7 +7937,7 @@
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt 3 ENTER</t>
+          <t>&amp;lt VIM_NORMAL_2 ENTER</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr"/>
@@ -7823,7 +8039,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -7832,18 +8048,20 @@
       <c r="B47" s="9" t="inlineStr"/>
       <c r="C47" s="9" t="inlineStr"/>
       <c r="D47" s="9" t="inlineStr"/>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_shift_4[0] → &amp;none</t>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_shift_4[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr"/>
       <c r="G47" s="9" t="inlineStr"/>
       <c r="H47" s="9" t="inlineStr"/>
       <c r="I47" s="9" t="inlineStr"/>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_shift_6[0] → &amp;none</t>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_shift_6[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr"/>
@@ -7855,7 +8073,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -7864,18 +8082,20 @@
       <c r="B48" s="9" t="inlineStr"/>
       <c r="C48" s="9" t="inlineStr"/>
       <c r="D48" s="9" t="inlineStr"/>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_shift_4[1] → &amp;kp END</t>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_shift_4[1]
+▸ &amp;kp END</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr"/>
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="9" t="inlineStr"/>
       <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_shift_6[1] → &amp;kp HOME</t>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_shift_6[1]
+▸ &amp;kp HOME</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr"/>
@@ -8025,9 +8245,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
           <t>N
@@ -8353,7 +8583,7 @@
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>K
-&amp;mo 5</t>
+&amp;mo SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -8387,7 +8617,7 @@
       <c r="K59" s="9" t="inlineStr"/>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo 5</t>
+          <t>&amp;mo SCROLL</t>
         </is>
       </c>
       <c r="M59" s="9" t="inlineStr"/>
@@ -8429,9 +8659,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
           <t>N
@@ -8817,9 +9057,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
           <t>N
@@ -9253,9 +9503,19 @@
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
           <t>N
@@ -9669,9 +9929,19 @@
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
           <t>N
@@ -10017,7 +10287,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="45" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -10035,9 +10305,11 @@
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[0] → td_vim_visual_g[0] → &amp;none</t>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[0]
+▸ td_vim_visual_g[0]
+▸ &amp;none</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr"/>
@@ -10069,7 +10341,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="45" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
           <t>ダブルタップ</t>
@@ -10087,9 +10359,11 @@
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr"/>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[0] → td_vim_visual_g[1] → &amp;kp LS(LC(HOME))</t>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[0]
+▸ td_vim_visual_g[1]
+▸ &amp;kp LS(LC(HOME))</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr"/>
@@ -10121,7 +10395,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="30" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
           <t>Shift+</t>
@@ -10139,9 +10413,10 @@
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr"/>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[1] → &amp;kp LS(LC(END))</t>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[1]
+▸ &amp;kp LS(LC(END))</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr"/>
@@ -10209,9 +10484,19 @@
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>mo中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>mo上段
+&amp;none</t>
+        </is>
+      </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
           <t>N

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -545,12 +545,12 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -635,7 +635,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DEFAULT レイヤー</t>
+          <t>BASE_QWERTY レイヤー</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1215,32 +1215,32 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_1 SPACE</t>
+&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_1 SPACE</t>
+&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo SYMBOL</t>
+&amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo VIM_NORMAL_1</t>
+&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt SYMBOL ENTER</t>
+&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>SYMBOL レイヤー</t>
+          <t>NUM_SYMBOL レイヤー</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1905,13 +1905,13 @@
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_2 SPACE</t>
+&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_2 SPACE</t>
+&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1924,7 +1924,7 @@
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo VIM_NORMAL_2</t>
+&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>VIM_NORMAL_1 レイヤー</t>
+          <t>VIM_NORMAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -2674,7 +2674,7 @@
       <c r="D40" s="9" t="inlineStr"/>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>⇒VIM_VISUAL</t>
+          <t>⇒VIM_VISUAL_BASE</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -2720,7 +2720,7 @@
         <is>
           <t>HOME
 ▸ ⇧↓
-▸ ⇒VIM_VISUAL</t>
+▸ ⇒VIM_VISUAL_BASE</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
@@ -2784,7 +2784,7 @@
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo VIM_NORMAL_2</t>
+&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
@@ -2797,7 +2797,7 @@
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt VIM_NORMAL_2 ENTER</t>
+&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -2898,7 +2898,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VIM_NORMAL_2 レイヤー</t>
+          <t>VIM_NORMAL_SYM レイヤー</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -3356,7 +3356,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MOUSE レイヤー</t>
+          <t>MOUSE_MOVE レイヤー</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -3517,7 +3517,7 @@
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>K
-&amp;mo SCROLL</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>SCROLL レイヤー</t>
+          <t>MOUSE_SCROLL レイヤー</t>
         </is>
       </c>
       <c r="B64" s="4" t="n"/>
@@ -4960,7 +4960,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>VIM_VISUAL レイヤー</t>
+          <t>VIM_VISUAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B91" s="4" t="n"/>
@@ -5075,7 +5075,7 @@
 ▸ RShift
 ▸ ⌃C
 ▸ →
-▸ ⇒DEFAULT</t>
+▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr"/>
@@ -5086,7 +5086,7 @@
           <t>LShift
 ▸ RShift
 ▸ ⌃V
-▸ ⇒DEFAULT</t>
+▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5177,7 @@
           <t>LShift
 ▸ RShift
 ▸ ⌃X
-▸ ⇒DEFAULT</t>
+▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr"/>
@@ -5411,7 +5411,7 @@
           <t>LShift
 ▸ RShift
 ▸ ⌃X
-▸ ⇒DEFAULT</t>
+▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr"/>
@@ -5420,7 +5420,7 @@
           <t>LShift
 ▸ RShift
 ▸ →
-▸ ⇒DEFAULT</t>
+▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
@@ -5564,12 +5564,12 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
@@ -5654,7 +5654,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DEFAULT レイヤー</t>
+          <t>BASE_QWERTY レイヤー</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -6234,32 +6234,32 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_1 SPACE</t>
+&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_1 SPACE</t>
+&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo SYMBOL</t>
+&amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo VIM_NORMAL_1</t>
+&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt SYMBOL ENTER</t>
+&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr"/>
@@ -6300,28 +6300,28 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo SYMBOL</t>
+          <t>&amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo VIM_NORMAL_1</t>
+          <t>&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt SYMBOL ENTER</t>
+          <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr"/>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt SYMBOL ENTER</t>
+          <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -6400,7 +6400,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>SYMBOL レイヤー</t>
+          <t>NUM_SYMBOL レイヤー</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -6924,13 +6924,13 @@
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_2 SPACE</t>
+&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_2 SPACE</t>
+&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -6943,7 +6943,7 @@
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>mo2
-&amp;mo VIM_NORMAL_2</t>
+&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -6986,19 +6986,19 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo VIM_NORMAL_2</t>
+          <t>&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr"/>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr"/>
@@ -7058,7 +7058,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>VIM_NORMAL_1 レイヤー</t>
+          <t>VIM_NORMAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -7728,7 +7728,7 @@
       <c r="E40" s="10" t="inlineStr">
         <is>
           <t>mm_vim_v[0]
-▸ &amp;to VIM_VISUAL</t>
+▸ &amp;to VIM_VISUAL_BASE</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -7838,7 +7838,7 @@
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo VIM_NORMAL_2</t>
+&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
@@ -7851,7 +7851,7 @@
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt VIM_NORMAL_2 ENTER</t>
+&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -7890,14 +7890,14 @@
       <c r="F43" s="9" t="inlineStr"/>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo VIM_NORMAL_2</t>
+          <t>&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr"/>
       <c r="I43" s="9" t="inlineStr"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 ENTER</t>
+          <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
       <c r="K43" s="9" t="inlineStr"/>
@@ -7937,7 +7937,7 @@
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 ENTER</t>
+          <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr"/>
@@ -7952,7 +7952,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VIM_NORMAL_2 レイヤー</t>
+          <t>VIM_NORMAL_SYM レイヤー</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -8422,7 +8422,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MOUSE レイヤー</t>
+          <t>MOUSE_MOVE レイヤー</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -8583,7 +8583,7 @@
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>K
-&amp;mo SCROLL</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -8617,7 +8617,7 @@
       <c r="K59" s="9" t="inlineStr"/>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo SCROLL</t>
+          <t>&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="M59" s="9" t="inlineStr"/>
@@ -8816,7 +8816,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>SCROLL レイヤー</t>
+          <t>MOUSE_SCROLL レイヤー</t>
         </is>
       </c>
       <c r="B64" s="4" t="n"/>
@@ -10094,7 +10094,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>VIM_VISUAL レイヤー</t>
+          <t>VIM_VISUAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B91" s="4" t="n"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -660,31 +660,31 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp Q</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp W</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp E</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp R</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp T</t>
         </is>
       </c>
@@ -693,31 +693,31 @@
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp Y</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp U</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp I</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp O</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp P</t>
         </is>
       </c>
@@ -790,31 +790,31 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LEFT_CONTROL A</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp S</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp D</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp F</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp G</t>
         </is>
       </c>
@@ -823,31 +823,31 @@
       <c r="I7" s="7" t="inlineStr"/>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;kp H</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;kp J</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;kp K</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;kp L</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;mt RCTRL MINUS</t>
         </is>
       </c>
@@ -980,74 +980,74 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;mt LEFT_SHIFT Z</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;kp X</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;kp C</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;kp V</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp B</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;kp N</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;kp M</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;kp COMMA</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;kp PERIOD</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;mt RIGHT_SHIFT SLASH</t>
         </is>
       </c>
@@ -1196,50 +1196,50 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
@@ -1247,13 +1247,13 @@
       <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;mo FUNCTION</t>
         </is>
       </c>
@@ -1406,31 +1406,31 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp N1</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp N2</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp N3</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp N4</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp N5</t>
         </is>
       </c>
@@ -1439,31 +1439,31 @@
       <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp N6</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp N7</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp N8</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp N9</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp N0</t>
         </is>
       </c>
@@ -1536,31 +1536,31 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LCTRL TAB</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp GRAVE</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp LEFT_BRACKET</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp RIGHT_BRACKET</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp DELETE</t>
         </is>
       </c>
@@ -1569,31 +1569,31 @@
       <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;kp BACKSPACE</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;kp SEMICOLON</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;kp BACKSLASH</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;trans</t>
         </is>
       </c>
@@ -1726,74 +1726,74 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;mt LEFT_SHIFT ESCAPE</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;kp EQUAL</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;trans</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;trans</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;trans</t>
         </is>
       </c>
@@ -1886,50 +1886,50 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -1937,13 +1937,13 @@
       <c r="L25" s="7" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;trans</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -2064,31 +2064,31 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;mm_vim_w</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LC(RIGHT)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_ctrl_r</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -2097,31 +2097,31 @@
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;mm_vim_y</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;mm_vim_u</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;mm_vim_o</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp LC(V)</t>
         </is>
       </c>
@@ -2312,31 +2312,31 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;mm_vim_d</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_g</t>
         </is>
       </c>
@@ -2345,31 +2345,31 @@
       <c r="I34" s="7" t="inlineStr"/>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;mm_vim_j</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;kp UP_ARROW</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;kp RIGHT</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -2583,74 +2583,74 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;kp DELETE</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;mm_vim_v</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;mm_vim_n</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -2753,50 +2753,50 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
@@ -2804,13 +2804,13 @@
       <c r="L42" s="7" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;trans</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -2923,31 +2923,31 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_shift_4</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -2956,31 +2956,31 @@
       <c r="I46" s="7" t="inlineStr"/>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;mm_vim_shift_6</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp HOME</t>
         </is>
       </c>
@@ -3049,31 +3049,31 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
@@ -3082,31 +3082,31 @@
       <c r="I49" s="7" t="inlineStr"/>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -3151,74 +3151,74 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -3259,50 +3259,50 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -3310,13 +3310,13 @@
       <c r="L53" s="7" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;trans</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -3381,31 +3381,31 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -3414,31 +3414,31 @@
       <c r="I56" s="7" t="inlineStr"/>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -3471,31 +3471,31 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
@@ -3504,31 +3504,31 @@
       <c r="I58" s="7" t="inlineStr"/>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -3565,74 +3565,74 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -3665,50 +3665,50 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -3716,13 +3716,13 @@
       <c r="L62" s="7" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -3775,31 +3775,31 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -3808,31 +3808,31 @@
       <c r="I65" s="7" t="inlineStr"/>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -3865,31 +3865,31 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
@@ -3898,31 +3898,31 @@
       <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;mkp MB1</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;mkp MB2</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -3955,74 +3955,74 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;mkp MB4</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;mkp MB5</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -4055,50 +4055,50 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -4106,13 +4106,13 @@
       <c r="L71" s="7" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4165,31 +4165,31 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp F1</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp F2</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp F3</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp F4</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp F5</t>
         </is>
       </c>
@@ -4198,31 +4198,31 @@
       <c r="I74" s="7" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp F10</t>
         </is>
       </c>
@@ -4295,31 +4295,31 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
@@ -4328,31 +4328,31 @@
       <c r="I76" s="7" t="inlineStr"/>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -4385,74 +4385,74 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;bootloader</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -4485,50 +4485,50 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -4536,13 +4536,13 @@
       <c r="L80" s="7" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4595,31 +4595,31 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;bt BT_SEL 0</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;bt BT_SEL 1</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;bt BT_SEL 2</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;bt BT_SEL 3</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;bt BT_SEL 4</t>
         </is>
       </c>
@@ -4628,31 +4628,31 @@
       <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;out OUT_USB</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -4685,31 +4685,31 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
@@ -4718,31 +4718,31 @@
       <c r="I85" s="7" t="inlineStr"/>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -4775,74 +4775,74 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;bt BT_CLR</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;out OUT_BLE</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -4875,50 +4875,50 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -4926,13 +4926,13 @@
       <c r="L89" s="7" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4985,31 +4985,31 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -5018,31 +5018,31 @@
       <c r="I92" s="7" t="inlineStr"/>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;macro_vim_visual_y</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;macro_vim_visual_p</t>
         </is>
       </c>
@@ -5098,31 +5098,31 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_visual_g</t>
         </is>
       </c>
@@ -5131,31 +5131,31 @@
       <c r="I94" s="7" t="inlineStr"/>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -5323,74 +5323,74 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;kp F3</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -5453,50 +5453,50 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -5504,13 +5504,13 @@
       <c r="L100" s="7" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -5679,31 +5679,31 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp Q</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp W</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp E</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp R</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp T</t>
         </is>
       </c>
@@ -5712,31 +5712,31 @@
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp Y</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp U</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp I</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp O</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp P</t>
         </is>
       </c>
@@ -5809,31 +5809,31 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LEFT_CONTROL A</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp S</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp D</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp F</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp G</t>
         </is>
       </c>
@@ -5842,31 +5842,31 @@
       <c r="I7" s="7" t="inlineStr"/>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;kp H</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;kp J</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;kp K</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;kp L</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;mt RCTRL MINUS</t>
         </is>
       </c>
@@ -5999,74 +5999,74 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;mt LEFT_SHIFT Z</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;kp X</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;kp C</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;kp V</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp B</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;kp N</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;kp M</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;kp COMMA</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;kp PERIOD</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;mt RIGHT_SHIFT SLASH</t>
         </is>
       </c>
@@ -6215,50 +6215,50 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
@@ -6266,13 +6266,13 @@
       <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;mo FUNCTION</t>
         </is>
       </c>
@@ -6425,31 +6425,31 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp N1</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp N2</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp N3</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp N4</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp N5</t>
         </is>
       </c>
@@ -6458,31 +6458,31 @@
       <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp N6</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp N7</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp N8</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp N9</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp N0</t>
         </is>
       </c>
@@ -6555,31 +6555,31 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LCTRL TAB</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp GRAVE</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp LEFT_BRACKET</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp RIGHT_BRACKET</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp DELETE</t>
         </is>
       </c>
@@ -6588,31 +6588,31 @@
       <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;kp BACKSPACE</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;kp SEMICOLON</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;kp BACKSLASH</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;trans</t>
         </is>
       </c>
@@ -6745,74 +6745,74 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;mt LEFT_SHIFT ESCAPE</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;kp EQUAL</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;trans</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;trans</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;trans</t>
         </is>
       </c>
@@ -6905,50 +6905,50 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -6956,13 +6956,13 @@
       <c r="L25" s="7" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;trans</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -7083,31 +7083,31 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;mm_vim_w</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LC(RIGHT)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_ctrl_r</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -7116,31 +7116,31 @@
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;mm_vim_y</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;mm_vim_u</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;mm_vim_o</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp LC(V)</t>
         </is>
       </c>
@@ -7346,31 +7346,31 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;mm_vim_d</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_g</t>
         </is>
       </c>
@@ -7379,31 +7379,31 @@
       <c r="I34" s="7" t="inlineStr"/>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;mm_vim_j</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;kp UP_ARROW</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;kp RIGHT</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -7636,74 +7636,74 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;kp DELETE</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;mm_vim_v</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;mm_vim_n</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -7807,50 +7807,50 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
@@ -7858,13 +7858,13 @@
       <c r="L42" s="7" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;trans</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -7977,31 +7977,31 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_shift_4</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -8010,31 +8010,31 @@
       <c r="I46" s="7" t="inlineStr"/>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;mm_vim_shift_6</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp HOME</t>
         </is>
       </c>
@@ -8115,31 +8115,31 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
@@ -8148,31 +8148,31 @@
       <c r="I49" s="7" t="inlineStr"/>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -8217,74 +8217,74 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -8325,50 +8325,50 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -8376,13 +8376,13 @@
       <c r="L53" s="7" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;trans</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -8447,31 +8447,31 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -8480,31 +8480,31 @@
       <c r="I56" s="7" t="inlineStr"/>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -8537,31 +8537,31 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
@@ -8570,31 +8570,31 @@
       <c r="I58" s="7" t="inlineStr"/>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -8631,74 +8631,74 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -8731,50 +8731,50 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -8782,13 +8782,13 @@
       <c r="L62" s="7" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -8841,31 +8841,31 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -8874,31 +8874,31 @@
       <c r="I65" s="7" t="inlineStr"/>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -8931,31 +8931,31 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
@@ -8964,31 +8964,31 @@
       <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;mkp MB1</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;mkp MB2</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -9029,74 +9029,74 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;mkp MB4</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;mkp MB5</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -9137,50 +9137,50 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -9188,13 +9188,13 @@
       <c r="L71" s="7" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -9247,31 +9247,31 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp F1</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp F2</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp F3</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp F4</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp F5</t>
         </is>
       </c>
@@ -9280,31 +9280,31 @@
       <c r="I74" s="7" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp F10</t>
         </is>
       </c>
@@ -9377,31 +9377,31 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
@@ -9410,31 +9410,31 @@
       <c r="I76" s="7" t="inlineStr"/>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -9475,74 +9475,74 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;bootloader</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -9583,50 +9583,50 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -9634,13 +9634,13 @@
       <c r="L80" s="7" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -9693,31 +9693,31 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;bt BT_SEL 0</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;bt BT_SEL 1</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;bt BT_SEL 2</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;bt BT_SEL 3</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;bt BT_SEL 4</t>
         </is>
       </c>
@@ -9726,31 +9726,31 @@
       <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;out OUT_USB</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -9807,31 +9807,31 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
@@ -9840,31 +9840,31 @@
       <c r="I85" s="7" t="inlineStr"/>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -9901,74 +9901,74 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;bt BT_CLR</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;out OUT_BLE</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -10009,50 +10009,50 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -10060,13 +10060,13 @@
       <c r="L89" s="7" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -10119,31 +10119,31 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -10152,31 +10152,31 @@
       <c r="I92" s="7" t="inlineStr"/>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;macro_vim_visual_y</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;macro_vim_visual_p</t>
         </is>
       </c>
@@ -10225,31 +10225,31 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_visual_g</t>
         </is>
       </c>
@@ -10258,31 +10258,31 @@
       <c r="I94" s="7" t="inlineStr"/>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 16
 &amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 17
 &amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 18
 &amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -10456,74 +10456,74 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 26
 &amp;kp F3</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -10580,50 +10580,50 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
@@ -10631,13 +10631,13 @@
       <c r="L100" s="7" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -549,12 +549,11 @@
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -624,11 +623,6 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
     </row>
@@ -649,8 +643,7 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -690,32 +683,31 @@
       </c>
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp Y</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp U</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp I</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp P</t>
@@ -755,28 +747,27 @@
       </c>
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>I</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>O</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -820,32 +811,31 @@
       </c>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp H</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp J</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp K</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp L</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;mt RCTRL MINUS</t>
@@ -885,28 +875,27 @@
       </c>
       <c r="G8" s="9" t="inlineStr"/>
       <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -945,7 +934,11 @@
       </c>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -962,11 +955,6 @@
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -1017,241 +1005,229 @@
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
+          <t>pos 26
+&amp;kp N</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;kp M</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>pos 28
+&amp;kp COMMA</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>pos 29
+&amp;kp PERIOD</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;mt RIGHT_SHIFT SLASH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>ホールド</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;mo FUNCTION</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;lt VIM_NORMAL_BASE SPACE</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;lt VIM_NORMAL_BASE SPACE</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;mo NUM_SYMBOL</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;lt NUM_SYMBOL ENTER</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
           <t>pos 38
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;kp N</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>pos 27
-&amp;kp M</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>pos 28
-&amp;kp COMMA</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;kp PERIOD</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;mt RIGHT_SHIFT SLASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr"/>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>,</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>ホールド</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>LShift</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>RShift</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;mo FUNCTION</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;kp LEFT_WIN</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;kp LEFT_ALT</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;lt VIM_NORMAL_BASE SPACE</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;lt VIM_NORMAL_BASE SPACE</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;mo NUM_SYMBOL</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;lt NUM_SYMBOL ENTER</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;mo FUNCTION</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;mo FUNCTION</t>
@@ -1297,22 +1273,25 @@
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
+          <t>ENTER</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>ENTER</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
       <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>L6</t>
         </is>
@@ -1357,22 +1336,25 @@
       <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>〃</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr"/>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1395,8 +1377,7 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -1436,32 +1417,31 @@
       </c>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr"/>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp N6</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp N7</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp N8</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp N9</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp N0</t>
@@ -1501,28 +1481,27 @@
       </c>
       <c r="G18" s="9" t="inlineStr"/>
       <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1566,32 +1545,31 @@
       </c>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp BACKSPACE</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp SEMICOLON</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp BACKSLASH</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;trans</t>
@@ -1631,28 +1609,27 @@
       </c>
       <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>;</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>;</t>
+          <t>'</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>'</t>
+          <t>\</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>\</t>
-        </is>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -1691,7 +1668,11 @@
       </c>
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1708,11 +1689,6 @@
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1763,35 +1739,29 @@
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;kp EQUAL</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;trans</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;trans</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;trans</t>
@@ -1816,10 +1786,14 @@
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="9" t="inlineStr"/>
       <c r="I23" s="9" t="inlineStr"/>
-      <c r="J23" s="9" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -1828,11 +1802,6 @@
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
-      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -1856,7 +1825,11 @@
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="9" t="inlineStr"/>
       <c r="I24" s="9" t="inlineStr"/>
-      <c r="J24" s="9" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1868,11 +1841,6 @@
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1923,25 +1891,29 @@
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr"/>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;trans</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -1977,20 +1949,19 @@
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr"/>
-      <c r="L26" s="9" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -2021,20 +1992,19 @@
       </c>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr"/>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I27" s="9" t="inlineStr"/>
       <c r="J27" s="9" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N27" s="9" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2053,8 +2023,7 @@
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -2094,32 +2063,31 @@
       </c>
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_y</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;mm_vim_u</t>
         </is>
       </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
       <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;mm_vim_o</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp LC(V)</t>
@@ -2148,20 +2116,19 @@
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr"/>
       <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="9" t="inlineStr"/>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>⌃Z</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr"/>
+      <c r="L30" s="10" t="inlineStr">
         <is>
           <t>END
 ▸ ENTER</t>
         </is>
       </c>
-      <c r="N30" s="9" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>⌃V</t>
         </is>
@@ -2188,26 +2155,25 @@
       <c r="F31" s="9" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="9" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ⇧END
 ▸ ⌃C</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr"/>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2234,27 +2200,26 @@
       <c r="F32" s="9" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr"/>
-      <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>⇧END
 ▸ ⌃C</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr"/>
+      <c r="L32" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ENTER
 ▸ ↑</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2286,19 +2251,18 @@
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="9" t="inlineStr"/>
       <c r="I33" s="9" t="inlineStr"/>
-      <c r="J33" s="9" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>PgUp</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2342,32 +2306,31 @@
       </c>
       <c r="G34" s="7" t="inlineStr"/>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mm_vim_j</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp UP_ARROW</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr">
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp RIGHT</t>
         </is>
       </c>
-      <c r="N34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -2391,28 +2354,27 @@
       <c r="F35" s="9" t="inlineStr"/>
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="9" t="inlineStr"/>
-      <c r="I35" s="9" t="inlineStr"/>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>←</t>
+        </is>
+      </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>←</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>→</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
-        <is>
-          <t>→</t>
-        </is>
-      </c>
-      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -2445,7 +2407,11 @@
       </c>
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -2462,11 +2428,6 @@
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2498,30 +2459,29 @@
       </c>
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="9" t="inlineStr"/>
-      <c r="I37" s="9" t="inlineStr"/>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>END
 ▸ DEL
 ▸ SPACE</t>
         </is>
       </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2548,7 +2508,11 @@
       <c r="F38" s="9" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="9" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -2565,11 +2529,6 @@
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2620,35 +2579,29 @@
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
           <t>pos 26
 &amp;mm_vim_n</t>
         </is>
       </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;none</t>
+        </is>
+      </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -2684,16 +2637,15 @@
       </c>
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="9" t="inlineStr"/>
-      <c r="I40" s="9" t="inlineStr"/>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
+      <c r="J40" s="9" t="inlineStr"/>
       <c r="K40" s="9" t="inlineStr"/>
       <c r="L40" s="9" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr"/>
-      <c r="N40" s="9" t="inlineStr">
+      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -2730,16 +2682,15 @@
       </c>
       <c r="G41" s="9" t="inlineStr"/>
       <c r="H41" s="9" t="inlineStr"/>
-      <c r="I41" s="9" t="inlineStr"/>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr"/>
       <c r="K41" s="9" t="inlineStr"/>
       <c r="L41" s="9" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr"/>
-      <c r="N41" s="9" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2790,25 +2741,29 @@
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr">
-        <is>
           <t>pos 37
 &amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
-      <c r="M42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;trans</t>
         </is>
       </c>
-      <c r="N42" s="7" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -2840,20 +2795,19 @@
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr"/>
-      <c r="I43" s="9" t="inlineStr"/>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>ENTER</t>
         </is>
       </c>
+      <c r="J43" s="9" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N43" s="9" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -2880,20 +2834,19 @@
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr"/>
-      <c r="I44" s="9" t="inlineStr"/>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
+      <c r="J44" s="9" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2912,8 +2865,7 @@
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -2953,32 +2905,31 @@
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr"/>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_shift_6</t>
         </is>
       </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N46" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp HOME</t>
@@ -3002,8 +2953,7 @@
       <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr"/>
       <c r="L47" s="9" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
-      <c r="N47" s="9" t="inlineStr">
+      <c r="M47" s="9" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
@@ -3026,16 +2976,15 @@
       <c r="F48" s="9" t="inlineStr"/>
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="9" t="inlineStr"/>
-      <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="9" t="inlineStr">
+      <c r="I48" s="9" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
+      <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr"/>
       <c r="L48" s="9" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr"/>
-      <c r="N48" s="9" t="inlineStr">
+      <c r="M48" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -3079,32 +3028,31 @@
       </c>
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>pos 16
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>pos 17
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -3128,16 +3076,15 @@
       <c r="F50" s="9" t="inlineStr"/>
       <c r="G50" s="9" t="inlineStr"/>
       <c r="H50" s="9" t="inlineStr"/>
-      <c r="I50" s="9" t="inlineStr"/>
-      <c r="J50" s="9" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>←</t>
         </is>
       </c>
+      <c r="J50" s="9" t="inlineStr"/>
       <c r="K50" s="9" t="inlineStr"/>
       <c r="L50" s="9" t="inlineStr"/>
-      <c r="M50" s="9" t="inlineStr"/>
-      <c r="N50" s="9" t="inlineStr">
+      <c r="M50" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -3188,35 +3135,29 @@
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>pos 26
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N51" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -3244,8 +3185,7 @@
       <c r="J52" s="9" t="inlineStr"/>
       <c r="K52" s="9" t="inlineStr"/>
       <c r="L52" s="9" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr"/>
-      <c r="N52" s="9" t="inlineStr">
+      <c r="M52" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -3296,25 +3236,29 @@
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr"/>
-      <c r="M53" s="7" t="inlineStr">
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;trans</t>
         </is>
       </c>
-      <c r="N53" s="7" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -3345,13 +3289,12 @@
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
-      <c r="L54" s="9" t="inlineStr"/>
-      <c r="M54" s="9" t="inlineStr">
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N54" s="9" t="inlineStr"/>
+      <c r="M54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -3370,8 +3313,7 @@
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -3411,32 +3353,31 @@
       </c>
       <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>pos 5
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N56" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -3461,7 +3402,6 @@
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr"/>
-      <c r="N57" s="9" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -3501,32 +3441,31 @@
       </c>
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>pos 15
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
-        <is>
-          <t>pos 16
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
       <c r="M58" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N58" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -3548,14 +3487,13 @@
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr"/>
       <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr"/>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
+      <c r="L59" s="9" t="inlineStr"/>
       <c r="M59" s="9" t="inlineStr"/>
-      <c r="N59" s="9" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
@@ -3602,35 +3540,29 @@
       <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>pos 26
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -3655,7 +3587,6 @@
       <c r="K61" s="9" t="inlineStr"/>
       <c r="L61" s="9" t="inlineStr"/>
       <c r="M61" s="9" t="inlineStr"/>
-      <c r="N61" s="9" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
@@ -3702,25 +3633,29 @@
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="inlineStr"/>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M62" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N62" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -3745,7 +3680,6 @@
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -3764,8 +3698,7 @@
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
@@ -3805,32 +3738,31 @@
       </c>
       <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>pos 5
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -3855,7 +3787,6 @@
       <c r="K66" s="9" t="inlineStr"/>
       <c r="L66" s="9" t="inlineStr"/>
       <c r="M66" s="9" t="inlineStr"/>
-      <c r="N66" s="9" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -3895,32 +3826,31 @@
       </c>
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J67" s="7" t="inlineStr">
-        <is>
-          <t>pos 15
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mkp MB1</t>
         </is>
       </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;none</t>
+        </is>
+      </c>
       <c r="L67" s="7" t="inlineStr">
-        <is>
-          <t>pos 17
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;mkp MB2</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -3945,7 +3875,6 @@
       <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="9" t="inlineStr"/>
       <c r="M68" s="9" t="inlineStr"/>
-      <c r="N68" s="9" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
@@ -3992,35 +3921,29 @@
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;mkp MB4</t>
         </is>
       </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>pos 28
+&amp;none</t>
+        </is>
+      </c>
       <c r="L69" s="7" t="inlineStr">
-        <is>
-          <t>pos 28
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M69" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;mkp MB5</t>
         </is>
       </c>
-      <c r="N69" s="7" t="inlineStr">
+      <c r="M69" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -4045,7 +3968,6 @@
       <c r="K70" s="9" t="inlineStr"/>
       <c r="L70" s="9" t="inlineStr"/>
       <c r="M70" s="9" t="inlineStr"/>
-      <c r="N70" s="9" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
@@ -4092,25 +4014,29 @@
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J71" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr"/>
-      <c r="L71" s="7" t="inlineStr"/>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M71" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N71" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -4135,7 +4061,6 @@
       <c r="K72" s="9" t="inlineStr"/>
       <c r="L72" s="9" t="inlineStr"/>
       <c r="M72" s="9" t="inlineStr"/>
-      <c r="N72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -4154,8 +4079,7 @@
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
@@ -4195,32 +4119,31 @@
       </c>
       <c r="G74" s="7" t="inlineStr"/>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="J74" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="K74" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
-      <c r="M74" s="7" t="inlineStr">
+      <c r="L74" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
-      <c r="N74" s="7" t="inlineStr">
+      <c r="M74" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp F10</t>
@@ -4260,28 +4183,27 @@
       </c>
       <c r="G75" s="9" t="inlineStr"/>
       <c r="H75" s="9" t="inlineStr"/>
-      <c r="I75" s="9" t="inlineStr"/>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>F9</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
-        <is>
-          <t>F9</t>
-        </is>
-      </c>
-      <c r="N75" s="9" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
@@ -4325,32 +4247,31 @@
       </c>
       <c r="G76" s="7" t="inlineStr"/>
       <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr"/>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>pos 15
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>pos 16
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
-        <is>
-          <t>pos 17
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="N76" s="7" t="inlineStr">
+      <c r="M76" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -4375,7 +4296,6 @@
       <c r="K77" s="9" t="inlineStr"/>
       <c r="L77" s="9" t="inlineStr"/>
       <c r="M77" s="9" t="inlineStr"/>
-      <c r="N77" s="9" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
@@ -4422,35 +4342,29 @@
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J78" s="7" t="inlineStr">
-        <is>
           <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;none</t>
+        </is>
+      </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N78" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -4475,7 +4389,6 @@
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr"/>
       <c r="M79" s="9" t="inlineStr"/>
-      <c r="N79" s="9" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
@@ -4522,25 +4435,29 @@
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr"/>
-      <c r="L80" s="7" t="inlineStr"/>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M80" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N80" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -4565,7 +4482,6 @@
       <c r="K81" s="9" t="inlineStr"/>
       <c r="L81" s="9" t="inlineStr"/>
       <c r="M81" s="9" t="inlineStr"/>
-      <c r="N81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -4584,8 +4500,7 @@
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -4625,32 +4540,31 @@
       </c>
       <c r="G83" s="7" t="inlineStr"/>
       <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J83" s="7" t="inlineStr">
-        <is>
-          <t>pos 5
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;out OUT_USB</t>
         </is>
       </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N83" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -4675,7 +4589,6 @@
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
-      <c r="N84" s="9" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
@@ -4715,32 +4628,31 @@
       </c>
       <c r="G85" s="7" t="inlineStr"/>
       <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>pos 15
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>pos 16
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>pos 17
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N85" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -4765,7 +4677,6 @@
       <c r="K86" s="9" t="inlineStr"/>
       <c r="L86" s="9" t="inlineStr"/>
       <c r="M86" s="9" t="inlineStr"/>
-      <c r="N86" s="9" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
@@ -4812,35 +4723,29 @@
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>pos 26
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N87" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -4865,7 +4770,6 @@
       <c r="K88" s="9" t="inlineStr"/>
       <c r="L88" s="9" t="inlineStr"/>
       <c r="M88" s="9" t="inlineStr"/>
-      <c r="N88" s="9" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
@@ -4912,25 +4816,29 @@
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr"/>
-      <c r="L89" s="7" t="inlineStr"/>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M89" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N89" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -4955,7 +4863,6 @@
       <c r="K90" s="9" t="inlineStr"/>
       <c r="L90" s="9" t="inlineStr"/>
       <c r="M90" s="9" t="inlineStr"/>
-      <c r="N90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -4974,8 +4881,7 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="n"/>
       <c r="L91" s="4" t="n"/>
-      <c r="M91" s="4" t="n"/>
-      <c r="N91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
@@ -5015,32 +4921,31 @@
       </c>
       <c r="G92" s="7" t="inlineStr"/>
       <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
-      <c r="J92" s="7" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;macro_vim_visual_y</t>
         </is>
       </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N92" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;macro_vim_visual_p</t>
@@ -5068,8 +4973,7 @@
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
-      <c r="I93" s="9" t="inlineStr"/>
-      <c r="J93" s="10" t="inlineStr">
+      <c r="I93" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -5078,10 +4982,10 @@
 ▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
+      <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
-      <c r="M93" s="9" t="inlineStr"/>
-      <c r="N93" s="10" t="inlineStr">
+      <c r="M93" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -5128,32 +5032,31 @@
       </c>
       <c r="G94" s="7" t="inlineStr"/>
       <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
-      <c r="J94" s="7" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="K94" s="7" t="inlineStr">
+      <c r="J94" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp LS(DOWN)</t>
         </is>
       </c>
-      <c r="L94" s="7" t="inlineStr">
+      <c r="K94" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp LS(UP)</t>
         </is>
       </c>
-      <c r="M94" s="7" t="inlineStr">
+      <c r="L94" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp LS(RIGHT)</t>
         </is>
       </c>
-      <c r="N94" s="7" t="inlineStr">
+      <c r="M94" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -5184,28 +5087,27 @@
       <c r="F95" s="9" t="inlineStr"/>
       <c r="G95" s="9" t="inlineStr"/>
       <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>⇧←</t>
+        </is>
+      </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>⇧←</t>
+          <t>⇧↓</t>
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr">
         <is>
-          <t>⇧↓</t>
+          <t>⇧↑</t>
         </is>
       </c>
       <c r="L95" s="9" t="inlineStr">
         <is>
-          <t>⇧↑</t>
+          <t>⇧→</t>
         </is>
       </c>
       <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>⇧→</t>
-        </is>
-      </c>
-      <c r="N95" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -5236,7 +5138,11 @@
       </c>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
-      <c r="I96" s="9" t="inlineStr"/>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -5253,11 +5159,6 @@
         </is>
       </c>
       <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N96" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -5288,7 +5189,11 @@
       </c>
       <c r="G97" s="9" t="inlineStr"/>
       <c r="H97" s="9" t="inlineStr"/>
-      <c r="I97" s="9" t="inlineStr"/>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -5305,11 +5210,6 @@
         </is>
       </c>
       <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N97" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -5360,35 +5260,29 @@
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J98" s="7" t="inlineStr">
-        <is>
           <t>pos 26
 &amp;kp F3</t>
         </is>
       </c>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;none</t>
+        </is>
+      </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N98" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -5430,16 +5324,15 @@
       </c>
       <c r="G99" s="9" t="inlineStr"/>
       <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr"/>
-      <c r="J99" s="9" t="inlineStr">
+      <c r="I99" s="9" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
+      <c r="J99" s="9" t="inlineStr"/>
       <c r="K99" s="9" t="inlineStr"/>
       <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="9" t="inlineStr">
+      <c r="M99" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -5490,25 +5383,29 @@
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr"/>
-      <c r="L100" s="7" t="inlineStr"/>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M100" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N100" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -5533,19 +5430,18 @@
       <c r="K101" s="9" t="inlineStr"/>
       <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
-      <c r="N101" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A91:N91"/>
-    <mergeCell ref="A55:N55"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A45:N45"/>
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A73:N73"/>
-    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A91:M91"/>
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="A64:M64"/>
+    <mergeCell ref="A73:M73"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A82:M82"/>
+    <mergeCell ref="A28:M28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5557,7 +5453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5568,12 +5464,11 @@
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5643,11 +5538,6 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
     </row>
@@ -5668,8 +5558,7 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -5709,32 +5598,31 @@
       </c>
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp Y</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp U</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp I</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp P</t>
@@ -5774,28 +5662,27 @@
       </c>
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp Y</t>
+        </is>
+      </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp Y</t>
+          <t>&amp;kp U</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp U</t>
+          <t>&amp;kp I</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp I</t>
+          <t>&amp;kp O</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp O</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp P</t>
         </is>
@@ -5839,32 +5726,31 @@
       </c>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp H</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp J</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp K</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp L</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;mt RCTRL MINUS</t>
@@ -5904,28 +5790,27 @@
       </c>
       <c r="G8" s="9" t="inlineStr"/>
       <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp H</t>
+        </is>
+      </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp H</t>
+          <t>&amp;kp J</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp J</t>
+          <t>&amp;kp K</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp K</t>
+          <t>&amp;kp L</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp L</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>&amp;mt RCTRL MINUS</t>
         </is>
@@ -5964,7 +5849,11 @@
       </c>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -5981,11 +5870,6 @@
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>&amp;mt RCTRL MINUS</t>
         </is>
@@ -6036,241 +5920,229 @@
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
+          <t>pos 26
+&amp;kp N</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;kp M</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>pos 28
+&amp;kp COMMA</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>pos 29
+&amp;kp PERIOD</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;mt RIGHT_SHIFT SLASH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mt LEFT_SHIFT Z</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp X</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp C</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp V</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp B</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp N</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp M</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp COMMA</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PERIOD</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mt RIGHT_SHIFT SLASH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>ホールド</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mt LEFT_SHIFT Z</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mt RIGHT_SHIFT SLASH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;mo FUNCTION</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;lt VIM_NORMAL_BASE SPACE</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;lt VIM_NORMAL_BASE SPACE</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;mo NUM_SYMBOL</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;lt NUM_SYMBOL ENTER</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
           <t>pos 38
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;kp N</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>pos 27
-&amp;kp M</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>pos 28
-&amp;kp COMMA</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;kp PERIOD</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;mt RIGHT_SHIFT SLASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mt LEFT_SHIFT Z</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp X</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp C</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp V</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp B</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo BLUETOOTH</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr"/>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo BLUETOOTH</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp N</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp M</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp COMMA</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp PERIOD</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mt RIGHT_SHIFT SLASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>ホールド</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mt LEFT_SHIFT Z</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mt RIGHT_SHIFT SLASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;mo FUNCTION</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;kp LEFT_WIN</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;kp LEFT_ALT</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;lt VIM_NORMAL_BASE SPACE</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;lt VIM_NORMAL_BASE SPACE</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;mo NUM_SYMBOL</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;lt NUM_SYMBOL ENTER</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;mo FUNCTION</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;mo FUNCTION</t>
@@ -6316,22 +6188,25 @@
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
+          <t>&amp;lt NUM_SYMBOL ENTER</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
           <t>&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;lt NUM_SYMBOL ENTER</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo FUNCTION</t>
+        </is>
+      </c>
       <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo FUNCTION</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>&amp;mo FUNCTION</t>
         </is>
@@ -6376,22 +6251,25 @@
       <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>〃</t>
+          <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt NUM_SYMBOL ENTER</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr"/>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -6414,8 +6292,7 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -6455,32 +6332,31 @@
       </c>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr"/>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp N6</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp N7</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp N8</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp N9</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp N0</t>
@@ -6520,28 +6396,27 @@
       </c>
       <c r="G18" s="9" t="inlineStr"/>
       <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp N6</t>
+        </is>
+      </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp N6</t>
+          <t>&amp;kp N7</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp N7</t>
+          <t>&amp;kp N8</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp N8</t>
+          <t>&amp;kp N9</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp N9</t>
-        </is>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N0</t>
         </is>
@@ -6585,32 +6460,31 @@
       </c>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp BACKSPACE</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp SEMICOLON</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp BACKSLASH</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;trans</t>
@@ -6650,28 +6524,27 @@
       </c>
       <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp BACKSPACE</t>
+        </is>
+      </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp BACKSPACE</t>
+          <t>&amp;kp SEMICOLON</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp SEMICOLON</t>
+          <t>&amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp SINGLE_QUOTE</t>
+          <t>&amp;kp BACKSLASH</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp BACKSLASH</t>
-        </is>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -6710,7 +6583,11 @@
       </c>
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6727,11 +6604,6 @@
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -6782,35 +6654,29 @@
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;kp EQUAL</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;trans</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;trans</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;trans</t>
@@ -6835,10 +6701,14 @@
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="9" t="inlineStr"/>
       <c r="I23" s="9" t="inlineStr"/>
-      <c r="J23" s="9" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp EQUAL</t>
+        </is>
+      </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp EQUAL</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -6847,11 +6717,6 @@
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
-      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -6875,7 +6740,11 @@
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="9" t="inlineStr"/>
       <c r="I24" s="9" t="inlineStr"/>
-      <c r="J24" s="9" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6887,11 +6756,6 @@
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -6942,25 +6806,29 @@
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr"/>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;trans</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -6996,20 +6864,19 @@
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr"/>
-      <c r="L26" s="9" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -7040,20 +6907,19 @@
       </c>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr"/>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I27" s="9" t="inlineStr"/>
       <c r="J27" s="9" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N27" s="9" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -7072,8 +6938,7 @@
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -7113,32 +6978,31 @@
       </c>
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_y</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;mm_vim_u</t>
         </is>
       </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
       <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;mm_vim_o</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp LC(V)</t>
@@ -7172,28 +7036,27 @@
       <c r="F30" s="9" t="inlineStr"/>
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr"/>
-      <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[0]
 ▸ td_vim_y[0]
 ▸ &amp;none</t>
         </is>
       </c>
-      <c r="K30" s="10" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_u[0]
 ▸ &amp;kp LC(Z)</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr"/>
+      <c r="L30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_o[0]
 ▸ macro_vim_o</t>
         </is>
       </c>
-      <c r="N30" s="9" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LC(V)</t>
         </is>
@@ -7220,26 +7083,25 @@
       <c r="F31" s="9" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="9" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[0]
 ▸ td_vim_y[1]
 ▸ macro_vim_yy</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr"/>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7266,26 +7128,25 @@
       <c r="F32" s="9" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr"/>
-      <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[1]
 ▸ macro_vim_shift_y</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr"/>
+      <c r="L32" s="10" t="inlineStr">
         <is>
           <t>mm_vim_o[1]
 ▸ macro_vim_shift_o</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7319,20 +7180,19 @@
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="9" t="inlineStr"/>
       <c r="I33" s="9" t="inlineStr"/>
-      <c r="J33" s="9" t="inlineStr"/>
-      <c r="K33" s="10" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>mm_vim_u[1]
 ▸ &amp;kp PAGE_UP</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7376,32 +7236,31 @@
       </c>
       <c r="G34" s="7" t="inlineStr"/>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mm_vim_j</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp UP_ARROW</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr">
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp RIGHT</t>
         </is>
       </c>
-      <c r="N34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -7438,29 +7297,28 @@
       </c>
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="9" t="inlineStr"/>
-      <c r="I35" s="9" t="inlineStr"/>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LEFT</t>
         </is>
       </c>
-      <c r="K35" s="10" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>mm_vim_j[0]
 ▸ &amp;kp DOWN</t>
         </is>
       </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp UP_ARROW</t>
+        </is>
+      </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp UP_ARROW</t>
+          <t>&amp;kp RIGHT</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RIGHT</t>
-        </is>
-      </c>
-      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -7496,7 +7354,11 @@
       </c>
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -7513,11 +7375,6 @@
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7551,29 +7408,28 @@
       </c>
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="9" t="inlineStr"/>
-      <c r="I37" s="9" t="inlineStr"/>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>mm_vim_j[1]
 ▸ macro_vim_join</t>
         </is>
       </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7601,7 +7457,11 @@
       <c r="F38" s="9" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="9" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -7618,11 +7478,6 @@
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7673,35 +7528,29 @@
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
           <t>pos 26
 &amp;mm_vim_n</t>
         </is>
       </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;none</t>
+        </is>
+      </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -7738,17 +7587,16 @@
       </c>
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="9" t="inlineStr"/>
-      <c r="I40" s="9" t="inlineStr"/>
-      <c r="J40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>mm_vim_n[0]
 ▸ &amp;kp F3</t>
         </is>
       </c>
+      <c r="J40" s="9" t="inlineStr"/>
       <c r="K40" s="9" t="inlineStr"/>
       <c r="L40" s="9" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr"/>
-      <c r="N40" s="9" t="inlineStr">
+      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -7784,16 +7632,15 @@
       </c>
       <c r="G41" s="9" t="inlineStr"/>
       <c r="H41" s="9" t="inlineStr"/>
-      <c r="I41" s="9" t="inlineStr"/>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr"/>
       <c r="K41" s="9" t="inlineStr"/>
       <c r="L41" s="9" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr"/>
-      <c r="N41" s="9" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7844,25 +7691,29 @@
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr">
-        <is>
           <t>pos 37
 &amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
-      <c r="M42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;trans</t>
         </is>
       </c>
-      <c r="N42" s="7" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -7894,20 +7745,19 @@
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr"/>
-      <c r="I43" s="9" t="inlineStr"/>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
+      <c r="J43" s="9" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N43" s="9" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -7934,20 +7784,19 @@
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr"/>
-      <c r="I44" s="9" t="inlineStr"/>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
+      <c r="J44" s="9" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -7966,8 +7815,7 @@
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -8007,32 +7855,31 @@
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr"/>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_shift_6</t>
         </is>
       </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N46" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp HOME</t>
@@ -8057,17 +7904,16 @@
       <c r="F47" s="9" t="inlineStr"/>
       <c r="G47" s="9" t="inlineStr"/>
       <c r="H47" s="9" t="inlineStr"/>
-      <c r="I47" s="9" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_6[0]
 ▸ &amp;none</t>
         </is>
       </c>
+      <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr"/>
       <c r="L47" s="9" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
-      <c r="N47" s="9" t="inlineStr">
+      <c r="M47" s="9" t="inlineStr">
         <is>
           <t>&amp;kp HOME</t>
         </is>
@@ -8091,17 +7937,16 @@
       <c r="F48" s="9" t="inlineStr"/>
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="9" t="inlineStr"/>
-      <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_6[1]
 ▸ &amp;kp HOME</t>
         </is>
       </c>
+      <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr"/>
       <c r="L48" s="9" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr"/>
-      <c r="N48" s="9" t="inlineStr">
+      <c r="M48" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -8145,32 +7990,31 @@
       </c>
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>pos 16
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>pos 17
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -8194,16 +8038,15 @@
       <c r="F50" s="9" t="inlineStr"/>
       <c r="G50" s="9" t="inlineStr"/>
       <c r="H50" s="9" t="inlineStr"/>
-      <c r="I50" s="9" t="inlineStr"/>
-      <c r="J50" s="9" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LEFT</t>
         </is>
       </c>
+      <c r="J50" s="9" t="inlineStr"/>
       <c r="K50" s="9" t="inlineStr"/>
       <c r="L50" s="9" t="inlineStr"/>
-      <c r="M50" s="9" t="inlineStr"/>
-      <c r="N50" s="9" t="inlineStr">
+      <c r="M50" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -8254,35 +8097,29 @@
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>pos 26
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N51" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -8310,8 +8147,7 @@
       <c r="J52" s="9" t="inlineStr"/>
       <c r="K52" s="9" t="inlineStr"/>
       <c r="L52" s="9" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr"/>
-      <c r="N52" s="9" t="inlineStr">
+      <c r="M52" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -8362,25 +8198,29 @@
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr"/>
-      <c r="M53" s="7" t="inlineStr">
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;trans</t>
         </is>
       </c>
-      <c r="N53" s="7" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -8411,13 +8251,12 @@
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
-      <c r="L54" s="9" t="inlineStr"/>
-      <c r="M54" s="9" t="inlineStr">
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N54" s="9" t="inlineStr"/>
+      <c r="M54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -8436,8 +8275,7 @@
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -8477,32 +8315,31 @@
       </c>
       <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>pos 5
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N56" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -8527,7 +8364,6 @@
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr"/>
-      <c r="N57" s="9" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -8567,32 +8403,31 @@
       </c>
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>pos 15
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
-        <is>
-          <t>pos 16
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
       <c r="M58" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N58" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -8614,14 +8449,13 @@
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr"/>
       <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr"/>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
+      <c r="L59" s="9" t="inlineStr"/>
       <c r="M59" s="9" t="inlineStr"/>
-      <c r="N59" s="9" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
@@ -8668,35 +8502,29 @@
       <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>pos 26
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -8721,7 +8549,6 @@
       <c r="K61" s="9" t="inlineStr"/>
       <c r="L61" s="9" t="inlineStr"/>
       <c r="M61" s="9" t="inlineStr"/>
-      <c r="N61" s="9" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
@@ -8768,25 +8595,29 @@
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="inlineStr"/>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M62" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N62" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -8811,7 +8642,6 @@
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -8830,8 +8660,7 @@
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
@@ -8871,32 +8700,31 @@
       </c>
       <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>pos 5
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -8921,7 +8749,6 @@
       <c r="K66" s="9" t="inlineStr"/>
       <c r="L66" s="9" t="inlineStr"/>
       <c r="M66" s="9" t="inlineStr"/>
-      <c r="N66" s="9" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -8961,32 +8788,31 @@
       </c>
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J67" s="7" t="inlineStr">
-        <is>
-          <t>pos 15
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mkp MB1</t>
         </is>
       </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;none</t>
+        </is>
+      </c>
       <c r="L67" s="7" t="inlineStr">
-        <is>
-          <t>pos 17
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;mkp MB2</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -9007,19 +8833,18 @@
       <c r="G68" s="9" t="inlineStr"/>
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
-      <c r="J68" s="9" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr">
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB1</t>
         </is>
       </c>
-      <c r="L68" s="9" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr">
+      <c r="K68" s="9" t="inlineStr"/>
+      <c r="L68" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB2</t>
         </is>
       </c>
-      <c r="N68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
@@ -9066,35 +8891,29 @@
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;mkp MB4</t>
         </is>
       </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>pos 28
+&amp;none</t>
+        </is>
+      </c>
       <c r="L69" s="7" t="inlineStr">
-        <is>
-          <t>pos 28
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M69" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;mkp MB5</t>
         </is>
       </c>
-      <c r="N69" s="7" t="inlineStr">
+      <c r="M69" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -9115,19 +8934,18 @@
       <c r="G70" s="9" t="inlineStr"/>
       <c r="H70" s="9" t="inlineStr"/>
       <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
-      <c r="K70" s="9" t="inlineStr">
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB4</t>
         </is>
       </c>
-      <c r="L70" s="9" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr">
+      <c r="K70" s="9" t="inlineStr"/>
+      <c r="L70" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB5</t>
         </is>
       </c>
-      <c r="N70" s="9" t="inlineStr"/>
+      <c r="M70" s="9" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
@@ -9174,25 +8992,29 @@
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J71" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr"/>
-      <c r="L71" s="7" t="inlineStr"/>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M71" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N71" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -9217,7 +9039,6 @@
       <c r="K72" s="9" t="inlineStr"/>
       <c r="L72" s="9" t="inlineStr"/>
       <c r="M72" s="9" t="inlineStr"/>
-      <c r="N72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -9236,8 +9057,7 @@
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
@@ -9277,32 +9097,31 @@
       </c>
       <c r="G74" s="7" t="inlineStr"/>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="J74" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="K74" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
-      <c r="M74" s="7" t="inlineStr">
+      <c r="L74" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
-      <c r="N74" s="7" t="inlineStr">
+      <c r="M74" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp F10</t>
@@ -9342,28 +9161,27 @@
       </c>
       <c r="G75" s="9" t="inlineStr"/>
       <c r="H75" s="9" t="inlineStr"/>
-      <c r="I75" s="9" t="inlineStr"/>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F6</t>
+        </is>
+      </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp F6</t>
+          <t>&amp;kp F7</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp F7</t>
+          <t>&amp;kp F8</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp F8</t>
+          <t>&amp;kp F9</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F9</t>
-        </is>
-      </c>
-      <c r="N75" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F10</t>
         </is>
@@ -9407,32 +9225,31 @@
       </c>
       <c r="G76" s="7" t="inlineStr"/>
       <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr"/>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>pos 15
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>pos 16
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
-        <is>
-          <t>pos 17
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="N76" s="7" t="inlineStr">
+      <c r="M76" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -9459,13 +9276,12 @@
       <c r="I77" s="9" t="inlineStr"/>
       <c r="J77" s="9" t="inlineStr"/>
       <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr">
+      <c r="L77" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="N77" s="9" t="inlineStr"/>
+      <c r="M77" s="9" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
@@ -9512,35 +9328,29 @@
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J78" s="7" t="inlineStr">
-        <is>
           <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;none</t>
+        </is>
+      </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N78" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -9564,16 +9374,15 @@
       </c>
       <c r="G79" s="9" t="inlineStr"/>
       <c r="H79" s="9" t="inlineStr"/>
-      <c r="I79" s="9" t="inlineStr"/>
-      <c r="J79" s="9" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t>&amp;bootloader</t>
         </is>
       </c>
+      <c r="J79" s="9" t="inlineStr"/>
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr"/>
       <c r="M79" s="9" t="inlineStr"/>
-      <c r="N79" s="9" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
@@ -9620,25 +9429,29 @@
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr"/>
-      <c r="L80" s="7" t="inlineStr"/>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M80" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N80" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -9663,7 +9476,6 @@
       <c r="K81" s="9" t="inlineStr"/>
       <c r="L81" s="9" t="inlineStr"/>
       <c r="M81" s="9" t="inlineStr"/>
-      <c r="N81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -9682,8 +9494,7 @@
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -9723,32 +9534,31 @@
       </c>
       <c r="G83" s="7" t="inlineStr"/>
       <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J83" s="7" t="inlineStr">
-        <is>
-          <t>pos 5
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;out OUT_USB</t>
         </is>
       </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N83" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -9789,15 +9599,14 @@
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
-      <c r="J84" s="9" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr">
+      <c r="J84" s="9" t="inlineStr">
         <is>
           <t>&amp;out OUT_USB</t>
         </is>
       </c>
+      <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
-      <c r="N84" s="9" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
@@ -9837,32 +9646,31 @@
       </c>
       <c r="G85" s="7" t="inlineStr"/>
       <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>pos 15
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>pos 16
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>pos 17
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N85" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -9891,7 +9699,6 @@
       <c r="K86" s="9" t="inlineStr"/>
       <c r="L86" s="9" t="inlineStr"/>
       <c r="M86" s="9" t="inlineStr"/>
-      <c r="N86" s="9" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
@@ -9938,35 +9745,29 @@
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>pos 26
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N87" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -9999,7 +9800,6 @@
       <c r="K88" s="9" t="inlineStr"/>
       <c r="L88" s="9" t="inlineStr"/>
       <c r="M88" s="9" t="inlineStr"/>
-      <c r="N88" s="9" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
@@ -10046,25 +9846,29 @@
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr"/>
-      <c r="L89" s="7" t="inlineStr"/>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M89" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N89" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -10089,7 +9893,6 @@
       <c r="K90" s="9" t="inlineStr"/>
       <c r="L90" s="9" t="inlineStr"/>
       <c r="M90" s="9" t="inlineStr"/>
-      <c r="N90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -10108,8 +9911,7 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="n"/>
       <c r="L91" s="4" t="n"/>
-      <c r="M91" s="4" t="n"/>
-      <c r="N91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
@@ -10149,32 +9951,31 @@
       </c>
       <c r="G92" s="7" t="inlineStr"/>
       <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
-      <c r="J92" s="7" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;macro_vim_visual_y</t>
         </is>
       </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N92" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;macro_vim_visual_p</t>
@@ -10202,16 +10003,15 @@
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
-      <c r="I93" s="9" t="inlineStr"/>
-      <c r="J93" s="9" t="inlineStr">
+      <c r="I93" s="9" t="inlineStr">
         <is>
           <t>macro_vim_visual_y</t>
         </is>
       </c>
+      <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
-      <c r="M93" s="9" t="inlineStr"/>
-      <c r="N93" s="9" t="inlineStr">
+      <c r="M93" s="9" t="inlineStr">
         <is>
           <t>macro_vim_visual_p</t>
         </is>
@@ -10255,32 +10055,31 @@
       </c>
       <c r="G94" s="7" t="inlineStr"/>
       <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
-      <c r="J94" s="7" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="K94" s="7" t="inlineStr">
+      <c r="J94" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp LS(DOWN)</t>
         </is>
       </c>
-      <c r="L94" s="7" t="inlineStr">
+      <c r="K94" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp LS(UP)</t>
         </is>
       </c>
-      <c r="M94" s="7" t="inlineStr">
+      <c r="L94" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp LS(RIGHT)</t>
         </is>
       </c>
-      <c r="N94" s="7" t="inlineStr">
+      <c r="M94" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -10314,28 +10113,27 @@
       </c>
       <c r="G95" s="9" t="inlineStr"/>
       <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LS(LEFT)</t>
+          <t>&amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LS(DOWN)</t>
+          <t>&amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="L95" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LS(UP)</t>
+          <t>&amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="N95" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -10368,7 +10166,11 @@
       </c>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
-      <c r="I96" s="9" t="inlineStr"/>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -10385,11 +10187,6 @@
         </is>
       </c>
       <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N96" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -10421,7 +10218,11 @@
       </c>
       <c r="G97" s="9" t="inlineStr"/>
       <c r="H97" s="9" t="inlineStr"/>
-      <c r="I97" s="9" t="inlineStr"/>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -10438,11 +10239,6 @@
         </is>
       </c>
       <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N97" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -10493,35 +10289,29 @@
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J98" s="7" t="inlineStr">
-        <is>
           <t>pos 26
 &amp;kp F3</t>
         </is>
       </c>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;none</t>
+        </is>
+      </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>pos 27
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>pos 28
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N98" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -10557,16 +10347,15 @@
       </c>
       <c r="G99" s="9" t="inlineStr"/>
       <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr"/>
-      <c r="J99" s="9" t="inlineStr">
+      <c r="I99" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F3</t>
         </is>
       </c>
+      <c r="J99" s="9" t="inlineStr"/>
       <c r="K99" s="9" t="inlineStr"/>
       <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="9" t="inlineStr">
+      <c r="M99" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -10617,25 +10406,29 @@
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr"/>
-      <c r="L100" s="7" t="inlineStr"/>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M100" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N100" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -10660,19 +10453,18 @@
       <c r="K101" s="9" t="inlineStr"/>
       <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
-      <c r="N101" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A91:N91"/>
-    <mergeCell ref="A55:N55"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A45:N45"/>
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A73:N73"/>
-    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A91:M91"/>
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="A64:M64"/>
+    <mergeCell ref="A73:M73"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A82:M82"/>
+    <mergeCell ref="A28:M28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -549,12 +549,11 @@
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -624,11 +623,6 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
     </row>
@@ -649,8 +643,7 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -660,64 +653,63 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp Q</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp W</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp E</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp R</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp T</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;kp Y</t>
+        </is>
+      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;kp Y</t>
+          <t>pos 6
+&amp;kp U</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>U
-&amp;kp U</t>
+          <t>pos 7
+&amp;kp I</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>I
-&amp;kp I</t>
+          <t>pos 8
+&amp;kp O</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;kp O</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;kp P</t>
         </is>
       </c>
@@ -755,28 +747,27 @@
       </c>
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>I</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>O</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -790,64 +781,63 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LEFT_CONTROL A</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp S</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp D</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp F</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp G</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp H</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;kp H</t>
+          <t>pos 16
+&amp;kp J</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;kp J</t>
+          <t>pos 17
+&amp;kp K</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;kp K</t>
+          <t>pos 18
+&amp;kp L</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;kp L</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;mt RCTRL MINUS</t>
         </is>
       </c>
@@ -885,28 +875,27 @@
       </c>
       <c r="G8" s="9" t="inlineStr"/>
       <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -945,7 +934,11 @@
       </c>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -962,11 +955,6 @@
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -980,74 +968,68 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;mt LEFT_SHIFT Z</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;kp X</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;kp C</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;kp V</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp B</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>mo上段
-&amp;mo BLUETOOTH</t>
+          <t>pos 26
+&amp;kp N</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;kp N</t>
+          <t>pos 27
+&amp;kp M</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>M
-&amp;kp M</t>
+          <t>pos 28
+&amp;kp COMMA</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>,
-&amp;kp COMMA</t>
+          <t>pos 29
+&amp;kp PERIOD</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;kp PERIOD</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;mt RIGHT_SHIFT SLASH</t>
         </is>
       </c>
@@ -1091,30 +1073,25 @@
       <c r="H11" s="9" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>,</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>,</t>
+          <t>.</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>/</t>
         </is>
@@ -1179,11 +1156,6 @@
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
           <t>RShift</t>
         </is>
       </c>
@@ -1196,64 +1168,68 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
+&amp;lt NUM_SYMBOL ENTER</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
 &amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>lt1 ENTER
-&amp;lt NUM_SYMBOL ENTER</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;mo FUNCTION</t>
+        </is>
+      </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;mo FUNCTION</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;mo FUNCTION</t>
         </is>
       </c>
@@ -1297,22 +1273,25 @@
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
+          <t>ENTER</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>ENTER</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
       <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>L6</t>
         </is>
@@ -1357,22 +1336,25 @@
       <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>〃</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr"/>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1395,8 +1377,7 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -1406,64 +1387,63 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp N1</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp N2</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp N3</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp N4</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp N5</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;kp N6</t>
+        </is>
+      </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;kp N6</t>
+          <t>pos 6
+&amp;kp N7</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>U
-&amp;kp N7</t>
+          <t>pos 7
+&amp;kp N8</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>I
-&amp;kp N8</t>
+          <t>pos 8
+&amp;kp N9</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;kp N9</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;kp N0</t>
         </is>
       </c>
@@ -1501,28 +1481,27 @@
       </c>
       <c r="G18" s="9" t="inlineStr"/>
       <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1536,64 +1515,63 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LCTRL TAB</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp GRAVE</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp LEFT_BRACKET</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp RIGHT_BRACKET</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp DELETE</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp BACKSPACE</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;kp BACKSPACE</t>
+          <t>pos 16
+&amp;kp SEMICOLON</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;kp SEMICOLON</t>
+          <t>pos 17
+&amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;kp SINGLE_QUOTE</t>
+          <t>pos 18
+&amp;kp BACKSLASH</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;kp BACKSLASH</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;trans</t>
         </is>
       </c>
@@ -1631,28 +1609,27 @@
       </c>
       <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>;</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>;</t>
+          <t>'</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>'</t>
+          <t>\</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>\</t>
-        </is>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -1691,7 +1668,11 @@
       </c>
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1708,11 +1689,6 @@
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1726,74 +1702,68 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;mt LEFT_SHIFT ESCAPE</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;none</t>
+          <t>pos 27
+&amp;kp EQUAL</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>M
-&amp;kp EQUAL</t>
+          <t>pos 28
+&amp;trans</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;trans</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;trans</t>
         </is>
       </c>
@@ -1816,10 +1786,14 @@
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="9" t="inlineStr"/>
       <c r="I23" s="9" t="inlineStr"/>
-      <c r="J23" s="9" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -1828,11 +1802,6 @@
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
-      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -1856,7 +1825,11 @@
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="9" t="inlineStr"/>
       <c r="I24" s="9" t="inlineStr"/>
-      <c r="J24" s="9" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1868,11 +1841,6 @@
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1886,64 +1854,68 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;trans</t>
+        </is>
+      </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -1977,20 +1949,19 @@
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr"/>
-      <c r="L26" s="9" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -2021,20 +1992,19 @@
       </c>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr"/>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I27" s="9" t="inlineStr"/>
       <c r="J27" s="9" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N27" s="9" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2053,8 +2023,7 @@
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -2064,64 +2033,63 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;mm_vim_w</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LC(RIGHT)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_ctrl_r</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;mm_vim_y</t>
+        </is>
+      </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;mm_vim_y</t>
+          <t>pos 6
+&amp;mm_vim_u</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>U
-&amp;mm_vim_u</t>
+          <t>pos 7
+&amp;none</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>I
-&amp;none</t>
+          <t>pos 8
+&amp;mm_vim_o</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;mm_vim_o</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;kp LC(V)</t>
         </is>
       </c>
@@ -2148,20 +2116,19 @@
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr"/>
       <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="9" t="inlineStr"/>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>⌃Z</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr"/>
+      <c r="L30" s="10" t="inlineStr">
         <is>
           <t>END
 ▸ ENTER</t>
         </is>
       </c>
-      <c r="N30" s="9" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>⌃V</t>
         </is>
@@ -2188,26 +2155,25 @@
       <c r="F31" s="9" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="9" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ⇧END
 ▸ ⌃C</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr"/>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2234,27 +2200,26 @@
       <c r="F32" s="9" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr"/>
-      <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>⇧END
 ▸ ⌃C</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr"/>
+      <c r="L32" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ENTER
 ▸ ↑</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2286,19 +2251,18 @@
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="9" t="inlineStr"/>
       <c r="I33" s="9" t="inlineStr"/>
-      <c r="J33" s="9" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>PgUp</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2312,64 +2276,63 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;mm_vim_d</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_g</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LEFT</t>
+        </is>
+      </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;kp LEFT</t>
+          <t>pos 16
+&amp;mm_vim_j</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;mm_vim_j</t>
+          <t>pos 17
+&amp;kp UP_ARROW</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;kp UP_ARROW</t>
+          <t>pos 18
+&amp;kp RIGHT</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;kp RIGHT</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -2391,28 +2354,27 @@
       <c r="F35" s="9" t="inlineStr"/>
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="9" t="inlineStr"/>
-      <c r="I35" s="9" t="inlineStr"/>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>←</t>
+        </is>
+      </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>←</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>→</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
-        <is>
-          <t>→</t>
-        </is>
-      </c>
-      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -2445,7 +2407,11 @@
       </c>
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -2462,11 +2428,6 @@
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2498,30 +2459,29 @@
       </c>
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="9" t="inlineStr"/>
-      <c r="I37" s="9" t="inlineStr"/>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>END
 ▸ DEL
 ▸ SPACE</t>
         </is>
       </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2548,7 +2508,11 @@
       <c r="F38" s="9" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="9" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -2565,11 +2529,6 @@
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2583,74 +2542,68 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;kp DELETE</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;mm_vim_v</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>mo上段
-&amp;none</t>
+          <t>pos 26
+&amp;mm_vim_n</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;mm_vim_n</t>
+          <t>pos 27
+&amp;none</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -2684,16 +2637,15 @@
       </c>
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="9" t="inlineStr"/>
-      <c r="I40" s="9" t="inlineStr"/>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
+      <c r="J40" s="9" t="inlineStr"/>
       <c r="K40" s="9" t="inlineStr"/>
       <c r="L40" s="9" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr"/>
-      <c r="N40" s="9" t="inlineStr">
+      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -2730,16 +2682,15 @@
       </c>
       <c r="G41" s="9" t="inlineStr"/>
       <c r="H41" s="9" t="inlineStr"/>
-      <c r="I41" s="9" t="inlineStr"/>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr"/>
       <c r="K41" s="9" t="inlineStr"/>
       <c r="L41" s="9" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr"/>
-      <c r="N41" s="9" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2753,64 +2704,68 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>mo2
-&amp;none</t>
+          <t>pos 37
+&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;lt VIM_NORMAL_SYM ENTER</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;trans</t>
+        </is>
+      </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="N42" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -2840,20 +2795,19 @@
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr"/>
-      <c r="I43" s="9" t="inlineStr"/>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>ENTER</t>
         </is>
       </c>
+      <c r="J43" s="9" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N43" s="9" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -2880,20 +2834,19 @@
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr"/>
-      <c r="I44" s="9" t="inlineStr"/>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
+      <c r="J44" s="9" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2912,8 +2865,7 @@
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -2923,64 +2875,63 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_shift_4</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;mm_vim_shift_6</t>
+        </is>
+      </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;mm_vim_shift_6</t>
+          <t>pos 6
+&amp;none</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N46" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;kp HOME</t>
         </is>
       </c>
@@ -3002,8 +2953,7 @@
       <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr"/>
       <c r="L47" s="9" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
-      <c r="N47" s="9" t="inlineStr">
+      <c r="M47" s="9" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
@@ -3026,16 +2976,15 @@
       <c r="F48" s="9" t="inlineStr"/>
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="9" t="inlineStr"/>
-      <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="9" t="inlineStr">
+      <c r="I48" s="9" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
+      <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr"/>
       <c r="L48" s="9" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr"/>
-      <c r="N48" s="9" t="inlineStr">
+      <c r="M48" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -3049,64 +2998,63 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LEFT</t>
+        </is>
+      </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;kp LEFT</t>
+          <t>pos 16
+&amp;none</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -3128,16 +3076,15 @@
       <c r="F50" s="9" t="inlineStr"/>
       <c r="G50" s="9" t="inlineStr"/>
       <c r="H50" s="9" t="inlineStr"/>
-      <c r="I50" s="9" t="inlineStr"/>
-      <c r="J50" s="9" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>←</t>
         </is>
       </c>
+      <c r="J50" s="9" t="inlineStr"/>
       <c r="K50" s="9" t="inlineStr"/>
       <c r="L50" s="9" t="inlineStr"/>
-      <c r="M50" s="9" t="inlineStr"/>
-      <c r="N50" s="9" t="inlineStr">
+      <c r="M50" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -3151,74 +3098,68 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N51" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -3244,8 +3185,7 @@
       <c r="J52" s="9" t="inlineStr"/>
       <c r="K52" s="9" t="inlineStr"/>
       <c r="L52" s="9" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr"/>
-      <c r="N52" s="9" t="inlineStr">
+      <c r="M52" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -3259,64 +3199,68 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;trans</t>
+        </is>
+      </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="N53" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -3345,13 +3289,12 @@
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
-      <c r="L54" s="9" t="inlineStr"/>
-      <c r="M54" s="9" t="inlineStr">
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N54" s="9" t="inlineStr"/>
+      <c r="M54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -3370,8 +3313,7 @@
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -3381,64 +3323,63 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N56" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -3461,7 +3402,6 @@
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr"/>
-      <c r="N57" s="9" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -3471,64 +3411,63 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;none</t>
+          <t>pos 17
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;mo MOUSE_SCROLL</t>
+          <t>pos 18
+&amp;none</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N58" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -3548,14 +3487,13 @@
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr"/>
       <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr"/>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
+      <c r="L59" s="9" t="inlineStr"/>
       <c r="M59" s="9" t="inlineStr"/>
-      <c r="N59" s="9" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
@@ -3565,74 +3503,68 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -3655,7 +3587,6 @@
       <c r="K61" s="9" t="inlineStr"/>
       <c r="L61" s="9" t="inlineStr"/>
       <c r="M61" s="9" t="inlineStr"/>
-      <c r="N61" s="9" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
@@ -3665,64 +3596,68 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N62" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -3745,7 +3680,6 @@
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -3764,8 +3698,7 @@
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
@@ -3775,64 +3708,63 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -3855,7 +3787,6 @@
       <c r="K66" s="9" t="inlineStr"/>
       <c r="L66" s="9" t="inlineStr"/>
       <c r="M66" s="9" t="inlineStr"/>
-      <c r="N66" s="9" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -3865,64 +3796,63 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;none</t>
+          <t>pos 16
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;mkp MB1</t>
+          <t>pos 17
+&amp;none</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;none</t>
+          <t>pos 18
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;mkp MB2</t>
-        </is>
-      </c>
-      <c r="N67" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -3945,7 +3875,6 @@
       <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="9" t="inlineStr"/>
       <c r="M68" s="9" t="inlineStr"/>
-      <c r="N68" s="9" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
@@ -3955,74 +3884,68 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;none</t>
+          <t>pos 27
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>M
-&amp;mkp MB4</t>
+          <t>pos 28
+&amp;none</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>,
-&amp;none</t>
+          <t>pos 29
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="N69" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -4045,7 +3968,6 @@
       <c r="K70" s="9" t="inlineStr"/>
       <c r="L70" s="9" t="inlineStr"/>
       <c r="M70" s="9" t="inlineStr"/>
-      <c r="N70" s="9" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
@@ -4055,64 +3977,68 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr"/>
-      <c r="L71" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N71" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4135,7 +4061,6 @@
       <c r="K72" s="9" t="inlineStr"/>
       <c r="L72" s="9" t="inlineStr"/>
       <c r="M72" s="9" t="inlineStr"/>
-      <c r="N72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -4154,8 +4079,7 @@
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
@@ -4165,64 +4089,63 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp F1</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp F2</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp F3</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp F4</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp F5</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;kp F6</t>
+        </is>
+      </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;kp F6</t>
+          <t>pos 6
+&amp;kp F7</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>U
-&amp;kp F7</t>
+          <t>pos 7
+&amp;kp F8</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>I
-&amp;kp F8</t>
+          <t>pos 8
+&amp;kp F9</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;kp F9</t>
-        </is>
-      </c>
-      <c r="N74" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;kp F10</t>
         </is>
       </c>
@@ -4260,28 +4183,27 @@
       </c>
       <c r="G75" s="9" t="inlineStr"/>
       <c r="H75" s="9" t="inlineStr"/>
-      <c r="I75" s="9" t="inlineStr"/>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>F9</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
-        <is>
-          <t>F9</t>
-        </is>
-      </c>
-      <c r="N75" s="9" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
@@ -4295,64 +4217,63 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr"/>
       <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr"/>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;none</t>
+          <t>pos 18
+&amp;sys_reset</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="N76" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -4375,7 +4296,6 @@
       <c r="K77" s="9" t="inlineStr"/>
       <c r="L77" s="9" t="inlineStr"/>
       <c r="M77" s="9" t="inlineStr"/>
-      <c r="N77" s="9" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
@@ -4385,74 +4305,68 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;bootloader</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>mo上段
-&amp;none</t>
+          <t>pos 26
+&amp;bootloader</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;bootloader</t>
+          <t>pos 27
+&amp;none</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N78" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -4475,7 +4389,6 @@
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr"/>
       <c r="M79" s="9" t="inlineStr"/>
-      <c r="N79" s="9" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
@@ -4485,64 +4398,68 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr"/>
-      <c r="L80" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N80" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4565,7 +4482,6 @@
       <c r="K81" s="9" t="inlineStr"/>
       <c r="L81" s="9" t="inlineStr"/>
       <c r="M81" s="9" t="inlineStr"/>
-      <c r="N81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -4584,8 +4500,7 @@
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -4595,64 +4510,63 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;bt BT_SEL 0</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;bt BT_SEL 1</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;bt BT_SEL 2</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;bt BT_SEL 3</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;bt BT_SEL 4</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr"/>
       <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;none</t>
+          <t>pos 6
+&amp;out OUT_USB</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>U
-&amp;out OUT_USB</t>
+          <t>pos 7
+&amp;none</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N83" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -4675,7 +4589,6 @@
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
-      <c r="N84" s="9" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
@@ -4685,64 +4598,63 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr"/>
       <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N85" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -4765,7 +4677,6 @@
       <c r="K86" s="9" t="inlineStr"/>
       <c r="L86" s="9" t="inlineStr"/>
       <c r="M86" s="9" t="inlineStr"/>
-      <c r="N86" s="9" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
@@ -4775,74 +4686,68 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;bt BT_CLR</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;out OUT_BLE</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N87" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -4865,7 +4770,6 @@
       <c r="K88" s="9" t="inlineStr"/>
       <c r="L88" s="9" t="inlineStr"/>
       <c r="M88" s="9" t="inlineStr"/>
-      <c r="N88" s="9" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
@@ -4875,64 +4779,68 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr"/>
-      <c r="L89" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N89" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4955,7 +4863,6 @@
       <c r="K90" s="9" t="inlineStr"/>
       <c r="L90" s="9" t="inlineStr"/>
       <c r="M90" s="9" t="inlineStr"/>
-      <c r="N90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -4974,8 +4881,7 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="n"/>
       <c r="L91" s="4" t="n"/>
-      <c r="M91" s="4" t="n"/>
-      <c r="N91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
@@ -4985,64 +4891,63 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr"/>
       <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;macro_vim_visual_y</t>
+        </is>
+      </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;macro_vim_visual_y</t>
+          <t>pos 6
+&amp;none</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N92" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;macro_vim_visual_p</t>
         </is>
       </c>
@@ -5068,8 +4973,7 @@
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
-      <c r="I93" s="9" t="inlineStr"/>
-      <c r="J93" s="10" t="inlineStr">
+      <c r="I93" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -5078,10 +4982,10 @@
 ▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
+      <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
-      <c r="M93" s="9" t="inlineStr"/>
-      <c r="N93" s="10" t="inlineStr">
+      <c r="M93" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -5098,64 +5002,63 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_visual_g</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr"/>
       <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;kp LS(LEFT)</t>
+          <t>pos 16
+&amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;kp LS(DOWN)</t>
+          <t>pos 17
+&amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;kp LS(UP)</t>
+          <t>pos 18
+&amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -5184,28 +5087,27 @@
       <c r="F95" s="9" t="inlineStr"/>
       <c r="G95" s="9" t="inlineStr"/>
       <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>⇧←</t>
+        </is>
+      </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>⇧←</t>
+          <t>⇧↓</t>
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr">
         <is>
-          <t>⇧↓</t>
+          <t>⇧↑</t>
         </is>
       </c>
       <c r="L95" s="9" t="inlineStr">
         <is>
-          <t>⇧↑</t>
+          <t>⇧→</t>
         </is>
       </c>
       <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>⇧→</t>
-        </is>
-      </c>
-      <c r="N95" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -5236,7 +5138,11 @@
       </c>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
-      <c r="I96" s="9" t="inlineStr"/>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -5253,11 +5159,6 @@
         </is>
       </c>
       <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N96" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -5288,7 +5189,11 @@
       </c>
       <c r="G97" s="9" t="inlineStr"/>
       <c r="H97" s="9" t="inlineStr"/>
-      <c r="I97" s="9" t="inlineStr"/>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -5305,11 +5210,6 @@
         </is>
       </c>
       <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N97" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -5323,74 +5223,68 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>mo上段
-&amp;none</t>
+          <t>pos 26
+&amp;kp F3</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;kp F3</t>
+          <t>pos 27
+&amp;none</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N98" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -5430,16 +5324,15 @@
       </c>
       <c r="G99" s="9" t="inlineStr"/>
       <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr"/>
-      <c r="J99" s="9" t="inlineStr">
+      <c r="I99" s="9" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
+      <c r="J99" s="9" t="inlineStr"/>
       <c r="K99" s="9" t="inlineStr"/>
       <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="9" t="inlineStr">
+      <c r="M99" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -5453,64 +5346,68 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr"/>
-      <c r="L100" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N100" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -5533,19 +5430,18 @@
       <c r="K101" s="9" t="inlineStr"/>
       <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
-      <c r="N101" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A91:N91"/>
-    <mergeCell ref="A55:N55"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A45:N45"/>
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A73:N73"/>
-    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A91:M91"/>
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="A64:M64"/>
+    <mergeCell ref="A73:M73"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A82:M82"/>
+    <mergeCell ref="A28:M28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5557,7 +5453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5568,12 +5464,11 @@
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5643,11 +5538,6 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
     </row>
@@ -5668,8 +5558,7 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -5679,64 +5568,63 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp Q</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp W</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp E</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp R</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp T</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;kp Y</t>
+        </is>
+      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;kp Y</t>
+          <t>pos 6
+&amp;kp U</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>U
-&amp;kp U</t>
+          <t>pos 7
+&amp;kp I</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>I
-&amp;kp I</t>
+          <t>pos 8
+&amp;kp O</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;kp O</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;kp P</t>
         </is>
       </c>
@@ -5774,28 +5662,27 @@
       </c>
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp Y</t>
+        </is>
+      </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp Y</t>
+          <t>&amp;kp U</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp U</t>
+          <t>&amp;kp I</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp I</t>
+          <t>&amp;kp O</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp O</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp P</t>
         </is>
@@ -5809,64 +5696,63 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LEFT_CONTROL A</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp S</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp D</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp F</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp G</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp H</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;kp H</t>
+          <t>pos 16
+&amp;kp J</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;kp J</t>
+          <t>pos 17
+&amp;kp K</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;kp K</t>
+          <t>pos 18
+&amp;kp L</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;kp L</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;mt RCTRL MINUS</t>
         </is>
       </c>
@@ -5904,28 +5790,27 @@
       </c>
       <c r="G8" s="9" t="inlineStr"/>
       <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp H</t>
+        </is>
+      </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp H</t>
+          <t>&amp;kp J</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp J</t>
+          <t>&amp;kp K</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp K</t>
+          <t>&amp;kp L</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp L</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>&amp;mt RCTRL MINUS</t>
         </is>
@@ -5964,7 +5849,11 @@
       </c>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -5981,11 +5870,6 @@
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>&amp;mt RCTRL MINUS</t>
         </is>
@@ -5999,74 +5883,68 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;mt LEFT_SHIFT Z</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;kp X</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;kp C</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;kp V</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp B</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>mo上段
-&amp;mo BLUETOOTH</t>
+          <t>pos 26
+&amp;kp N</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;kp N</t>
+          <t>pos 27
+&amp;kp M</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>M
-&amp;kp M</t>
+          <t>pos 28
+&amp;kp COMMA</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>,
-&amp;kp COMMA</t>
+          <t>pos 29
+&amp;kp PERIOD</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;kp PERIOD</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;mt RIGHT_SHIFT SLASH</t>
         </is>
       </c>
@@ -6110,30 +5988,25 @@
       <c r="H11" s="9" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo BLUETOOTH</t>
+          <t>&amp;kp N</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp N</t>
+          <t>&amp;kp M</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp M</t>
+          <t>&amp;kp COMMA</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp COMMA</t>
+          <t>&amp;kp PERIOD</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp PERIOD</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>&amp;mt RIGHT_SHIFT SLASH</t>
         </is>
@@ -6198,11 +6071,6 @@
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
           <t>&amp;mt RIGHT_SHIFT SLASH</t>
         </is>
       </c>
@@ -6215,64 +6083,68 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
+&amp;lt NUM_SYMBOL ENTER</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
 &amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>lt1 ENTER
-&amp;lt NUM_SYMBOL ENTER</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;mo FUNCTION</t>
+        </is>
+      </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;mo FUNCTION</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;mo FUNCTION</t>
         </is>
       </c>
@@ -6316,22 +6188,25 @@
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
+          <t>&amp;lt NUM_SYMBOL ENTER</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
           <t>&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;lt NUM_SYMBOL ENTER</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo FUNCTION</t>
+        </is>
+      </c>
       <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo FUNCTION</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>&amp;mo FUNCTION</t>
         </is>
@@ -6376,22 +6251,25 @@
       <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>〃</t>
+          <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt NUM_SYMBOL ENTER</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr"/>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -6414,8 +6292,7 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -6425,64 +6302,63 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp N1</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp N2</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp N3</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp N4</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp N5</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;kp N6</t>
+        </is>
+      </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;kp N6</t>
+          <t>pos 6
+&amp;kp N7</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>U
-&amp;kp N7</t>
+          <t>pos 7
+&amp;kp N8</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>I
-&amp;kp N8</t>
+          <t>pos 8
+&amp;kp N9</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;kp N9</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;kp N0</t>
         </is>
       </c>
@@ -6520,28 +6396,27 @@
       </c>
       <c r="G18" s="9" t="inlineStr"/>
       <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp N6</t>
+        </is>
+      </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp N6</t>
+          <t>&amp;kp N7</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp N7</t>
+          <t>&amp;kp N8</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp N8</t>
+          <t>&amp;kp N9</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp N9</t>
-        </is>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N0</t>
         </is>
@@ -6555,64 +6430,63 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LCTRL TAB</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp GRAVE</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp LEFT_BRACKET</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp RIGHT_BRACKET</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp DELETE</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp BACKSPACE</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;kp BACKSPACE</t>
+          <t>pos 16
+&amp;kp SEMICOLON</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;kp SEMICOLON</t>
+          <t>pos 17
+&amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;kp SINGLE_QUOTE</t>
+          <t>pos 18
+&amp;kp BACKSLASH</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;kp BACKSLASH</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;trans</t>
         </is>
       </c>
@@ -6650,28 +6524,27 @@
       </c>
       <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp BACKSPACE</t>
+        </is>
+      </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp BACKSPACE</t>
+          <t>&amp;kp SEMICOLON</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp SEMICOLON</t>
+          <t>&amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp SINGLE_QUOTE</t>
+          <t>&amp;kp BACKSLASH</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp BACKSLASH</t>
-        </is>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -6710,7 +6583,11 @@
       </c>
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6727,11 +6604,6 @@
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -6745,74 +6617,68 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;mt LEFT_SHIFT ESCAPE</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;none</t>
+          <t>pos 27
+&amp;kp EQUAL</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>M
-&amp;kp EQUAL</t>
+          <t>pos 28
+&amp;trans</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;trans</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;trans</t>
         </is>
       </c>
@@ -6835,10 +6701,14 @@
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="9" t="inlineStr"/>
       <c r="I23" s="9" t="inlineStr"/>
-      <c r="J23" s="9" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp EQUAL</t>
+        </is>
+      </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp EQUAL</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -6847,11 +6717,6 @@
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
-      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -6875,7 +6740,11 @@
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="9" t="inlineStr"/>
       <c r="I24" s="9" t="inlineStr"/>
-      <c r="J24" s="9" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6887,11 +6756,6 @@
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -6905,64 +6769,68 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;trans</t>
+        </is>
+      </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -6996,20 +6864,19 @@
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr"/>
-      <c r="L26" s="9" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -7040,20 +6907,19 @@
       </c>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr"/>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I27" s="9" t="inlineStr"/>
       <c r="J27" s="9" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N27" s="9" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -7072,8 +6938,7 @@
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -7083,64 +6948,63 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;mm_vim_w</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LC(RIGHT)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_ctrl_r</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;mm_vim_y</t>
+        </is>
+      </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;mm_vim_y</t>
+          <t>pos 6
+&amp;mm_vim_u</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>U
-&amp;mm_vim_u</t>
+          <t>pos 7
+&amp;none</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>I
-&amp;none</t>
+          <t>pos 8
+&amp;mm_vim_o</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;mm_vim_o</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;kp LC(V)</t>
         </is>
       </c>
@@ -7172,28 +7036,27 @@
       <c r="F30" s="9" t="inlineStr"/>
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr"/>
-      <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[0]
 ▸ td_vim_y[0]
 ▸ &amp;none</t>
         </is>
       </c>
-      <c r="K30" s="10" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_u[0]
 ▸ &amp;kp LC(Z)</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr"/>
+      <c r="L30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_o[0]
 ▸ macro_vim_o</t>
         </is>
       </c>
-      <c r="N30" s="9" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LC(V)</t>
         </is>
@@ -7220,26 +7083,25 @@
       <c r="F31" s="9" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="9" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[0]
 ▸ td_vim_y[1]
 ▸ macro_vim_yy</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr"/>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7266,26 +7128,25 @@
       <c r="F32" s="9" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr"/>
-      <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[1]
 ▸ macro_vim_shift_y</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr"/>
+      <c r="L32" s="10" t="inlineStr">
         <is>
           <t>mm_vim_o[1]
 ▸ macro_vim_shift_o</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7319,20 +7180,19 @@
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="9" t="inlineStr"/>
       <c r="I33" s="9" t="inlineStr"/>
-      <c r="J33" s="9" t="inlineStr"/>
-      <c r="K33" s="10" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>mm_vim_u[1]
 ▸ &amp;kp PAGE_UP</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7346,64 +7206,63 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;mm_vim_d</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_g</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LEFT</t>
+        </is>
+      </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;kp LEFT</t>
+          <t>pos 16
+&amp;mm_vim_j</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;mm_vim_j</t>
+          <t>pos 17
+&amp;kp UP_ARROW</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;kp UP_ARROW</t>
+          <t>pos 18
+&amp;kp RIGHT</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;kp RIGHT</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -7438,29 +7297,28 @@
       </c>
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="9" t="inlineStr"/>
-      <c r="I35" s="9" t="inlineStr"/>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LEFT</t>
         </is>
       </c>
-      <c r="K35" s="10" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>mm_vim_j[0]
 ▸ &amp;kp DOWN</t>
         </is>
       </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp UP_ARROW</t>
+        </is>
+      </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp UP_ARROW</t>
+          <t>&amp;kp RIGHT</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RIGHT</t>
-        </is>
-      </c>
-      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -7496,7 +7354,11 @@
       </c>
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -7513,11 +7375,6 @@
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7551,29 +7408,28 @@
       </c>
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="9" t="inlineStr"/>
-      <c r="I37" s="9" t="inlineStr"/>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>mm_vim_j[1]
 ▸ macro_vim_join</t>
         </is>
       </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7601,7 +7457,11 @@
       <c r="F38" s="9" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="9" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -7618,11 +7478,6 @@
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7636,74 +7491,68 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;kp DELETE</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;mm_vim_v</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>mo上段
-&amp;none</t>
+          <t>pos 26
+&amp;mm_vim_n</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;mm_vim_n</t>
+          <t>pos 27
+&amp;none</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -7738,17 +7587,16 @@
       </c>
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="9" t="inlineStr"/>
-      <c r="I40" s="9" t="inlineStr"/>
-      <c r="J40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>mm_vim_n[0]
 ▸ &amp;kp F3</t>
         </is>
       </c>
+      <c r="J40" s="9" t="inlineStr"/>
       <c r="K40" s="9" t="inlineStr"/>
       <c r="L40" s="9" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr"/>
-      <c r="N40" s="9" t="inlineStr">
+      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -7784,16 +7632,15 @@
       </c>
       <c r="G41" s="9" t="inlineStr"/>
       <c r="H41" s="9" t="inlineStr"/>
-      <c r="I41" s="9" t="inlineStr"/>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr"/>
       <c r="K41" s="9" t="inlineStr"/>
       <c r="L41" s="9" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr"/>
-      <c r="N41" s="9" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7807,64 +7654,68 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>mo2
-&amp;none</t>
+          <t>pos 37
+&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;lt VIM_NORMAL_SYM ENTER</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;trans</t>
+        </is>
+      </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="N42" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -7894,20 +7745,19 @@
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr"/>
-      <c r="I43" s="9" t="inlineStr"/>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
+      <c r="J43" s="9" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N43" s="9" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -7934,20 +7784,19 @@
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr"/>
-      <c r="I44" s="9" t="inlineStr"/>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
+      <c r="J44" s="9" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -7966,8 +7815,7 @@
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -7977,64 +7825,63 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_shift_4</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;mm_vim_shift_6</t>
+        </is>
+      </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;mm_vim_shift_6</t>
+          <t>pos 6
+&amp;none</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N46" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;kp HOME</t>
         </is>
       </c>
@@ -8057,17 +7904,16 @@
       <c r="F47" s="9" t="inlineStr"/>
       <c r="G47" s="9" t="inlineStr"/>
       <c r="H47" s="9" t="inlineStr"/>
-      <c r="I47" s="9" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_6[0]
 ▸ &amp;none</t>
         </is>
       </c>
+      <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr"/>
       <c r="L47" s="9" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
-      <c r="N47" s="9" t="inlineStr">
+      <c r="M47" s="9" t="inlineStr">
         <is>
           <t>&amp;kp HOME</t>
         </is>
@@ -8091,17 +7937,16 @@
       <c r="F48" s="9" t="inlineStr"/>
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="9" t="inlineStr"/>
-      <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_6[1]
 ▸ &amp;kp HOME</t>
         </is>
       </c>
+      <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr"/>
       <c r="L48" s="9" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr"/>
-      <c r="N48" s="9" t="inlineStr">
+      <c r="M48" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -8115,64 +7960,63 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LEFT</t>
+        </is>
+      </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;kp LEFT</t>
+          <t>pos 16
+&amp;none</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -8194,16 +8038,15 @@
       <c r="F50" s="9" t="inlineStr"/>
       <c r="G50" s="9" t="inlineStr"/>
       <c r="H50" s="9" t="inlineStr"/>
-      <c r="I50" s="9" t="inlineStr"/>
-      <c r="J50" s="9" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LEFT</t>
         </is>
       </c>
+      <c r="J50" s="9" t="inlineStr"/>
       <c r="K50" s="9" t="inlineStr"/>
       <c r="L50" s="9" t="inlineStr"/>
-      <c r="M50" s="9" t="inlineStr"/>
-      <c r="N50" s="9" t="inlineStr">
+      <c r="M50" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -8217,74 +8060,68 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N51" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -8310,8 +8147,7 @@
       <c r="J52" s="9" t="inlineStr"/>
       <c r="K52" s="9" t="inlineStr"/>
       <c r="L52" s="9" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr"/>
-      <c r="N52" s="9" t="inlineStr">
+      <c r="M52" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -8325,64 +8161,68 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;trans</t>
+        </is>
+      </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="N53" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -8411,13 +8251,12 @@
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
-      <c r="L54" s="9" t="inlineStr"/>
-      <c r="M54" s="9" t="inlineStr">
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="N54" s="9" t="inlineStr"/>
+      <c r="M54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -8436,8 +8275,7 @@
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -8447,64 +8285,63 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N56" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -8527,7 +8364,6 @@
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr"/>
-      <c r="N57" s="9" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -8537,64 +8373,63 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;none</t>
+          <t>pos 17
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;mo MOUSE_SCROLL</t>
+          <t>pos 18
+&amp;none</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N58" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -8614,14 +8449,13 @@
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr"/>
       <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr"/>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
+      <c r="L59" s="9" t="inlineStr"/>
       <c r="M59" s="9" t="inlineStr"/>
-      <c r="N59" s="9" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
@@ -8631,74 +8465,68 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -8721,7 +8549,6 @@
       <c r="K61" s="9" t="inlineStr"/>
       <c r="L61" s="9" t="inlineStr"/>
       <c r="M61" s="9" t="inlineStr"/>
-      <c r="N61" s="9" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
@@ -8731,64 +8558,68 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N62" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -8811,7 +8642,6 @@
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -8830,8 +8660,7 @@
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
@@ -8841,64 +8670,63 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -8921,7 +8749,6 @@
       <c r="K66" s="9" t="inlineStr"/>
       <c r="L66" s="9" t="inlineStr"/>
       <c r="M66" s="9" t="inlineStr"/>
-      <c r="N66" s="9" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -8931,64 +8758,63 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;none</t>
+          <t>pos 16
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;mkp MB1</t>
+          <t>pos 17
+&amp;none</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;none</t>
+          <t>pos 18
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;mkp MB2</t>
-        </is>
-      </c>
-      <c r="N67" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -9007,19 +8833,18 @@
       <c r="G68" s="9" t="inlineStr"/>
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
-      <c r="J68" s="9" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr">
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB1</t>
         </is>
       </c>
-      <c r="L68" s="9" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr">
+      <c r="K68" s="9" t="inlineStr"/>
+      <c r="L68" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB2</t>
         </is>
       </c>
-      <c r="N68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
@@ -9029,74 +8854,68 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;none</t>
+          <t>pos 27
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>M
-&amp;mkp MB4</t>
+          <t>pos 28
+&amp;none</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>,
-&amp;none</t>
+          <t>pos 29
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="N69" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -9115,19 +8934,18 @@
       <c r="G70" s="9" t="inlineStr"/>
       <c r="H70" s="9" t="inlineStr"/>
       <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
-      <c r="K70" s="9" t="inlineStr">
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB4</t>
         </is>
       </c>
-      <c r="L70" s="9" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr">
+      <c r="K70" s="9" t="inlineStr"/>
+      <c r="L70" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB5</t>
         </is>
       </c>
-      <c r="N70" s="9" t="inlineStr"/>
+      <c r="M70" s="9" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
@@ -9137,64 +8955,68 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr"/>
-      <c r="L71" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N71" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -9217,7 +9039,6 @@
       <c r="K72" s="9" t="inlineStr"/>
       <c r="L72" s="9" t="inlineStr"/>
       <c r="M72" s="9" t="inlineStr"/>
-      <c r="N72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -9236,8 +9057,7 @@
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
@@ -9247,64 +9067,63 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp F1</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp F2</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp F3</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp F4</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp F5</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;kp F6</t>
+        </is>
+      </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;kp F6</t>
+          <t>pos 6
+&amp;kp F7</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>U
-&amp;kp F7</t>
+          <t>pos 7
+&amp;kp F8</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>I
-&amp;kp F8</t>
+          <t>pos 8
+&amp;kp F9</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;kp F9</t>
-        </is>
-      </c>
-      <c r="N74" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;kp F10</t>
         </is>
       </c>
@@ -9342,28 +9161,27 @@
       </c>
       <c r="G75" s="9" t="inlineStr"/>
       <c r="H75" s="9" t="inlineStr"/>
-      <c r="I75" s="9" t="inlineStr"/>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F6</t>
+        </is>
+      </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp F6</t>
+          <t>&amp;kp F7</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp F7</t>
+          <t>&amp;kp F8</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp F8</t>
+          <t>&amp;kp F9</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F9</t>
-        </is>
-      </c>
-      <c r="N75" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F10</t>
         </is>
@@ -9377,64 +9195,63 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr"/>
       <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr"/>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;none</t>
+          <t>pos 18
+&amp;sys_reset</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="N76" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -9459,13 +9276,12 @@
       <c r="I77" s="9" t="inlineStr"/>
       <c r="J77" s="9" t="inlineStr"/>
       <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr">
+      <c r="L77" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="N77" s="9" t="inlineStr"/>
+      <c r="M77" s="9" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
@@ -9475,74 +9291,68 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;bootloader</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>mo上段
-&amp;none</t>
+          <t>pos 26
+&amp;bootloader</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;bootloader</t>
+          <t>pos 27
+&amp;none</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N78" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -9564,16 +9374,15 @@
       </c>
       <c r="G79" s="9" t="inlineStr"/>
       <c r="H79" s="9" t="inlineStr"/>
-      <c r="I79" s="9" t="inlineStr"/>
-      <c r="J79" s="9" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t>&amp;bootloader</t>
         </is>
       </c>
+      <c r="J79" s="9" t="inlineStr"/>
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr"/>
       <c r="M79" s="9" t="inlineStr"/>
-      <c r="N79" s="9" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
@@ -9583,64 +9392,68 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr"/>
-      <c r="L80" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N80" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -9663,7 +9476,6 @@
       <c r="K81" s="9" t="inlineStr"/>
       <c r="L81" s="9" t="inlineStr"/>
       <c r="M81" s="9" t="inlineStr"/>
-      <c r="N81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -9682,8 +9494,7 @@
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -9693,64 +9504,63 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;bt BT_SEL 0</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;bt BT_SEL 1</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;bt BT_SEL 2</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;bt BT_SEL 3</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;bt BT_SEL 4</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr"/>
       <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;none</t>
+          <t>pos 6
+&amp;out OUT_USB</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>U
-&amp;out OUT_USB</t>
+          <t>pos 7
+&amp;none</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N83" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -9789,15 +9599,14 @@
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
-      <c r="J84" s="9" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr">
+      <c r="J84" s="9" t="inlineStr">
         <is>
           <t>&amp;out OUT_USB</t>
         </is>
       </c>
+      <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
-      <c r="N84" s="9" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
@@ -9807,64 +9616,63 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr"/>
       <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N85" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
@@ -9891,7 +9699,6 @@
       <c r="K86" s="9" t="inlineStr"/>
       <c r="L86" s="9" t="inlineStr"/>
       <c r="M86" s="9" t="inlineStr"/>
-      <c r="N86" s="9" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
@@ -9901,74 +9708,68 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;bt BT_CLR</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;out OUT_BLE</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>mo上段
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N87" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
@@ -9999,7 +9800,6 @@
       <c r="K88" s="9" t="inlineStr"/>
       <c r="L88" s="9" t="inlineStr"/>
       <c r="M88" s="9" t="inlineStr"/>
-      <c r="N88" s="9" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
@@ -10009,64 +9809,68 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr"/>
-      <c r="L89" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N89" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -10089,7 +9893,6 @@
       <c r="K90" s="9" t="inlineStr"/>
       <c r="L90" s="9" t="inlineStr"/>
       <c r="M90" s="9" t="inlineStr"/>
-      <c r="N90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -10108,8 +9911,7 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="n"/>
       <c r="L91" s="4" t="n"/>
-      <c r="M91" s="4" t="n"/>
-      <c r="N91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
@@ -10119,64 +9921,63 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr"/>
       <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;macro_vim_visual_y</t>
+        </is>
+      </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>Y
-&amp;macro_vim_visual_y</t>
+          <t>pos 6
+&amp;none</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>O
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N92" s="7" t="inlineStr">
-        <is>
-          <t>P
+          <t>pos 9
 &amp;macro_vim_visual_p</t>
         </is>
       </c>
@@ -10202,16 +10003,15 @@
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
-      <c r="I93" s="9" t="inlineStr"/>
-      <c r="J93" s="9" t="inlineStr">
+      <c r="I93" s="9" t="inlineStr">
         <is>
           <t>macro_vim_visual_y</t>
         </is>
       </c>
+      <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
-      <c r="M93" s="9" t="inlineStr"/>
-      <c r="N93" s="9" t="inlineStr">
+      <c r="M93" s="9" t="inlineStr">
         <is>
           <t>macro_vim_visual_p</t>
         </is>
@@ -10225,64 +10025,63 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_visual_g</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr"/>
       <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>H
-&amp;kp LS(LEFT)</t>
+          <t>pos 16
+&amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>J
-&amp;kp LS(DOWN)</t>
+          <t>pos 17
+&amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>K
-&amp;kp LS(UP)</t>
+          <t>pos 18
+&amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>L
-&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>-
+          <t>pos 19
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -10314,28 +10113,27 @@
       </c>
       <c r="G95" s="9" t="inlineStr"/>
       <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LS(LEFT)</t>
+          <t>&amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LS(DOWN)</t>
+          <t>&amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="L95" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LS(UP)</t>
+          <t>&amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="N95" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -10368,7 +10166,11 @@
       </c>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
-      <c r="I96" s="9" t="inlineStr"/>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -10385,11 +10187,6 @@
         </is>
       </c>
       <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N96" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -10421,7 +10218,11 @@
       </c>
       <c r="G97" s="9" t="inlineStr"/>
       <c r="H97" s="9" t="inlineStr"/>
-      <c r="I97" s="9" t="inlineStr"/>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -10438,11 +10239,6 @@
         </is>
       </c>
       <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N97" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -10456,74 +10252,68 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 20
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 21
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 23
 &amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 24
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>mo中央
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>mo上段
-&amp;none</t>
+          <t>pos 26
+&amp;kp F3</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>N
-&amp;kp F3</t>
+          <t>pos 27
+&amp;none</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>.
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N98" s="7" t="inlineStr">
-        <is>
-          <t>/
+          <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -10557,16 +10347,15 @@
       </c>
       <c r="G99" s="9" t="inlineStr"/>
       <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr"/>
-      <c r="J99" s="9" t="inlineStr">
+      <c r="I99" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F3</t>
         </is>
       </c>
+      <c r="J99" s="9" t="inlineStr"/>
       <c r="K99" s="9" t="inlineStr"/>
       <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="9" t="inlineStr">
+      <c r="M99" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -10580,64 +10369,68 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>mo2
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr"/>
-      <c r="L100" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R)
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N100" s="7" t="inlineStr">
-        <is>
-          <t>mo6 (R outer)
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -10660,19 +10453,18 @@
       <c r="K101" s="9" t="inlineStr"/>
       <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
-      <c r="N101" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A91:N91"/>
-    <mergeCell ref="A55:N55"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A45:N45"/>
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A73:N73"/>
-    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A91:M91"/>
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="A64:M64"/>
+    <mergeCell ref="A73:M73"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A82:M82"/>
+    <mergeCell ref="A28:M28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -3871,9 +3871,17 @@
       <c r="G68" s="9" t="inlineStr"/>
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
-      <c r="J68" s="9" t="inlineStr"/>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="K68" s="9" t="inlineStr"/>
-      <c r="L68" s="9" t="inlineStr"/>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
       <c r="M68" s="9" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
@@ -3964,9 +3972,17 @@
       <c r="G70" s="9" t="inlineStr"/>
       <c r="H70" s="9" t="inlineStr"/>
       <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="K70" s="9" t="inlineStr"/>
-      <c r="L70" s="9" t="inlineStr"/>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
       <c r="M70" s="9" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
@@ -4577,15 +4593,39 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr"/>
-      <c r="C84" s="9" t="inlineStr"/>
-      <c r="D84" s="9" t="inlineStr"/>
-      <c r="E84" s="9" t="inlineStr"/>
-      <c r="F84" s="9" t="inlineStr"/>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>BT0</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>BT1</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>BT2</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>BT3</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>BT4</t>
+        </is>
+      </c>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
-      <c r="J84" s="9" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>USB出力</t>
+        </is>
+      </c>
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
@@ -4665,7 +4705,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr"/>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>BT全解除</t>
+        </is>
+      </c>
       <c r="C86" s="9" t="inlineStr"/>
       <c r="D86" s="9" t="inlineStr"/>
       <c r="E86" s="9" t="inlineStr"/>
@@ -4760,9 +4804,17 @@
       </c>
       <c r="B88" s="9" t="inlineStr"/>
       <c r="C88" s="9" t="inlineStr"/>
-      <c r="D88" s="9" t="inlineStr"/>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>BT解除</t>
+        </is>
+      </c>
       <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr"/>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>BLE出力</t>
+        </is>
+      </c>
       <c r="G88" s="9" t="inlineStr"/>
       <c r="H88" s="9" t="inlineStr"/>
       <c r="I88" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4301,7 +4301,11 @@
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr"/>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
       <c r="D77" s="9" t="inlineStr"/>
       <c r="E77" s="9" t="inlineStr"/>
       <c r="F77" s="9" t="inlineStr"/>
@@ -4310,7 +4314,11 @@
       <c r="I77" s="9" t="inlineStr"/>
       <c r="J77" s="9" t="inlineStr"/>
       <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
       <c r="M77" s="9" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
@@ -4397,10 +4405,18 @@
       <c r="C79" s="9" t="inlineStr"/>
       <c r="D79" s="9" t="inlineStr"/>
       <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr"/>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>ブートローダ</t>
+        </is>
+      </c>
       <c r="G79" s="9" t="inlineStr"/>
       <c r="H79" s="9" t="inlineStr"/>
-      <c r="I79" s="9" t="inlineStr"/>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>ブートローダ</t>
+        </is>
+      </c>
       <c r="J79" s="9" t="inlineStr"/>
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -3871,9 +3871,17 @@
       <c r="G68" s="9" t="inlineStr"/>
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
-      <c r="J68" s="9" t="inlineStr"/>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="K68" s="9" t="inlineStr"/>
-      <c r="L68" s="9" t="inlineStr"/>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
       <c r="M68" s="9" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
@@ -3964,9 +3972,17 @@
       <c r="G70" s="9" t="inlineStr"/>
       <c r="H70" s="9" t="inlineStr"/>
       <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="K70" s="9" t="inlineStr"/>
-      <c r="L70" s="9" t="inlineStr"/>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
       <c r="M70" s="9" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
@@ -4285,7 +4301,11 @@
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr"/>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
       <c r="D77" s="9" t="inlineStr"/>
       <c r="E77" s="9" t="inlineStr"/>
       <c r="F77" s="9" t="inlineStr"/>
@@ -4294,7 +4314,11 @@
       <c r="I77" s="9" t="inlineStr"/>
       <c r="J77" s="9" t="inlineStr"/>
       <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
       <c r="M77" s="9" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
@@ -4381,10 +4405,18 @@
       <c r="C79" s="9" t="inlineStr"/>
       <c r="D79" s="9" t="inlineStr"/>
       <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr"/>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>ブートローダ</t>
+        </is>
+      </c>
       <c r="G79" s="9" t="inlineStr"/>
       <c r="H79" s="9" t="inlineStr"/>
-      <c r="I79" s="9" t="inlineStr"/>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>ブートローダ</t>
+        </is>
+      </c>
       <c r="J79" s="9" t="inlineStr"/>
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr"/>
@@ -4577,15 +4609,39 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr"/>
-      <c r="C84" s="9" t="inlineStr"/>
-      <c r="D84" s="9" t="inlineStr"/>
-      <c r="E84" s="9" t="inlineStr"/>
-      <c r="F84" s="9" t="inlineStr"/>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>BT0</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>BT1</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>BT2</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>BT3</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>BT4</t>
+        </is>
+      </c>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
-      <c r="J84" s="9" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>USB出力</t>
+        </is>
+      </c>
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
@@ -4665,7 +4721,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr"/>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>BT全解除</t>
+        </is>
+      </c>
       <c r="C86" s="9" t="inlineStr"/>
       <c r="D86" s="9" t="inlineStr"/>
       <c r="E86" s="9" t="inlineStr"/>
@@ -4760,9 +4820,17 @@
       </c>
       <c r="B88" s="9" t="inlineStr"/>
       <c r="C88" s="9" t="inlineStr"/>
-      <c r="D88" s="9" t="inlineStr"/>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>BT解除</t>
+        </is>
+      </c>
       <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr"/>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>BLE出力</t>
+        </is>
+      </c>
       <c r="G88" s="9" t="inlineStr"/>
       <c r="H88" s="9" t="inlineStr"/>
       <c r="I88" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5445,14 +5445,14 @@
       <c r="G100" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
           <t>pos 37
-&amp;none</t>
+&amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
@@ -5491,16 +5491,461 @@
       <c r="D101" s="9" t="inlineStr"/>
       <c r="E101" s="9" t="inlineStr"/>
       <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr"/>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
       <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr"/>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
       <c r="J101" s="9" t="inlineStr"/>
       <c r="K101" s="9" t="inlineStr"/>
       <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>VIM_VISUAL_SYM レイヤー</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="n"/>
+      <c r="J102" s="4" t="n"/>
+      <c r="K102" s="4" t="n"/>
+      <c r="L102" s="4" t="n"/>
+      <c r="M102" s="5" t="n"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;mm_vim_visual_shift_4</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr"/>
+      <c r="H103" s="7" t="inlineStr"/>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;mm_vim_visual_shift_6</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M103" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;kp LS(HOME)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr"/>
+      <c r="C104" s="9" t="inlineStr"/>
+      <c r="D104" s="9" t="inlineStr"/>
+      <c r="E104" s="9" t="inlineStr"/>
+      <c r="F104" s="9" t="inlineStr"/>
+      <c r="G104" s="9" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
+      <c r="I104" s="9" t="inlineStr"/>
+      <c r="J104" s="9" t="inlineStr"/>
+      <c r="K104" s="9" t="inlineStr"/>
+      <c r="L104" s="9" t="inlineStr"/>
+      <c r="M104" s="9" t="inlineStr">
+        <is>
+          <t>⇧HOME</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr"/>
+      <c r="C105" s="9" t="inlineStr"/>
+      <c r="D105" s="9" t="inlineStr"/>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>⇧END</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr"/>
+      <c r="G105" s="9" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr"/>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>⇧HOME</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr"/>
+      <c r="K105" s="9" t="inlineStr"/>
+      <c r="L105" s="9" t="inlineStr"/>
+      <c r="M105" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr"/>
+      <c r="D107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr"/>
+      <c r="F107" s="9" t="inlineStr"/>
+      <c r="G107" s="9" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr"/>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>⇧←</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="inlineStr"/>
+      <c r="K107" s="9" t="inlineStr"/>
+      <c r="L107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Row 3</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>pos 20
+&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>pos 21
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>pos 22
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>pos 23
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>pos 24
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>pos 25
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr"/>
+      <c r="I108" s="7" t="inlineStr">
+        <is>
+          <t>pos 26
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>pos 28
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>pos 29
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr"/>
+      <c r="D109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr"/>
+      <c r="F109" s="9" t="inlineStr"/>
+      <c r="G109" s="9" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr"/>
+      <c r="I109" s="9" t="inlineStr"/>
+      <c r="J109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr"/>
+      <c r="L109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M110" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr"/>
+      <c r="D111" s="9" t="inlineStr"/>
+      <c r="E111" s="9" t="inlineStr"/>
+      <c r="F111" s="9" t="inlineStr"/>
+      <c r="G111" s="9" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
+      <c r="I111" s="9" t="inlineStr"/>
+      <c r="J111" s="9" t="inlineStr"/>
+      <c r="K111" s="9" t="inlineStr"/>
+      <c r="L111" s="9" t="inlineStr"/>
+      <c r="M111" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="A102:M102"/>
     <mergeCell ref="A45:M45"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A91:M91"/>
@@ -5521,7 +5966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10468,14 +10913,14 @@
       <c r="G100" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
           <t>pos 37
-&amp;none</t>
+&amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
@@ -10514,16 +10959,473 @@
       <c r="D101" s="9" t="inlineStr"/>
       <c r="E101" s="9" t="inlineStr"/>
       <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr"/>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
       <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr"/>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
       <c r="J101" s="9" t="inlineStr"/>
       <c r="K101" s="9" t="inlineStr"/>
       <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>VIM_VISUAL_SYM レイヤー</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="n"/>
+      <c r="J102" s="4" t="n"/>
+      <c r="K102" s="4" t="n"/>
+      <c r="L102" s="4" t="n"/>
+      <c r="M102" s="5" t="n"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;mm_vim_visual_shift_4</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr"/>
+      <c r="H103" s="7" t="inlineStr"/>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;mm_vim_visual_shift_6</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M103" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;kp LS(HOME)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr"/>
+      <c r="C104" s="9" t="inlineStr"/>
+      <c r="D104" s="9" t="inlineStr"/>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_4[0]
+▸ &amp;none</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr"/>
+      <c r="G104" s="9" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_6[0]
+▸ &amp;none</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="inlineStr"/>
+      <c r="K104" s="9" t="inlineStr"/>
+      <c r="L104" s="9" t="inlineStr"/>
+      <c r="M104" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(HOME)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr"/>
+      <c r="C105" s="9" t="inlineStr"/>
+      <c r="D105" s="9" t="inlineStr"/>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_4[1]
+▸ &amp;kp LS(END)</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr"/>
+      <c r="G105" s="9" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr"/>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_6[1]
+▸ &amp;kp LS(HOME)</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr"/>
+      <c r="K105" s="9" t="inlineStr"/>
+      <c r="L105" s="9" t="inlineStr"/>
+      <c r="M105" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr"/>
+      <c r="D107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr"/>
+      <c r="F107" s="9" t="inlineStr"/>
+      <c r="G107" s="9" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr"/>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="inlineStr"/>
+      <c r="K107" s="9" t="inlineStr"/>
+      <c r="L107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Row 3</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>pos 20
+&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>pos 21
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>pos 22
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>pos 23
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>pos 24
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>pos 25
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr"/>
+      <c r="I108" s="7" t="inlineStr">
+        <is>
+          <t>pos 26
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>pos 28
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>pos 29
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr"/>
+      <c r="D109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr"/>
+      <c r="F109" s="9" t="inlineStr"/>
+      <c r="G109" s="9" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr"/>
+      <c r="I109" s="9" t="inlineStr"/>
+      <c r="J109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr"/>
+      <c r="L109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M110" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr"/>
+      <c r="D111" s="9" t="inlineStr"/>
+      <c r="E111" s="9" t="inlineStr"/>
+      <c r="F111" s="9" t="inlineStr"/>
+      <c r="G111" s="9" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
+      <c r="I111" s="9" t="inlineStr"/>
+      <c r="J111" s="9" t="inlineStr"/>
+      <c r="K111" s="9" t="inlineStr"/>
+      <c r="L111" s="9" t="inlineStr"/>
+      <c r="M111" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="A102:M102"/>
     <mergeCell ref="A45:M45"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A91:M91"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -3299,7 +3299,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MOUSE_MOVE レイヤー</t>
+          <t>VIM_VISUAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -3330,13 +3330,13 @@
       <c r="C56" s="7" t="inlineStr">
         <is>
           <t>pos 1
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
           <t>pos 2
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -3356,7 +3356,7 @@
       <c r="I56" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;none</t>
+&amp;macro_vim_visual_y</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
@@ -3380,28 +3380,51 @@
       <c r="M56" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
+&amp;macro_vim_visual_p</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="75" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr"/>
-      <c r="C57" s="9" t="inlineStr"/>
-      <c r="D57" s="9" t="inlineStr"/>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃→</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃→</t>
+        </is>
+      </c>
       <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="9" t="inlineStr"/>
-      <c r="I57" s="9" t="inlineStr"/>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃C
+▸ →
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
       <c r="J57" s="9" t="inlineStr"/>
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
-      <c r="M57" s="9" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃V
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -3412,7 +3435,7 @@
       <c r="B58" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -3424,7 +3447,7 @@
       <c r="D58" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -3436,7 +3459,7 @@
       <c r="F58" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;mm_vim_visual_g</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
@@ -3444,383 +3467,462 @@
       <c r="I58" s="7" t="inlineStr">
         <is>
           <t>pos 15
-&amp;none</t>
+&amp;kp LS(LEFT)</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
           <t>pos 16
-&amp;none</t>
+&amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
           <t>pos 17
-&amp;mo MOUSE_SCROLL</t>
+&amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr"/>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C59" s="9" t="inlineStr"/>
-      <c r="D59" s="9" t="inlineStr"/>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃X
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
       <c r="E59" s="9" t="inlineStr"/>
       <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="9" t="inlineStr"/>
       <c r="H59" s="9" t="inlineStr"/>
-      <c r="I59" s="9" t="inlineStr"/>
-      <c r="J59" s="9" t="inlineStr"/>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>⇧←</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>⇧↓</t>
+        </is>
+      </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="L59" s="9" t="inlineStr"/>
-      <c r="M59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Row 3</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>pos 20
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>pos 21
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>pos 22
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>pos 23
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>pos 24
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>pos 25
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>pos 27
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>pos 28
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;none</t>
+          <t>⇧↑</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>⇧→</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>ダブルタップ</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr"/>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃HOME</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr"/>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="C61" s="9" t="inlineStr"/>
-      <c r="D61" s="9" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="9" t="inlineStr"/>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃END</t>
+        </is>
+      </c>
       <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="9" t="inlineStr"/>
-      <c r="I61" s="9" t="inlineStr"/>
-      <c r="J61" s="9" t="inlineStr"/>
-      <c r="K61" s="9" t="inlineStr"/>
-      <c r="L61" s="9" t="inlineStr"/>
-      <c r="M61" s="9" t="inlineStr"/>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Row 4</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;none</t>
+          <t>pos 20
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>pos 32
-&amp;none</t>
+          <t>pos 21
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>pos 33
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>pos 34
-&amp;none</t>
+          <t>pos 23
+&amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>pos 35
-&amp;none</t>
+          <t>pos 24
+&amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>pos 36
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>pos 37
-&amp;none</t>
+          <t>pos 26
+&amp;kp F3</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>pos 39
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>pos 40
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
+          <t>pos 30
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr"/>
-      <c r="C63" s="9" t="inlineStr"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃X
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
       <c r="D63" s="9" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="9" t="inlineStr"/>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ →
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃←</t>
+        </is>
+      </c>
       <c r="G63" s="9" t="inlineStr"/>
       <c r="H63" s="9" t="inlineStr"/>
-      <c r="I63" s="9" t="inlineStr"/>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
       <c r="J63" s="9" t="inlineStr"/>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
-      <c r="M63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>MOUSE_SCROLL レイヤー</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="5" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Row 1</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>pos 0
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>pos 1
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>pos 2
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>pos 3
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>pos 5
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>pos 9
-&amp;none</t>
-        </is>
-      </c>
+      <c r="M63" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr"/>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr"/>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr"/>
+      <c r="K65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr"/>
-      <c r="C66" s="9" t="inlineStr"/>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="9" t="inlineStr"/>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
-      <c r="I66" s="9" t="inlineStr"/>
-      <c r="J66" s="9" t="inlineStr"/>
-      <c r="K66" s="9" t="inlineStr"/>
-      <c r="L66" s="9" t="inlineStr"/>
-      <c r="M66" s="9" t="inlineStr"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>VIM_VISUAL_SYM レイヤー</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="5" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Row 2</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>pos 10
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>pos 11
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>pos 12
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>pos 13
-&amp;none</t>
+          <t>pos 3
+&amp;mm_vim_visual_shift_4</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>pos 14
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -3828,32 +3930,32 @@
       <c r="H67" s="7" t="inlineStr"/>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>pos 15
-&amp;none</t>
+          <t>pos 5
+&amp;mm_vim_visual_shift_6</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>pos 16
-&amp;mkp MB1</t>
+          <t>pos 6
+&amp;none</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>pos 17
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>pos 18
-&amp;mkp MB2</t>
+          <t>pos 8
+&amp;none</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>pos 19
-&amp;none</t>
+          <t>pos 9
+&amp;kp LS(HOME)</t>
         </is>
       </c>
     </row>
@@ -3871,734 +3973,754 @@
       <c r="G68" s="9" t="inlineStr"/>
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
-      <c r="J68" s="9" t="inlineStr">
-        <is>
-          <t>🖱左</t>
-        </is>
-      </c>
+      <c r="J68" s="9" t="inlineStr"/>
       <c r="K68" s="9" t="inlineStr"/>
-      <c r="L68" s="9" t="inlineStr">
-        <is>
-          <t>🖱右</t>
-        </is>
-      </c>
-      <c r="M68" s="9" t="inlineStr"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="L68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>⇧HOME</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr"/>
+      <c r="C69" s="9" t="inlineStr"/>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>⇧END</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="9" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>⇧HOME</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr"/>
+      <c r="K69" s="9" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr"/>
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr"/>
+      <c r="D71" s="9" t="inlineStr"/>
+      <c r="E71" s="9" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="9" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>⇧←</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr"/>
+      <c r="K71" s="9" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
+&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;none</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J69" s="7" t="inlineStr">
+      <c r="J72" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;mkp MB4</t>
-        </is>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L69" s="7" t="inlineStr">
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="M69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr"/>
-      <c r="C70" s="9" t="inlineStr"/>
-      <c r="D70" s="9" t="inlineStr"/>
-      <c r="E70" s="9" t="inlineStr"/>
-      <c r="F70" s="9" t="inlineStr"/>
-      <c r="G70" s="9" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
-      <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>🖱戻</t>
-        </is>
-      </c>
-      <c r="K70" s="9" t="inlineStr"/>
-      <c r="L70" s="9" t="inlineStr">
-        <is>
-          <t>🖱進</t>
-        </is>
-      </c>
-      <c r="M70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L71" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M71" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr"/>
-      <c r="C72" s="9" t="inlineStr"/>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr"/>
-      <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="9" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr"/>
-      <c r="I72" s="9" t="inlineStr"/>
-      <c r="J72" s="9" t="inlineStr"/>
-      <c r="K72" s="9" t="inlineStr"/>
-      <c r="L72" s="9" t="inlineStr"/>
-      <c r="M72" s="9" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>FUNCTION レイヤー</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="5" t="n"/>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="9" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
+      <c r="I73" s="9" t="inlineStr"/>
+      <c r="J73" s="9" t="inlineStr"/>
+      <c r="K73" s="9" t="inlineStr"/>
+      <c r="L73" s="9" t="inlineStr"/>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr"/>
+      <c r="C75" s="9" t="inlineStr"/>
+      <c r="D75" s="9" t="inlineStr"/>
+      <c r="E75" s="9" t="inlineStr"/>
+      <c r="F75" s="9" t="inlineStr"/>
+      <c r="G75" s="9" t="inlineStr"/>
+      <c r="H75" s="9" t="inlineStr"/>
+      <c r="I75" s="9" t="inlineStr"/>
+      <c r="J75" s="9" t="inlineStr"/>
+      <c r="K75" s="9" t="inlineStr"/>
+      <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>FUNCTION レイヤー</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="5" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
           <t>Row 1</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>pos 0
 &amp;kp F1</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>pos 1
 &amp;kp F2</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>pos 2
 &amp;kp F3</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>pos 3
 &amp;kp F4</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>pos 4
 &amp;kp F5</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="J77" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
-      <c r="M74" s="7" t="inlineStr">
+      <c r="M77" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp F10</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F78" s="9" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr"/>
-      <c r="H75" s="9" t="inlineStr"/>
-      <c r="I75" s="9" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr"/>
+      <c r="I78" s="9" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
       </c>
-      <c r="J75" s="9" t="inlineStr">
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>F7</t>
         </is>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>F8</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>F9</t>
         </is>
       </c>
-      <c r="M75" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;none</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr"/>
-      <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J76" s="7" t="inlineStr">
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K76" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L76" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="M76" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr"/>
-      <c r="E77" s="9" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr"/>
-      <c r="G77" s="9" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
-      <c r="I77" s="9" t="inlineStr"/>
-      <c r="J77" s="9" t="inlineStr"/>
-      <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="9" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr"/>
+      <c r="G80" s="9" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr"/>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
+      <c r="K80" s="9" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="M77" s="9" t="inlineStr"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="M80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;none</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="J78" s="7" t="inlineStr">
+      <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M78" s="7" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr"/>
-      <c r="C79" s="9" t="inlineStr"/>
-      <c r="D79" s="9" t="inlineStr"/>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr"/>
+      <c r="E82" s="9" t="inlineStr"/>
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>ブートローダ</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
-      <c r="I79" s="9" t="inlineStr">
+      <c r="G82" s="9" t="inlineStr"/>
+      <c r="H82" s="9" t="inlineStr"/>
+      <c r="I82" s="9" t="inlineStr">
         <is>
           <t>ブートローダ</t>
         </is>
       </c>
-      <c r="J79" s="9" t="inlineStr"/>
-      <c r="K79" s="9" t="inlineStr"/>
-      <c r="L79" s="9" t="inlineStr"/>
-      <c r="M79" s="9" t="inlineStr"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr"/>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L80" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M80" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr"/>
-      <c r="C81" s="9" t="inlineStr"/>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="9" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
-      <c r="I81" s="9" t="inlineStr"/>
-      <c r="J81" s="9" t="inlineStr"/>
-      <c r="K81" s="9" t="inlineStr"/>
-      <c r="L81" s="9" t="inlineStr"/>
-      <c r="M81" s="9" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>BLUETOOTH レイヤー</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="n"/>
-      <c r="C82" s="4" t="n"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="5" t="n"/>
+      <c r="J82" s="9" t="inlineStr"/>
+      <c r="K82" s="9" t="inlineStr"/>
+      <c r="L82" s="9" t="inlineStr"/>
+      <c r="M82" s="9" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>pos 0
-&amp;bt BT_SEL 0</t>
+          <t>pos 31
+&amp;none</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;bt BT_SEL 1</t>
+          <t>pos 32
+&amp;none</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;bt BT_SEL 2</t>
+          <t>pos 33
+&amp;none</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>pos 3
-&amp;bt BT_SEL 3</t>
+          <t>pos 34
+&amp;none</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;bt BT_SEL 4</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
       <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>pos 5
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>pos 6
-&amp;out OUT_USB</t>
+          <t>pos 38
+&amp;none</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>pos 8
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>pos 9
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4609,1045 +4731,927 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>BT0</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>BT1</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>BT2</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>BT3</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>BT4</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="inlineStr"/>
+      <c r="C84" s="9" t="inlineStr"/>
+      <c r="D84" s="9" t="inlineStr"/>
+      <c r="E84" s="9" t="inlineStr"/>
+      <c r="F84" s="9" t="inlineStr"/>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>USB出力</t>
-        </is>
-      </c>
+      <c r="J84" s="9" t="inlineStr"/>
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
     </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>BLUETOOTH レイヤー</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="5" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;bt BT_SEL 0</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;bt BT_SEL 1</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;bt BT_SEL 2</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;bt BT_SEL 3</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;bt BT_SEL 4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;out OUT_USB</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>BT0</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>BT1</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>BT2</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>BT3</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>BT4</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
+      <c r="I87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>USB出力</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr"/>
+      <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;none</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J85" s="7" t="inlineStr">
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>BT全解除</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr"/>
-      <c r="D86" s="9" t="inlineStr"/>
-      <c r="E86" s="9" t="inlineStr"/>
-      <c r="F86" s="9" t="inlineStr"/>
-      <c r="G86" s="9" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr"/>
-      <c r="I86" s="9" t="inlineStr"/>
-      <c r="J86" s="9" t="inlineStr"/>
-      <c r="K86" s="9" t="inlineStr"/>
-      <c r="L86" s="9" t="inlineStr"/>
-      <c r="M86" s="9" t="inlineStr"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr"/>
+      <c r="D89" s="9" t="inlineStr"/>
+      <c r="E89" s="9" t="inlineStr"/>
+      <c r="F89" s="9" t="inlineStr"/>
+      <c r="G89" s="9" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
+      <c r="I89" s="9" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr"/>
+      <c r="K89" s="9" t="inlineStr"/>
+      <c r="L89" s="9" t="inlineStr"/>
+      <c r="M89" s="9" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;none</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;bt BT_CLR</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J87" s="7" t="inlineStr">
+      <c r="J90" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr">
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M87" s="7" t="inlineStr">
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr"/>
-      <c r="C88" s="9" t="inlineStr"/>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr"/>
+      <c r="C91" s="9" t="inlineStr"/>
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>BT解除</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr"/>
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>BLE出力</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
-      <c r="I88" s="9" t="inlineStr"/>
-      <c r="J88" s="9" t="inlineStr"/>
-      <c r="K88" s="9" t="inlineStr"/>
-      <c r="L88" s="9" t="inlineStr"/>
-      <c r="M88" s="9" t="inlineStr"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr"/>
-      <c r="C90" s="9" t="inlineStr"/>
-      <c r="D90" s="9" t="inlineStr"/>
-      <c r="E90" s="9" t="inlineStr"/>
-      <c r="F90" s="9" t="inlineStr"/>
-      <c r="G90" s="9" t="inlineStr"/>
-      <c r="H90" s="9" t="inlineStr"/>
-      <c r="I90" s="9" t="inlineStr"/>
-      <c r="J90" s="9" t="inlineStr"/>
-      <c r="K90" s="9" t="inlineStr"/>
-      <c r="L90" s="9" t="inlineStr"/>
-      <c r="M90" s="9" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_BASE レイヤー</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
-      <c r="J91" s="4" t="n"/>
-      <c r="K91" s="4" t="n"/>
-      <c r="L91" s="4" t="n"/>
-      <c r="M91" s="5" t="n"/>
+      <c r="G91" s="9" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
+      <c r="I91" s="9" t="inlineStr"/>
+      <c r="J91" s="9" t="inlineStr"/>
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>pos 0
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 32
+&amp;none</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 33
+&amp;none</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>pos 3
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
       <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;macro_vim_visual_y</t>
+          <t>pos 37
+&amp;none</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>pos 8
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>pos 9
-&amp;macro_vim_visual_p</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="75" customHeight="1">
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr"/>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃→</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃→</t>
-        </is>
-      </c>
+      <c r="C93" s="9" t="inlineStr"/>
+      <c r="D93" s="9" t="inlineStr"/>
       <c r="E93" s="9" t="inlineStr"/>
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
-      <c r="I93" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃C
-▸ →
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
+      <c r="I93" s="9" t="inlineStr"/>
       <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
-      <c r="M93" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃V
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Row 2</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>pos 10
-&amp;kp LCTRL</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>pos 11
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>pos 12
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>pos 13
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>pos 14
-&amp;mm_vim_visual_g</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>pos 15
-&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>pos 16
-&amp;kp LS(DOWN)</t>
-        </is>
-      </c>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>pos 17
-&amp;kp LS(UP)</t>
-        </is>
-      </c>
-      <c r="L94" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="inlineStr">
-        <is>
-          <t>pos 19
-&amp;kp RCTRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>LCtrl</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr"/>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃X
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="9" t="inlineStr"/>
-      <c r="G95" s="9" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>⇧←</t>
-        </is>
-      </c>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>⇧↓</t>
-        </is>
-      </c>
-      <c r="K95" s="9" t="inlineStr">
-        <is>
-          <t>⇧↑</t>
-        </is>
-      </c>
-      <c r="L95" s="9" t="inlineStr">
-        <is>
-          <t>⇧→</t>
-        </is>
-      </c>
-      <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>RCtrl</t>
+      <c r="M93" s="9" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_MOVE レイヤー</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="5" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>ダブルタップ</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr"/>
       <c r="C96" s="9" t="inlineStr"/>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="D96" s="9" t="inlineStr"/>
       <c r="E96" s="9" t="inlineStr"/>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃HOME</t>
-        </is>
-      </c>
+      <c r="F96" s="9" t="inlineStr"/>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>Shift+</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr"/>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr"/>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃END</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="I96" s="9" t="inlineStr"/>
+      <c r="J96" s="9" t="inlineStr"/>
+      <c r="K96" s="9" t="inlineStr"/>
+      <c r="L96" s="9" t="inlineStr"/>
+      <c r="M96" s="9" t="inlineStr"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr"/>
+      <c r="C98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr"/>
+      <c r="E98" s="9" t="inlineStr"/>
+      <c r="F98" s="9" t="inlineStr"/>
+      <c r="G98" s="9" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="9" t="inlineStr"/>
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr"/>
+      <c r="M98" s="9" t="inlineStr"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;macro_vim_visual_exit</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;kp LS(LC(LEFT))</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="J98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K98" s="7" t="inlineStr">
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L98" s="7" t="inlineStr">
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M98" s="7" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>LShift</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃X
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr"/>
-      <c r="E99" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ →
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃←</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="J99" s="9" t="inlineStr"/>
-      <c r="K99" s="9" t="inlineStr"/>
-      <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr">
-        <is>
-          <t>RShift</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr"/>
+      <c r="C100" s="9" t="inlineStr"/>
+      <c r="D100" s="9" t="inlineStr"/>
+      <c r="E100" s="9" t="inlineStr"/>
+      <c r="F100" s="9" t="inlineStr"/>
+      <c r="G100" s="9" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr"/>
+      <c r="K100" s="9" t="inlineStr"/>
+      <c r="L100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>Row 4</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 32
 &amp;none</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>pos 37
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="J100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="K100" s="7" t="inlineStr">
+      <c r="K101" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="L100" s="7" t="inlineStr">
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M100" s="7" t="inlineStr">
+      <c r="M101" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr"/>
-      <c r="C101" s="9" t="inlineStr"/>
-      <c r="D101" s="9" t="inlineStr"/>
-      <c r="E101" s="9" t="inlineStr"/>
-      <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
-      <c r="J101" s="9" t="inlineStr"/>
-      <c r="K101" s="9" t="inlineStr"/>
-      <c r="L101" s="9" t="inlineStr"/>
-      <c r="M101" s="9" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_SYM レイヤー</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
-      <c r="K102" s="4" t="n"/>
-      <c r="L102" s="4" t="n"/>
-      <c r="M102" s="5" t="n"/>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr"/>
+      <c r="D102" s="9" t="inlineStr"/>
+      <c r="E102" s="9" t="inlineStr"/>
+      <c r="F102" s="9" t="inlineStr"/>
+      <c r="G102" s="9" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr"/>
+      <c r="K102" s="9" t="inlineStr"/>
+      <c r="L102" s="9" t="inlineStr"/>
+      <c r="M102" s="9" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_SCROLL レイヤー</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="5" t="n"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>Row 1</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>pos 0
 &amp;none</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>pos 1
 &amp;none</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>pos 2
 &amp;none</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>pos 3
-&amp;mm_vim_visual_shift_4</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>pos 4
 &amp;none</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr"/>
-      <c r="H103" s="7" t="inlineStr"/>
-      <c r="I103" s="7" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;mm_vim_visual_shift_6</t>
-        </is>
-      </c>
-      <c r="J103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K103" s="7" t="inlineStr">
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L103" s="7" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M103" s="7" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;kp LS(HOME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr"/>
-      <c r="C104" s="9" t="inlineStr"/>
-      <c r="D104" s="9" t="inlineStr"/>
-      <c r="E104" s="9" t="inlineStr"/>
-      <c r="F104" s="9" t="inlineStr"/>
-      <c r="G104" s="9" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
-      <c r="I104" s="9" t="inlineStr"/>
-      <c r="J104" s="9" t="inlineStr"/>
-      <c r="K104" s="9" t="inlineStr"/>
-      <c r="L104" s="9" t="inlineStr"/>
-      <c r="M104" s="9" t="inlineStr">
-        <is>
-          <t>⇧HOME</t>
+&amp;none</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Shift+</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr"/>
       <c r="C105" s="9" t="inlineStr"/>
       <c r="D105" s="9" t="inlineStr"/>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>⇧END</t>
-        </is>
-      </c>
+      <c r="E105" s="9" t="inlineStr"/>
       <c r="F105" s="9" t="inlineStr"/>
       <c r="G105" s="9" t="inlineStr"/>
       <c r="H105" s="9" t="inlineStr"/>
-      <c r="I105" s="9" t="inlineStr">
-        <is>
-          <t>⇧HOME</t>
-        </is>
-      </c>
+      <c r="I105" s="9" t="inlineStr"/>
       <c r="J105" s="9" t="inlineStr"/>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
-      <c r="M105" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="M105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -5658,7 +5662,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -5690,13 +5694,13 @@
       <c r="I106" s="7" t="inlineStr">
         <is>
           <t>pos 15
-&amp;kp LS(LEFT)</t>
+&amp;none</t>
         </is>
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
           <t>pos 16
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
@@ -5708,13 +5712,13 @@
       <c r="L106" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;kp RCTRL</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -5724,30 +5728,26 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>LCtrl</t>
-        </is>
-      </c>
+      <c r="B107" s="9" t="inlineStr"/>
       <c r="C107" s="9" t="inlineStr"/>
       <c r="D107" s="9" t="inlineStr"/>
       <c r="E107" s="9" t="inlineStr"/>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>⇧←</t>
-        </is>
-      </c>
-      <c r="J107" s="9" t="inlineStr"/>
+      <c r="I107" s="9" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="K107" s="9" t="inlineStr"/>
-      <c r="L107" s="9" t="inlineStr"/>
-      <c r="M107" s="9" t="inlineStr">
-        <is>
-          <t>RCtrl</t>
-        </is>
-      </c>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
+      <c r="M107" s="9" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -5758,7 +5758,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -5801,7 +5801,7 @@
       <c r="J108" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="K108" s="7" t="inlineStr">
@@ -5813,13 +5813,13 @@
       <c r="L108" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="M108" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;kp RIGHT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -5829,11 +5829,7 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>LShift</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="inlineStr"/>
       <c r="C109" s="9" t="inlineStr"/>
       <c r="D109" s="9" t="inlineStr"/>
       <c r="E109" s="9" t="inlineStr"/>
@@ -5841,14 +5837,18 @@
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
       <c r="I109" s="9" t="inlineStr"/>
-      <c r="J109" s="9" t="inlineStr"/>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="K109" s="9" t="inlineStr"/>
-      <c r="L109" s="9" t="inlineStr"/>
-      <c r="M109" s="9" t="inlineStr">
-        <is>
-          <t>RShift</t>
-        </is>
-      </c>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
+      <c r="M109" s="9" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -5945,15 +5945,15 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A102:M102"/>
+    <mergeCell ref="A76:M76"/>
+    <mergeCell ref="A66:M66"/>
     <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A94:M94"/>
+    <mergeCell ref="A103:M103"/>
     <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A91:M91"/>
     <mergeCell ref="A55:M55"/>
-    <mergeCell ref="A64:M64"/>
-    <mergeCell ref="A73:M73"/>
     <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A82:M82"/>
+    <mergeCell ref="A85:M85"/>
     <mergeCell ref="A28:M28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8774,7 +8774,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MOUSE_MOVE レイヤー</t>
+          <t>VIM_VISUAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -8805,13 +8805,13 @@
       <c r="C56" s="7" t="inlineStr">
         <is>
           <t>pos 1
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
           <t>pos 2
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -8831,7 +8831,7 @@
       <c r="I56" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;none</t>
+&amp;macro_vim_visual_y</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
@@ -8855,7 +8855,7 @@
       <c r="M56" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;none</t>
+&amp;macro_vim_visual_p</t>
         </is>
       </c>
     </row>
@@ -8866,17 +8866,33 @@
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr"/>
-      <c r="C57" s="9" t="inlineStr"/>
-      <c r="D57" s="9" t="inlineStr"/>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LC(RIGHT))</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LC(RIGHT))</t>
+        </is>
+      </c>
       <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="9" t="inlineStr"/>
-      <c r="I57" s="9" t="inlineStr"/>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_y</t>
+        </is>
+      </c>
       <c r="J57" s="9" t="inlineStr"/>
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
-      <c r="M57" s="9" t="inlineStr"/>
+      <c r="M57" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_p</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -8887,7 +8903,7 @@
       <c r="B58" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -8899,7 +8915,7 @@
       <c r="D58" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -8911,7 +8927,7 @@
       <c r="F58" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;mm_vim_visual_g</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
@@ -8919,221 +8935,263 @@
       <c r="I58" s="7" t="inlineStr">
         <is>
           <t>pos 15
-&amp;none</t>
+&amp;kp LS(LEFT)</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
           <t>pos 16
-&amp;none</t>
+&amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
           <t>pos 17
-&amp;mo MOUSE_SCROLL</t>
+&amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr"/>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C59" s="9" t="inlineStr"/>
-      <c r="D59" s="9" t="inlineStr"/>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_cut</t>
+        </is>
+      </c>
       <c r="E59" s="9" t="inlineStr"/>
-      <c r="F59" s="9" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[0]
+▸ td_vim_visual_g[0]
+▸ &amp;none</t>
+        </is>
+      </c>
       <c r="G59" s="9" t="inlineStr"/>
       <c r="H59" s="9" t="inlineStr"/>
-      <c r="I59" s="9" t="inlineStr"/>
-      <c r="J59" s="9" t="inlineStr"/>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(DOWN)</t>
+        </is>
+      </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo MOUSE_SCROLL</t>
-        </is>
-      </c>
-      <c r="L59" s="9" t="inlineStr"/>
-      <c r="M59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Row 3</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>pos 20
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>pos 21
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>pos 22
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>pos 23
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>pos 24
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>pos 25
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>pos 27
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>pos 28
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
+          <t>&amp;kp LS(UP)</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(RIGHT)</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>ダブルタップ</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr"/>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[0]
+▸ td_vim_visual_g[1]
+▸ &amp;kp LS(LC(HOME))</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr"/>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="C61" s="9" t="inlineStr"/>
-      <c r="D61" s="9" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="9" t="inlineStr"/>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[1]
+▸ &amp;kp LS(LC(END))</t>
+        </is>
+      </c>
       <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="9" t="inlineStr"/>
-      <c r="I61" s="9" t="inlineStr"/>
-      <c r="J61" s="9" t="inlineStr"/>
-      <c r="K61" s="9" t="inlineStr"/>
-      <c r="L61" s="9" t="inlineStr"/>
-      <c r="M61" s="9" t="inlineStr"/>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Row 4</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;none</t>
+          <t>pos 20
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>pos 32
-&amp;none</t>
+          <t>pos 21
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>pos 33
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>pos 34
-&amp;none</t>
+          <t>pos 23
+&amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>pos 35
-&amp;none</t>
+          <t>pos 24
+&amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>pos 36
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>pos 37
-&amp;none</t>
+          <t>pos 26
+&amp;kp F3</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>pos 39
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>pos 40
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>pos 41
-&amp;none</t>
+          <t>pos 30
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -9143,159 +9201,196 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr"/>
-      <c r="C63" s="9" t="inlineStr"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_cut</t>
+        </is>
+      </c>
       <c r="D63" s="9" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="9" t="inlineStr"/>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_exit</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LC(LEFT))</t>
+        </is>
+      </c>
       <c r="G63" s="9" t="inlineStr"/>
       <c r="H63" s="9" t="inlineStr"/>
-      <c r="I63" s="9" t="inlineStr"/>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F3</t>
+        </is>
+      </c>
       <c r="J63" s="9" t="inlineStr"/>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
-      <c r="M63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>MOUSE_SCROLL レイヤー</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="5" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Row 1</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>pos 0
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>pos 1
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>pos 2
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>pos 3
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>pos 5
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>pos 9
-&amp;none</t>
-        </is>
-      </c>
+      <c r="M63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr"/>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr"/>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr"/>
+      <c r="K65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr"/>
-      <c r="C66" s="9" t="inlineStr"/>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="9" t="inlineStr"/>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
-      <c r="I66" s="9" t="inlineStr"/>
-      <c r="J66" s="9" t="inlineStr"/>
-      <c r="K66" s="9" t="inlineStr"/>
-      <c r="L66" s="9" t="inlineStr"/>
-      <c r="M66" s="9" t="inlineStr"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>VIM_VISUAL_SYM レイヤー</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="5" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Row 2</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>pos 10
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>pos 11
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>pos 12
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>pos 13
-&amp;none</t>
+          <t>pos 3
+&amp;mm_vim_visual_shift_4</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>pos 14
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -9303,36 +9398,36 @@
       <c r="H67" s="7" t="inlineStr"/>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>pos 15
-&amp;none</t>
+          <t>pos 5
+&amp;mm_vim_visual_shift_6</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>pos 16
-&amp;mkp MB1</t>
+          <t>pos 6
+&amp;none</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>pos 17
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>pos 18
-&amp;mkp MB2</t>
+          <t>pos 8
+&amp;none</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>pos 19
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
+          <t>pos 9
+&amp;kp LS(HOME)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -9341,739 +9436,771 @@
       <c r="B68" s="9" t="inlineStr"/>
       <c r="C68" s="9" t="inlineStr"/>
       <c r="D68" s="9" t="inlineStr"/>
-      <c r="E68" s="9" t="inlineStr"/>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_4[0]
+▸ &amp;none</t>
+        </is>
+      </c>
       <c r="F68" s="9" t="inlineStr"/>
       <c r="G68" s="9" t="inlineStr"/>
       <c r="H68" s="9" t="inlineStr"/>
-      <c r="I68" s="9" t="inlineStr"/>
-      <c r="J68" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB1</t>
-        </is>
-      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_6[0]
+▸ &amp;none</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr"/>
       <c r="K68" s="9" t="inlineStr"/>
-      <c r="L68" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB2</t>
-        </is>
-      </c>
-      <c r="M68" s="9" t="inlineStr"/>
+      <c r="L68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(HOME)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr"/>
+      <c r="C69" s="9" t="inlineStr"/>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_4[1]
+▸ &amp;kp LS(END)</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="9" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_6[1]
+▸ &amp;kp LS(HOME)</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr"/>
+      <c r="K69" s="9" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr"/>
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr"/>
+      <c r="D71" s="9" t="inlineStr"/>
+      <c r="E71" s="9" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="9" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr"/>
+      <c r="K71" s="9" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
+&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;none</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J69" s="7" t="inlineStr">
+      <c r="J72" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;mkp MB4</t>
-        </is>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L69" s="7" t="inlineStr">
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="M69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr"/>
-      <c r="C70" s="9" t="inlineStr"/>
-      <c r="D70" s="9" t="inlineStr"/>
-      <c r="E70" s="9" t="inlineStr"/>
-      <c r="F70" s="9" t="inlineStr"/>
-      <c r="G70" s="9" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
-      <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB4</t>
-        </is>
-      </c>
-      <c r="K70" s="9" t="inlineStr"/>
-      <c r="L70" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="M70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L71" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M71" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr"/>
-      <c r="C72" s="9" t="inlineStr"/>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr"/>
-      <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="9" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr"/>
-      <c r="I72" s="9" t="inlineStr"/>
-      <c r="J72" s="9" t="inlineStr"/>
-      <c r="K72" s="9" t="inlineStr"/>
-      <c r="L72" s="9" t="inlineStr"/>
-      <c r="M72" s="9" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>FUNCTION レイヤー</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="5" t="n"/>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="9" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
+      <c r="I73" s="9" t="inlineStr"/>
+      <c r="J73" s="9" t="inlineStr"/>
+      <c r="K73" s="9" t="inlineStr"/>
+      <c r="L73" s="9" t="inlineStr"/>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr"/>
+      <c r="C75" s="9" t="inlineStr"/>
+      <c r="D75" s="9" t="inlineStr"/>
+      <c r="E75" s="9" t="inlineStr"/>
+      <c r="F75" s="9" t="inlineStr"/>
+      <c r="G75" s="9" t="inlineStr"/>
+      <c r="H75" s="9" t="inlineStr"/>
+      <c r="I75" s="9" t="inlineStr"/>
+      <c r="J75" s="9" t="inlineStr"/>
+      <c r="K75" s="9" t="inlineStr"/>
+      <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>FUNCTION レイヤー</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="5" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
           <t>Row 1</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>pos 0
 &amp;kp F1</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>pos 1
 &amp;kp F2</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>pos 2
 &amp;kp F3</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>pos 3
 &amp;kp F4</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>pos 4
 &amp;kp F5</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="J77" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
-      <c r="M74" s="7" t="inlineStr">
+      <c r="M77" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp F10</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F1</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F2</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F3</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F4</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F5</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr"/>
-      <c r="H75" s="9" t="inlineStr"/>
-      <c r="I75" s="9" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr"/>
+      <c r="I78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F6</t>
         </is>
       </c>
-      <c r="J75" s="9" t="inlineStr">
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F7</t>
         </is>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F8</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F9</t>
         </is>
       </c>
-      <c r="M75" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F10</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;none</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr"/>
-      <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J76" s="7" t="inlineStr">
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K76" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L76" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="M76" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr"/>
-      <c r="E77" s="9" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr"/>
-      <c r="G77" s="9" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
-      <c r="I77" s="9" t="inlineStr"/>
-      <c r="J77" s="9" t="inlineStr"/>
-      <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="9" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr"/>
+      <c r="G80" s="9" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr"/>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
+      <c r="K80" s="9" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="M77" s="9" t="inlineStr"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="M80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;none</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="J78" s="7" t="inlineStr">
+      <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M78" s="7" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr"/>
-      <c r="C79" s="9" t="inlineStr"/>
-      <c r="D79" s="9" t="inlineStr"/>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr"/>
+      <c r="E82" s="9" t="inlineStr"/>
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>&amp;bootloader</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
-      <c r="I79" s="9" t="inlineStr">
+      <c r="G82" s="9" t="inlineStr"/>
+      <c r="H82" s="9" t="inlineStr"/>
+      <c r="I82" s="9" t="inlineStr">
         <is>
           <t>&amp;bootloader</t>
         </is>
       </c>
-      <c r="J79" s="9" t="inlineStr"/>
-      <c r="K79" s="9" t="inlineStr"/>
-      <c r="L79" s="9" t="inlineStr"/>
-      <c r="M79" s="9" t="inlineStr"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr"/>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L80" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M80" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr"/>
-      <c r="C81" s="9" t="inlineStr"/>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="9" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
-      <c r="I81" s="9" t="inlineStr"/>
-      <c r="J81" s="9" t="inlineStr"/>
-      <c r="K81" s="9" t="inlineStr"/>
-      <c r="L81" s="9" t="inlineStr"/>
-      <c r="M81" s="9" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>BLUETOOTH レイヤー</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="n"/>
-      <c r="C82" s="4" t="n"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="5" t="n"/>
+      <c r="J82" s="9" t="inlineStr"/>
+      <c r="K82" s="9" t="inlineStr"/>
+      <c r="L82" s="9" t="inlineStr"/>
+      <c r="M82" s="9" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>pos 0
-&amp;bt BT_SEL 0</t>
+          <t>pos 31
+&amp;none</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;bt BT_SEL 1</t>
+          <t>pos 32
+&amp;none</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;bt BT_SEL 2</t>
+          <t>pos 33
+&amp;none</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>pos 3
-&amp;bt BT_SEL 3</t>
+          <t>pos 34
+&amp;none</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;bt BT_SEL 4</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
       <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>pos 5
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>pos 6
-&amp;out OUT_USB</t>
+          <t>pos 38
+&amp;none</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>pos 8
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>pos 9
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -10084,414 +10211,414 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 0</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 1</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 2</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 3</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 4</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="inlineStr"/>
+      <c r="C84" s="9" t="inlineStr"/>
+      <c r="D84" s="9" t="inlineStr"/>
+      <c r="E84" s="9" t="inlineStr"/>
+      <c r="F84" s="9" t="inlineStr"/>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;out OUT_USB</t>
-        </is>
-      </c>
+      <c r="J84" s="9" t="inlineStr"/>
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
     </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>BLUETOOTH レイヤー</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="5" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;bt BT_SEL 0</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;bt BT_SEL 1</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;bt BT_SEL 2</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;bt BT_SEL 3</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;bt BT_SEL 4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;out OUT_USB</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 0</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 1</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 2</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 3</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 4</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
+      <c r="I87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;out OUT_USB</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr"/>
+      <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;none</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J85" s="7" t="inlineStr">
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>&amp;bt BT_CLR_ALL</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr"/>
-      <c r="D86" s="9" t="inlineStr"/>
-      <c r="E86" s="9" t="inlineStr"/>
-      <c r="F86" s="9" t="inlineStr"/>
-      <c r="G86" s="9" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr"/>
-      <c r="I86" s="9" t="inlineStr"/>
-      <c r="J86" s="9" t="inlineStr"/>
-      <c r="K86" s="9" t="inlineStr"/>
-      <c r="L86" s="9" t="inlineStr"/>
-      <c r="M86" s="9" t="inlineStr"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr"/>
+      <c r="D89" s="9" t="inlineStr"/>
+      <c r="E89" s="9" t="inlineStr"/>
+      <c r="F89" s="9" t="inlineStr"/>
+      <c r="G89" s="9" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
+      <c r="I89" s="9" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr"/>
+      <c r="K89" s="9" t="inlineStr"/>
+      <c r="L89" s="9" t="inlineStr"/>
+      <c r="M89" s="9" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;none</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;bt BT_CLR</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J87" s="7" t="inlineStr">
+      <c r="J90" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr">
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M87" s="7" t="inlineStr">
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr"/>
-      <c r="C88" s="9" t="inlineStr"/>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr"/>
+      <c r="C91" s="9" t="inlineStr"/>
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>&amp;bt BT_CLR</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr"/>
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>&amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
-      <c r="I88" s="9" t="inlineStr"/>
-      <c r="J88" s="9" t="inlineStr"/>
-      <c r="K88" s="9" t="inlineStr"/>
-      <c r="L88" s="9" t="inlineStr"/>
-      <c r="M88" s="9" t="inlineStr"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr"/>
-      <c r="C90" s="9" t="inlineStr"/>
-      <c r="D90" s="9" t="inlineStr"/>
-      <c r="E90" s="9" t="inlineStr"/>
-      <c r="F90" s="9" t="inlineStr"/>
-      <c r="G90" s="9" t="inlineStr"/>
-      <c r="H90" s="9" t="inlineStr"/>
-      <c r="I90" s="9" t="inlineStr"/>
-      <c r="J90" s="9" t="inlineStr"/>
-      <c r="K90" s="9" t="inlineStr"/>
-      <c r="L90" s="9" t="inlineStr"/>
-      <c r="M90" s="9" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_BASE レイヤー</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
-      <c r="J91" s="4" t="n"/>
-      <c r="K91" s="4" t="n"/>
-      <c r="L91" s="4" t="n"/>
-      <c r="M91" s="5" t="n"/>
+      <c r="G91" s="9" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
+      <c r="I91" s="9" t="inlineStr"/>
+      <c r="J91" s="9" t="inlineStr"/>
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>pos 0
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 32
+&amp;none</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 33
+&amp;none</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>pos 3
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
       <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;macro_vim_visual_y</t>
+          <t>pos 37
+&amp;none</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>pos 8
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>pos 9
-&amp;macro_vim_visual_p</t>
+          <t>pos 41
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -10502,632 +10629,509 @@
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr"/>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LC(RIGHT))</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LC(RIGHT))</t>
-        </is>
-      </c>
+      <c r="C93" s="9" t="inlineStr"/>
+      <c r="D93" s="9" t="inlineStr"/>
       <c r="E93" s="9" t="inlineStr"/>
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_y</t>
-        </is>
-      </c>
+      <c r="I93" s="9" t="inlineStr"/>
       <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
-      <c r="M93" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_p</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Row 2</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>pos 10
-&amp;kp LCTRL</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>pos 11
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>pos 12
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>pos 13
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>pos 14
-&amp;mm_vim_visual_g</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>pos 15
-&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>pos 16
-&amp;kp LS(DOWN)</t>
-        </is>
-      </c>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>pos 17
-&amp;kp LS(UP)</t>
-        </is>
-      </c>
-      <c r="L94" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="inlineStr">
-        <is>
-          <t>pos 19
-&amp;kp RCTRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="45" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="M93" s="9" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_MOVE レイヤー</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="5" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LCTRL</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr"/>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[0]
-▸ td_vim_visual_g[0]
-▸ &amp;none</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(DOWN)</t>
-        </is>
-      </c>
-      <c r="K95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(UP)</t>
-        </is>
-      </c>
-      <c r="L95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RCTRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="45" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>ダブルタップ</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="B96" s="9" t="inlineStr"/>
       <c r="C96" s="9" t="inlineStr"/>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="D96" s="9" t="inlineStr"/>
       <c r="E96" s="9" t="inlineStr"/>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[0]
-▸ td_vim_visual_g[1]
-▸ &amp;kp LS(LC(HOME))</t>
-        </is>
-      </c>
+      <c r="F96" s="9" t="inlineStr"/>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I96" s="9" t="inlineStr"/>
+      <c r="J96" s="9" t="inlineStr"/>
+      <c r="K96" s="9" t="inlineStr"/>
+      <c r="L96" s="9" t="inlineStr"/>
+      <c r="M96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>Shift+</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr"/>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr"/>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[1]
-▸ &amp;kp LS(LC(END))</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr"/>
+      <c r="C98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr"/>
+      <c r="E98" s="9" t="inlineStr"/>
+      <c r="F98" s="9" t="inlineStr"/>
+      <c r="G98" s="9" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="9" t="inlineStr"/>
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr"/>
+      <c r="M98" s="9" t="inlineStr"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;macro_vim_visual_exit</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;kp LS(LC(LEFT))</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="J98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K98" s="7" t="inlineStr">
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L98" s="7" t="inlineStr">
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M98" s="7" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr"/>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_exit</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LC(LEFT))</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="J99" s="9" t="inlineStr"/>
-      <c r="K99" s="9" t="inlineStr"/>
-      <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr"/>
+      <c r="C100" s="9" t="inlineStr"/>
+      <c r="D100" s="9" t="inlineStr"/>
+      <c r="E100" s="9" t="inlineStr"/>
+      <c r="F100" s="9" t="inlineStr"/>
+      <c r="G100" s="9" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr"/>
+      <c r="K100" s="9" t="inlineStr"/>
+      <c r="L100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>Row 4</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 32
 &amp;none</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>pos 37
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="J100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="K100" s="7" t="inlineStr">
+      <c r="K101" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="L100" s="7" t="inlineStr">
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M100" s="7" t="inlineStr">
+      <c r="M101" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr"/>
-      <c r="C101" s="9" t="inlineStr"/>
-      <c r="D101" s="9" t="inlineStr"/>
-      <c r="E101" s="9" t="inlineStr"/>
-      <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="J101" s="9" t="inlineStr"/>
-      <c r="K101" s="9" t="inlineStr"/>
-      <c r="L101" s="9" t="inlineStr"/>
-      <c r="M101" s="9" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_SYM レイヤー</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
-      <c r="K102" s="4" t="n"/>
-      <c r="L102" s="4" t="n"/>
-      <c r="M102" s="5" t="n"/>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr"/>
+      <c r="D102" s="9" t="inlineStr"/>
+      <c r="E102" s="9" t="inlineStr"/>
+      <c r="F102" s="9" t="inlineStr"/>
+      <c r="G102" s="9" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr"/>
+      <c r="K102" s="9" t="inlineStr"/>
+      <c r="L102" s="9" t="inlineStr"/>
+      <c r="M102" s="9" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_SCROLL レイヤー</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="5" t="n"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>Row 1</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>pos 0
 &amp;none</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>pos 1
 &amp;none</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>pos 2
 &amp;none</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>pos 3
-&amp;mm_vim_visual_shift_4</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>pos 4
 &amp;none</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr"/>
-      <c r="H103" s="7" t="inlineStr"/>
-      <c r="I103" s="7" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;mm_vim_visual_shift_6</t>
-        </is>
-      </c>
-      <c r="J103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K103" s="7" t="inlineStr">
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L103" s="7" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M103" s="7" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;kp LS(HOME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr"/>
-      <c r="C104" s="9" t="inlineStr"/>
-      <c r="D104" s="9" t="inlineStr"/>
-      <c r="E104" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_4[0]
-▸ &amp;none</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr"/>
-      <c r="G104" s="9" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_6[0]
-▸ &amp;none</t>
-        </is>
-      </c>
-      <c r="J104" s="9" t="inlineStr"/>
-      <c r="K104" s="9" t="inlineStr"/>
-      <c r="L104" s="9" t="inlineStr"/>
-      <c r="M104" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(HOME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>Shift+</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr"/>
       <c r="C105" s="9" t="inlineStr"/>
       <c r="D105" s="9" t="inlineStr"/>
-      <c r="E105" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_4[1]
-▸ &amp;kp LS(END)</t>
-        </is>
-      </c>
+      <c r="E105" s="9" t="inlineStr"/>
       <c r="F105" s="9" t="inlineStr"/>
       <c r="G105" s="9" t="inlineStr"/>
       <c r="H105" s="9" t="inlineStr"/>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_6[1]
-▸ &amp;kp LS(HOME)</t>
-        </is>
-      </c>
+      <c r="I105" s="9" t="inlineStr"/>
       <c r="J105" s="9" t="inlineStr"/>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
-      <c r="M105" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="M105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -11138,7 +11142,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -11170,13 +11174,13 @@
       <c r="I106" s="7" t="inlineStr">
         <is>
           <t>pos 15
-&amp;kp LS(LEFT)</t>
+&amp;none</t>
         </is>
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
           <t>pos 16
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
@@ -11188,13 +11192,13 @@
       <c r="L106" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;kp RCTRL</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -11204,30 +11208,26 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LCTRL</t>
-        </is>
-      </c>
+      <c r="B107" s="9" t="inlineStr"/>
       <c r="C107" s="9" t="inlineStr"/>
       <c r="D107" s="9" t="inlineStr"/>
       <c r="E107" s="9" t="inlineStr"/>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="J107" s="9" t="inlineStr"/>
+      <c r="I107" s="9" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB1</t>
+        </is>
+      </c>
       <c r="K107" s="9" t="inlineStr"/>
-      <c r="L107" s="9" t="inlineStr"/>
-      <c r="M107" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RCTRL</t>
-        </is>
-      </c>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB2</t>
+        </is>
+      </c>
+      <c r="M107" s="9" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -11238,7 +11238,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -11281,7 +11281,7 @@
       <c r="J108" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="K108" s="7" t="inlineStr">
@@ -11293,13 +11293,13 @@
       <c r="L108" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="M108" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;kp RIGHT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -11309,11 +11309,7 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="inlineStr"/>
       <c r="C109" s="9" t="inlineStr"/>
       <c r="D109" s="9" t="inlineStr"/>
       <c r="E109" s="9" t="inlineStr"/>
@@ -11321,14 +11317,18 @@
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
       <c r="I109" s="9" t="inlineStr"/>
-      <c r="J109" s="9" t="inlineStr"/>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB4</t>
+        </is>
+      </c>
       <c r="K109" s="9" t="inlineStr"/>
-      <c r="L109" s="9" t="inlineStr"/>
-      <c r="M109" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB5</t>
+        </is>
+      </c>
+      <c r="M109" s="9" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -11425,15 +11425,15 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A102:M102"/>
+    <mergeCell ref="A76:M76"/>
+    <mergeCell ref="A66:M66"/>
     <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A94:M94"/>
+    <mergeCell ref="A103:M103"/>
     <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A91:M91"/>
     <mergeCell ref="A55:M55"/>
-    <mergeCell ref="A64:M64"/>
-    <mergeCell ref="A73:M73"/>
     <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A82:M82"/>
+    <mergeCell ref="A85:M85"/>
     <mergeCell ref="A28:M28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
